--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,14 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40F8F3F8-54AF-4D5D-BCF8-24AA864B7A71}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1A6996-0A93-4C50-8D95-672D46F56434}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
+    <sheet name="Creation1" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="25">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -451,14 +452,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,7 +470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -480,7 +481,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -491,7 +492,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -502,7 +503,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -513,7 +514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -524,7 +525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -535,7 +536,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -546,7 +547,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -557,7 +558,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -568,7 +569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -579,7 +580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -590,7 +591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -601,7 +602,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -612,7 +613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -630,4 +631,186 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A1553C-F7A5-4DD1-9371-6162AF52CB21}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="40.5703125" customWidth="1"/>
+    <col min="3" max="3" width="64.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{BC8EC09B-8BBA-411A-B94C-0975C77042EA}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1A6996-0A93-4C50-8D95-672D46F56434}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0104B4FC-431A-4D61-AF32-73B657BC7FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
     <sheet name="Creation1" sheetId="4" r:id="rId2"/>
+    <sheet name="CreationWithoutDescription" sheetId="5" r:id="rId3"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="26">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -96,6 +97,9 @@
   </si>
   <si>
     <t>fieldIsWBSRequired__c</t>
+  </si>
+  <si>
+    <t>Automation Internal Program for description</t>
   </si>
 </sst>
 </file>
@@ -159,7 +163,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -170,6 +174,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -452,14 +468,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,7 +486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -481,7 +497,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -492,7 +508,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -503,7 +519,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -514,7 +530,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -525,7 +541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -536,7 +552,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -547,7 +563,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -558,7 +574,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -569,7 +585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -580,7 +596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -591,7 +607,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -602,7 +618,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -613,7 +629,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -636,13 +652,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A1553C-F7A5-4DD1-9371-6162AF52CB21}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="40.5703125" customWidth="1"/>
-    <col min="3" max="3" width="64.28515625" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" customWidth="1"/>
+    <col min="3" max="3" width="64.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -653,7 +669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -664,7 +680,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -675,7 +691,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -686,7 +702,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -697,7 +713,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -708,7 +724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -719,7 +735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -730,7 +746,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -741,7 +757,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -752,7 +768,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -763,7 +779,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -774,7 +790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -785,7 +801,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -796,7 +812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -813,4 +829,176 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50E0F2B-3F25-474D-88CC-BA332CE28F6A}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="30.90625" customWidth="1"/>
+    <col min="3" max="3" width="44.81640625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{74176F69-6666-426F-8C26-039BF58B3877}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,16 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0104B4FC-431A-4D61-AF32-73B657BC7FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31A8171-F5E4-4C99-A795-CE56041B2248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
     <sheet name="Creation1" sheetId="4" r:id="rId2"/>
     <sheet name="CreationWithoutDescription" sheetId="5" r:id="rId3"/>
+    <sheet name="CreationForAnnouncement" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="27">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -101,6 +102,9 @@
   <si>
     <t>Automation Internal Program for description</t>
   </si>
+  <si>
+    <t xml:space="preserve">Automation Internal Program for Announcement </t>
+  </si>
 </sst>
 </file>
 
@@ -163,7 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -186,6 +190,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -468,14 +474,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -497,7 +503,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -508,7 +514,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -519,7 +525,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -530,7 +536,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -541,7 +547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -552,7 +558,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -563,7 +569,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -574,7 +580,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -585,7 +591,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -596,7 +602,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -607,7 +613,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -618,7 +624,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -629,7 +635,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -652,13 +658,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A1553C-F7A5-4DD1-9371-6162AF52CB21}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.54296875" customWidth="1"/>
-    <col min="3" max="3" width="64.26953125" customWidth="1"/>
+    <col min="2" max="2" width="40.5703125" customWidth="1"/>
+    <col min="3" max="3" width="64.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -669,7 +675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -680,7 +686,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -691,7 +697,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -702,7 +708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -713,7 +719,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -724,7 +730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -735,7 +741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -746,7 +752,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -757,7 +763,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -768,7 +774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -779,7 +785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -790,7 +796,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -801,7 +807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -812,7 +818,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -834,14 +840,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50E0F2B-3F25-474D-88CC-BA332CE28F6A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.90625" customWidth="1"/>
-    <col min="3" max="3" width="44.81640625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="20.26953125" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -852,7 +858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -863,7 +869,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -874,7 +880,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -885,7 +891,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -896,7 +902,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -907,7 +913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -918,7 +924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -929,7 +935,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -940,7 +946,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -951,7 +957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -962,7 +968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -973,7 +979,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -984,7 +990,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1001,4 +1007,5653 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0851E1-AAF8-44F9-AFC4-73C66EBF0B6F}">
+  <dimension ref="A1:XFC15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="2" width="39" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" style="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AD1" s="6"/>
+      <c r="AG1" s="6"/>
+      <c r="AJ1" s="6"/>
+      <c r="AM1" s="6"/>
+      <c r="AP1" s="6"/>
+      <c r="AS1" s="6"/>
+      <c r="AV1" s="6"/>
+      <c r="AY1" s="6"/>
+      <c r="BB1" s="6"/>
+      <c r="BE1" s="6"/>
+      <c r="BH1" s="6"/>
+      <c r="BK1" s="6"/>
+      <c r="BN1" s="6"/>
+      <c r="BQ1" s="6"/>
+      <c r="BT1" s="6"/>
+      <c r="BW1" s="6"/>
+      <c r="BZ1" s="6"/>
+      <c r="CC1" s="6"/>
+      <c r="CF1" s="6"/>
+      <c r="CI1" s="6"/>
+      <c r="CL1" s="6"/>
+      <c r="CO1" s="6"/>
+      <c r="CR1" s="6"/>
+      <c r="CU1" s="6"/>
+      <c r="CX1" s="6"/>
+      <c r="DA1" s="6"/>
+      <c r="DD1" s="6"/>
+      <c r="DG1" s="6"/>
+      <c r="DJ1" s="6"/>
+      <c r="DM1" s="6"/>
+      <c r="DP1" s="6"/>
+      <c r="DS1" s="6"/>
+      <c r="DV1" s="6"/>
+      <c r="DY1" s="6"/>
+      <c r="EB1" s="6"/>
+      <c r="EE1" s="6"/>
+      <c r="EH1" s="6"/>
+      <c r="EK1" s="6"/>
+      <c r="EN1" s="6"/>
+      <c r="EQ1" s="6"/>
+      <c r="ET1" s="6"/>
+      <c r="EW1" s="6"/>
+      <c r="EZ1" s="6"/>
+      <c r="FC1" s="6"/>
+      <c r="FF1" s="6"/>
+      <c r="FI1" s="6"/>
+      <c r="FL1" s="6"/>
+      <c r="FO1" s="6"/>
+      <c r="FR1" s="6"/>
+      <c r="FU1" s="6"/>
+      <c r="FX1" s="6"/>
+      <c r="GA1" s="6"/>
+      <c r="GD1" s="6"/>
+      <c r="GG1" s="6"/>
+      <c r="GJ1" s="6"/>
+      <c r="GM1" s="6"/>
+      <c r="GP1" s="6"/>
+      <c r="GS1" s="6"/>
+      <c r="GV1" s="6"/>
+      <c r="GY1" s="6"/>
+      <c r="HB1" s="6"/>
+      <c r="HE1" s="6"/>
+      <c r="HH1" s="6"/>
+      <c r="HK1" s="6"/>
+      <c r="HN1" s="6"/>
+      <c r="HQ1" s="6"/>
+      <c r="HT1" s="6"/>
+      <c r="HW1" s="6"/>
+      <c r="HZ1" s="6"/>
+      <c r="IC1" s="6"/>
+      <c r="IF1" s="6"/>
+      <c r="II1" s="6"/>
+      <c r="IL1" s="6"/>
+      <c r="IO1" s="6"/>
+      <c r="IR1" s="6"/>
+      <c r="IU1" s="6"/>
+      <c r="IX1" s="6"/>
+      <c r="JA1" s="6"/>
+      <c r="JD1" s="6"/>
+      <c r="JG1" s="6"/>
+      <c r="JJ1" s="6"/>
+      <c r="JM1" s="6"/>
+      <c r="JP1" s="6"/>
+      <c r="JS1" s="6"/>
+      <c r="JV1" s="6"/>
+      <c r="JY1" s="6"/>
+      <c r="KB1" s="6"/>
+      <c r="KE1" s="6"/>
+      <c r="KH1" s="6"/>
+      <c r="KK1" s="6"/>
+      <c r="KN1" s="6"/>
+      <c r="KQ1" s="6"/>
+      <c r="KT1" s="6"/>
+      <c r="KW1" s="6"/>
+      <c r="KZ1" s="6"/>
+      <c r="LC1" s="6"/>
+      <c r="LF1" s="6"/>
+      <c r="LI1" s="6"/>
+      <c r="LL1" s="6"/>
+      <c r="LO1" s="6"/>
+      <c r="LR1" s="6"/>
+      <c r="LU1" s="6"/>
+      <c r="LX1" s="6"/>
+      <c r="MA1" s="6"/>
+      <c r="MD1" s="6"/>
+      <c r="MG1" s="6"/>
+      <c r="MJ1" s="6"/>
+      <c r="MM1" s="6"/>
+      <c r="MP1" s="6"/>
+      <c r="MS1" s="6"/>
+      <c r="MV1" s="6"/>
+      <c r="MY1" s="6"/>
+      <c r="NB1" s="6"/>
+      <c r="NE1" s="6"/>
+      <c r="NH1" s="6"/>
+      <c r="NK1" s="6"/>
+      <c r="NN1" s="6"/>
+      <c r="NQ1" s="6"/>
+      <c r="NT1" s="6"/>
+      <c r="NW1" s="6"/>
+      <c r="NZ1" s="6"/>
+      <c r="OC1" s="6"/>
+      <c r="OF1" s="6"/>
+      <c r="OI1" s="6"/>
+      <c r="OL1" s="6"/>
+      <c r="OO1" s="6"/>
+      <c r="OR1" s="6"/>
+      <c r="OU1" s="6"/>
+      <c r="OX1" s="6"/>
+      <c r="PA1" s="6"/>
+      <c r="PD1" s="6"/>
+      <c r="PG1" s="6"/>
+      <c r="PJ1" s="6"/>
+      <c r="PM1" s="6"/>
+      <c r="PP1" s="6"/>
+      <c r="PS1" s="6"/>
+      <c r="PV1" s="6"/>
+      <c r="PY1" s="6"/>
+      <c r="QB1" s="6"/>
+      <c r="QE1" s="6"/>
+      <c r="QH1" s="6"/>
+      <c r="QK1" s="6"/>
+      <c r="QN1" s="6"/>
+      <c r="QQ1" s="6"/>
+      <c r="QT1" s="6"/>
+      <c r="QW1" s="6"/>
+      <c r="QZ1" s="6"/>
+      <c r="RC1" s="6"/>
+      <c r="RF1" s="6"/>
+      <c r="RI1" s="6"/>
+      <c r="RL1" s="6"/>
+      <c r="RO1" s="6"/>
+      <c r="RR1" s="6"/>
+      <c r="RU1" s="6"/>
+      <c r="RX1" s="6"/>
+      <c r="SA1" s="6"/>
+      <c r="SD1" s="6"/>
+      <c r="SG1" s="6"/>
+      <c r="SJ1" s="6"/>
+      <c r="SM1" s="6"/>
+      <c r="SP1" s="6"/>
+      <c r="SS1" s="6"/>
+      <c r="SV1" s="6"/>
+      <c r="SY1" s="6"/>
+      <c r="TB1" s="6"/>
+      <c r="TE1" s="6"/>
+      <c r="TH1" s="6"/>
+      <c r="TK1" s="6"/>
+      <c r="TN1" s="6"/>
+      <c r="TQ1" s="6"/>
+      <c r="TT1" s="6"/>
+      <c r="TW1" s="6"/>
+      <c r="TZ1" s="6"/>
+      <c r="UC1" s="6"/>
+      <c r="UF1" s="6"/>
+      <c r="UI1" s="6"/>
+      <c r="UL1" s="6"/>
+      <c r="UO1" s="6"/>
+      <c r="UR1" s="6"/>
+      <c r="UU1" s="6"/>
+      <c r="UX1" s="6"/>
+      <c r="VA1" s="6"/>
+      <c r="VD1" s="6"/>
+      <c r="VG1" s="6"/>
+      <c r="VJ1" s="6"/>
+      <c r="VM1" s="6"/>
+      <c r="VP1" s="6"/>
+      <c r="VS1" s="6"/>
+      <c r="VV1" s="6"/>
+      <c r="VY1" s="6"/>
+      <c r="WB1" s="6"/>
+      <c r="WE1" s="6"/>
+      <c r="WH1" s="6"/>
+      <c r="WK1" s="6"/>
+      <c r="WN1" s="6"/>
+      <c r="WQ1" s="6"/>
+      <c r="WT1" s="6"/>
+      <c r="WW1" s="6"/>
+      <c r="WZ1" s="6"/>
+      <c r="XC1" s="6"/>
+      <c r="XF1" s="6"/>
+      <c r="XI1" s="6"/>
+      <c r="XL1" s="6"/>
+      <c r="XO1" s="6"/>
+      <c r="XR1" s="6"/>
+      <c r="XU1" s="6"/>
+      <c r="XX1" s="6"/>
+      <c r="YA1" s="6"/>
+      <c r="YD1" s="6"/>
+      <c r="YG1" s="6"/>
+      <c r="YJ1" s="6"/>
+      <c r="YM1" s="6"/>
+      <c r="YP1" s="6"/>
+      <c r="YS1" s="6"/>
+      <c r="YV1" s="6"/>
+      <c r="YY1" s="6"/>
+      <c r="ZB1" s="6"/>
+      <c r="ZE1" s="6"/>
+      <c r="ZH1" s="6"/>
+      <c r="ZK1" s="6"/>
+      <c r="ZN1" s="6"/>
+      <c r="ZQ1" s="6"/>
+      <c r="ZT1" s="6"/>
+      <c r="ZW1" s="6"/>
+      <c r="ZZ1" s="6"/>
+      <c r="AAC1" s="6"/>
+      <c r="AAF1" s="6"/>
+      <c r="AAI1" s="6"/>
+      <c r="AAL1" s="6"/>
+      <c r="AAO1" s="6"/>
+      <c r="AAR1" s="6"/>
+      <c r="AAU1" s="6"/>
+      <c r="AAX1" s="6"/>
+      <c r="ABA1" s="6"/>
+      <c r="ABD1" s="6"/>
+      <c r="ABG1" s="6"/>
+      <c r="ABJ1" s="6"/>
+      <c r="ABM1" s="6"/>
+      <c r="ABP1" s="6"/>
+      <c r="ABS1" s="6"/>
+      <c r="ABV1" s="6"/>
+      <c r="ABY1" s="6"/>
+      <c r="ACB1" s="6"/>
+      <c r="ACE1" s="6"/>
+      <c r="ACH1" s="6"/>
+      <c r="ACK1" s="6"/>
+      <c r="ACN1" s="6"/>
+      <c r="ACQ1" s="6"/>
+      <c r="ACT1" s="6"/>
+      <c r="ACW1" s="6"/>
+      <c r="ACZ1" s="6"/>
+      <c r="ADC1" s="6"/>
+      <c r="ADF1" s="6"/>
+      <c r="ADI1" s="6"/>
+      <c r="ADL1" s="6"/>
+      <c r="ADO1" s="6"/>
+      <c r="ADR1" s="6"/>
+      <c r="ADU1" s="6"/>
+      <c r="ADX1" s="6"/>
+      <c r="AEA1" s="6"/>
+      <c r="AED1" s="6"/>
+      <c r="AEG1" s="6"/>
+      <c r="AEJ1" s="6"/>
+      <c r="AEM1" s="6"/>
+      <c r="AEP1" s="6"/>
+      <c r="AES1" s="6"/>
+      <c r="AEV1" s="6"/>
+      <c r="AEY1" s="6"/>
+      <c r="AFB1" s="6"/>
+      <c r="AFE1" s="6"/>
+      <c r="AFH1" s="6"/>
+      <c r="AFK1" s="6"/>
+      <c r="AFN1" s="6"/>
+      <c r="AFQ1" s="6"/>
+      <c r="AFT1" s="6"/>
+      <c r="AFW1" s="6"/>
+      <c r="AFZ1" s="6"/>
+      <c r="AGC1" s="6"/>
+      <c r="AGF1" s="6"/>
+      <c r="AGI1" s="6"/>
+      <c r="AGL1" s="6"/>
+      <c r="AGO1" s="6"/>
+      <c r="AGR1" s="6"/>
+      <c r="AGU1" s="6"/>
+      <c r="AGX1" s="6"/>
+      <c r="AHA1" s="6"/>
+      <c r="AHD1" s="6"/>
+      <c r="AHG1" s="6"/>
+      <c r="AHJ1" s="6"/>
+      <c r="AHM1" s="6"/>
+      <c r="AHP1" s="6"/>
+      <c r="AHS1" s="6"/>
+      <c r="AHV1" s="6"/>
+      <c r="AHY1" s="6"/>
+      <c r="AIB1" s="6"/>
+      <c r="AIE1" s="6"/>
+      <c r="AIH1" s="6"/>
+      <c r="AIK1" s="6"/>
+      <c r="AIN1" s="6"/>
+      <c r="AIQ1" s="6"/>
+      <c r="AIT1" s="6"/>
+      <c r="AIW1" s="6"/>
+      <c r="AIZ1" s="6"/>
+      <c r="AJC1" s="6"/>
+      <c r="AJF1" s="6"/>
+      <c r="AJI1" s="6"/>
+      <c r="AJL1" s="6"/>
+      <c r="AJO1" s="6"/>
+      <c r="AJR1" s="6"/>
+      <c r="AJU1" s="6"/>
+      <c r="AJX1" s="6"/>
+      <c r="AKA1" s="6"/>
+      <c r="AKD1" s="6"/>
+      <c r="AKG1" s="6"/>
+      <c r="AKJ1" s="6"/>
+      <c r="AKM1" s="6"/>
+      <c r="AKP1" s="6"/>
+      <c r="AKS1" s="6"/>
+      <c r="AKV1" s="6"/>
+      <c r="AKY1" s="6"/>
+      <c r="ALB1" s="6"/>
+      <c r="ALE1" s="6"/>
+      <c r="ALH1" s="6"/>
+      <c r="ALK1" s="6"/>
+      <c r="ALN1" s="6"/>
+      <c r="ALQ1" s="6"/>
+      <c r="ALT1" s="6"/>
+      <c r="ALW1" s="6"/>
+      <c r="ALZ1" s="6"/>
+      <c r="AMC1" s="6"/>
+      <c r="AMF1" s="6"/>
+      <c r="AMI1" s="6"/>
+      <c r="AML1" s="6"/>
+      <c r="AMO1" s="6"/>
+      <c r="AMR1" s="6"/>
+      <c r="AMU1" s="6"/>
+      <c r="AMX1" s="6"/>
+      <c r="ANA1" s="6"/>
+      <c r="AND1" s="6"/>
+      <c r="ANG1" s="6"/>
+      <c r="ANJ1" s="6"/>
+      <c r="ANM1" s="6"/>
+      <c r="ANP1" s="6"/>
+      <c r="ANS1" s="6"/>
+      <c r="ANV1" s="6"/>
+      <c r="ANY1" s="6"/>
+      <c r="AOB1" s="6"/>
+      <c r="AOE1" s="6"/>
+      <c r="AOH1" s="6"/>
+      <c r="AOK1" s="6"/>
+      <c r="AON1" s="6"/>
+      <c r="AOQ1" s="6"/>
+      <c r="AOT1" s="6"/>
+      <c r="AOW1" s="6"/>
+      <c r="AOZ1" s="6"/>
+      <c r="APC1" s="6"/>
+      <c r="APF1" s="6"/>
+      <c r="API1" s="6"/>
+      <c r="APL1" s="6"/>
+      <c r="APO1" s="6"/>
+      <c r="APR1" s="6"/>
+      <c r="APU1" s="6"/>
+      <c r="APX1" s="6"/>
+      <c r="AQA1" s="6"/>
+      <c r="AQD1" s="6"/>
+      <c r="AQG1" s="6"/>
+      <c r="AQJ1" s="6"/>
+      <c r="AQM1" s="6"/>
+      <c r="AQP1" s="6"/>
+      <c r="AQS1" s="6"/>
+      <c r="AQV1" s="6"/>
+      <c r="AQY1" s="6"/>
+      <c r="ARB1" s="6"/>
+      <c r="ARE1" s="6"/>
+      <c r="ARH1" s="6"/>
+      <c r="ARK1" s="6"/>
+      <c r="ARN1" s="6"/>
+      <c r="ARQ1" s="6"/>
+      <c r="ART1" s="6"/>
+      <c r="ARW1" s="6"/>
+      <c r="ARZ1" s="6"/>
+      <c r="ASC1" s="6"/>
+      <c r="ASF1" s="6"/>
+      <c r="ASI1" s="6"/>
+      <c r="ASL1" s="6"/>
+      <c r="ASO1" s="6"/>
+      <c r="ASR1" s="6"/>
+      <c r="ASU1" s="6"/>
+      <c r="ASX1" s="6"/>
+      <c r="ATA1" s="6"/>
+      <c r="ATD1" s="6"/>
+      <c r="ATG1" s="6"/>
+      <c r="ATJ1" s="6"/>
+      <c r="ATM1" s="6"/>
+      <c r="ATP1" s="6"/>
+      <c r="ATS1" s="6"/>
+      <c r="ATV1" s="6"/>
+      <c r="ATY1" s="6"/>
+      <c r="AUB1" s="6"/>
+      <c r="AUE1" s="6"/>
+      <c r="AUH1" s="6"/>
+      <c r="AUK1" s="6"/>
+      <c r="AUN1" s="6"/>
+      <c r="AUQ1" s="6"/>
+      <c r="AUT1" s="6"/>
+      <c r="AUW1" s="6"/>
+      <c r="AUZ1" s="6"/>
+      <c r="AVC1" s="6"/>
+      <c r="AVF1" s="6"/>
+      <c r="AVI1" s="6"/>
+      <c r="AVL1" s="6"/>
+      <c r="AVO1" s="6"/>
+      <c r="AVR1" s="6"/>
+      <c r="AVU1" s="6"/>
+      <c r="AVX1" s="6"/>
+      <c r="AWA1" s="6"/>
+      <c r="AWD1" s="6"/>
+      <c r="AWG1" s="6"/>
+      <c r="AWJ1" s="6"/>
+      <c r="AWM1" s="6"/>
+      <c r="AWP1" s="6"/>
+      <c r="AWS1" s="6"/>
+      <c r="AWV1" s="6"/>
+      <c r="AWY1" s="6"/>
+      <c r="AXB1" s="6"/>
+      <c r="AXE1" s="6"/>
+      <c r="AXH1" s="6"/>
+      <c r="AXK1" s="6"/>
+      <c r="AXN1" s="6"/>
+      <c r="AXQ1" s="6"/>
+      <c r="AXT1" s="6"/>
+      <c r="AXW1" s="6"/>
+      <c r="AXZ1" s="6"/>
+      <c r="AYC1" s="6"/>
+      <c r="AYF1" s="6"/>
+      <c r="AYI1" s="6"/>
+      <c r="AYL1" s="6"/>
+      <c r="AYO1" s="6"/>
+      <c r="AYR1" s="6"/>
+      <c r="AYU1" s="6"/>
+      <c r="AYX1" s="6"/>
+      <c r="AZA1" s="6"/>
+      <c r="AZD1" s="6"/>
+      <c r="AZG1" s="6"/>
+      <c r="AZJ1" s="6"/>
+      <c r="AZM1" s="6"/>
+      <c r="AZP1" s="6"/>
+      <c r="AZS1" s="6"/>
+      <c r="AZV1" s="6"/>
+      <c r="AZY1" s="6"/>
+      <c r="BAB1" s="6"/>
+      <c r="BAE1" s="6"/>
+      <c r="BAH1" s="6"/>
+      <c r="BAK1" s="6"/>
+      <c r="BAN1" s="6"/>
+      <c r="BAQ1" s="6"/>
+      <c r="BAT1" s="6"/>
+      <c r="BAW1" s="6"/>
+      <c r="BAZ1" s="6"/>
+      <c r="BBC1" s="6"/>
+      <c r="BBF1" s="6"/>
+      <c r="BBI1" s="6"/>
+      <c r="BBL1" s="6"/>
+      <c r="BBO1" s="6"/>
+      <c r="BBR1" s="6"/>
+      <c r="BBU1" s="6"/>
+      <c r="BBX1" s="6"/>
+      <c r="BCA1" s="6"/>
+      <c r="BCD1" s="6"/>
+      <c r="BCG1" s="6"/>
+      <c r="BCJ1" s="6"/>
+      <c r="BCM1" s="6"/>
+      <c r="BCP1" s="6"/>
+      <c r="BCS1" s="6"/>
+      <c r="BCV1" s="6"/>
+      <c r="BCY1" s="6"/>
+      <c r="BDB1" s="6"/>
+      <c r="BDE1" s="6"/>
+      <c r="BDH1" s="6"/>
+      <c r="BDK1" s="6"/>
+      <c r="BDN1" s="6"/>
+      <c r="BDQ1" s="6"/>
+      <c r="BDT1" s="6"/>
+      <c r="BDW1" s="6"/>
+      <c r="BDZ1" s="6"/>
+      <c r="BEC1" s="6"/>
+      <c r="BEF1" s="6"/>
+      <c r="BEI1" s="6"/>
+      <c r="BEL1" s="6"/>
+      <c r="BEO1" s="6"/>
+      <c r="BER1" s="6"/>
+      <c r="BEU1" s="6"/>
+      <c r="BEX1" s="6"/>
+      <c r="BFA1" s="6"/>
+      <c r="BFD1" s="6"/>
+      <c r="BFG1" s="6"/>
+      <c r="BFJ1" s="6"/>
+      <c r="BFM1" s="6"/>
+      <c r="BFP1" s="6"/>
+      <c r="BFS1" s="6"/>
+      <c r="BFV1" s="6"/>
+      <c r="BFY1" s="6"/>
+      <c r="BGB1" s="6"/>
+      <c r="BGE1" s="6"/>
+      <c r="BGH1" s="6"/>
+      <c r="BGK1" s="6"/>
+      <c r="BGN1" s="6"/>
+      <c r="BGQ1" s="6"/>
+      <c r="BGT1" s="6"/>
+      <c r="BGW1" s="6"/>
+      <c r="BGZ1" s="6"/>
+      <c r="BHC1" s="6"/>
+      <c r="BHF1" s="6"/>
+      <c r="BHI1" s="6"/>
+      <c r="BHL1" s="6"/>
+      <c r="BHO1" s="6"/>
+      <c r="BHR1" s="6"/>
+      <c r="BHU1" s="6"/>
+      <c r="BHX1" s="6"/>
+      <c r="BIA1" s="6"/>
+      <c r="BID1" s="6"/>
+      <c r="BIG1" s="6"/>
+      <c r="BIJ1" s="6"/>
+      <c r="BIM1" s="6"/>
+      <c r="BIP1" s="6"/>
+      <c r="BIS1" s="6"/>
+      <c r="BIV1" s="6"/>
+      <c r="BIY1" s="6"/>
+      <c r="BJB1" s="6"/>
+      <c r="BJE1" s="6"/>
+      <c r="BJH1" s="6"/>
+      <c r="BJK1" s="6"/>
+      <c r="BJN1" s="6"/>
+      <c r="BJQ1" s="6"/>
+      <c r="BJT1" s="6"/>
+      <c r="BJW1" s="6"/>
+      <c r="BJZ1" s="6"/>
+      <c r="BKC1" s="6"/>
+      <c r="BKF1" s="6"/>
+      <c r="BKI1" s="6"/>
+      <c r="BKL1" s="6"/>
+      <c r="BKO1" s="6"/>
+      <c r="BKR1" s="6"/>
+      <c r="BKU1" s="6"/>
+      <c r="BKX1" s="6"/>
+      <c r="BLA1" s="6"/>
+      <c r="BLD1" s="6"/>
+      <c r="BLG1" s="6"/>
+      <c r="BLJ1" s="6"/>
+      <c r="BLM1" s="6"/>
+      <c r="BLP1" s="6"/>
+      <c r="BLS1" s="6"/>
+      <c r="BLV1" s="6"/>
+      <c r="BLY1" s="6"/>
+      <c r="BMB1" s="6"/>
+      <c r="BME1" s="6"/>
+      <c r="BMH1" s="6"/>
+      <c r="BMK1" s="6"/>
+      <c r="BMN1" s="6"/>
+      <c r="BMQ1" s="6"/>
+      <c r="BMT1" s="6"/>
+      <c r="BMW1" s="6"/>
+      <c r="BMZ1" s="6"/>
+      <c r="BNC1" s="6"/>
+      <c r="BNF1" s="6"/>
+      <c r="BNI1" s="6"/>
+      <c r="BNL1" s="6"/>
+      <c r="BNO1" s="6"/>
+      <c r="BNR1" s="6"/>
+      <c r="BNU1" s="6"/>
+      <c r="BNX1" s="6"/>
+      <c r="BOA1" s="6"/>
+      <c r="BOD1" s="6"/>
+      <c r="BOG1" s="6"/>
+      <c r="BOJ1" s="6"/>
+      <c r="BOM1" s="6"/>
+      <c r="BOP1" s="6"/>
+      <c r="BOS1" s="6"/>
+      <c r="BOV1" s="6"/>
+      <c r="BOY1" s="6"/>
+      <c r="BPB1" s="6"/>
+      <c r="BPE1" s="6"/>
+      <c r="BPH1" s="6"/>
+      <c r="BPK1" s="6"/>
+      <c r="BPN1" s="6"/>
+      <c r="BPQ1" s="6"/>
+      <c r="BPT1" s="6"/>
+      <c r="BPW1" s="6"/>
+      <c r="BPZ1" s="6"/>
+      <c r="BQC1" s="6"/>
+      <c r="BQF1" s="6"/>
+      <c r="BQI1" s="6"/>
+      <c r="BQL1" s="6"/>
+      <c r="BQO1" s="6"/>
+      <c r="BQR1" s="6"/>
+      <c r="BQU1" s="6"/>
+      <c r="BQX1" s="6"/>
+      <c r="BRA1" s="6"/>
+      <c r="BRD1" s="6"/>
+      <c r="BRG1" s="6"/>
+      <c r="BRJ1" s="6"/>
+      <c r="BRM1" s="6"/>
+      <c r="BRP1" s="6"/>
+      <c r="BRS1" s="6"/>
+      <c r="BRV1" s="6"/>
+      <c r="BRY1" s="6"/>
+      <c r="BSB1" s="6"/>
+      <c r="BSE1" s="6"/>
+      <c r="BSH1" s="6"/>
+      <c r="BSK1" s="6"/>
+      <c r="BSN1" s="6"/>
+      <c r="BSQ1" s="6"/>
+      <c r="BST1" s="6"/>
+      <c r="BSW1" s="6"/>
+      <c r="BSZ1" s="6"/>
+      <c r="BTC1" s="6"/>
+      <c r="BTF1" s="6"/>
+      <c r="BTI1" s="6"/>
+      <c r="BTL1" s="6"/>
+      <c r="BTO1" s="6"/>
+      <c r="BTR1" s="6"/>
+      <c r="BTU1" s="6"/>
+      <c r="BTX1" s="6"/>
+      <c r="BUA1" s="6"/>
+      <c r="BUD1" s="6"/>
+      <c r="BUG1" s="6"/>
+      <c r="BUJ1" s="6"/>
+      <c r="BUM1" s="6"/>
+      <c r="BUP1" s="6"/>
+      <c r="BUS1" s="6"/>
+      <c r="BUV1" s="6"/>
+      <c r="BUY1" s="6"/>
+      <c r="BVB1" s="6"/>
+      <c r="BVE1" s="6"/>
+      <c r="BVH1" s="6"/>
+      <c r="BVK1" s="6"/>
+      <c r="BVN1" s="6"/>
+      <c r="BVQ1" s="6"/>
+      <c r="BVT1" s="6"/>
+      <c r="BVW1" s="6"/>
+      <c r="BVZ1" s="6"/>
+      <c r="BWC1" s="6"/>
+      <c r="BWF1" s="6"/>
+      <c r="BWI1" s="6"/>
+      <c r="BWL1" s="6"/>
+      <c r="BWO1" s="6"/>
+      <c r="BWR1" s="6"/>
+      <c r="BWU1" s="6"/>
+      <c r="BWX1" s="6"/>
+      <c r="BXA1" s="6"/>
+      <c r="BXD1" s="6"/>
+      <c r="BXG1" s="6"/>
+      <c r="BXJ1" s="6"/>
+      <c r="BXM1" s="6"/>
+      <c r="BXP1" s="6"/>
+      <c r="BXS1" s="6"/>
+      <c r="BXV1" s="6"/>
+      <c r="BXY1" s="6"/>
+      <c r="BYB1" s="6"/>
+      <c r="BYE1" s="6"/>
+      <c r="BYH1" s="6"/>
+      <c r="BYK1" s="6"/>
+      <c r="BYN1" s="6"/>
+      <c r="BYQ1" s="6"/>
+      <c r="BYT1" s="6"/>
+      <c r="BYW1" s="6"/>
+      <c r="BYZ1" s="6"/>
+      <c r="BZC1" s="6"/>
+      <c r="BZF1" s="6"/>
+      <c r="BZI1" s="6"/>
+      <c r="BZL1" s="6"/>
+      <c r="BZO1" s="6"/>
+      <c r="BZR1" s="6"/>
+      <c r="BZU1" s="6"/>
+      <c r="BZX1" s="6"/>
+      <c r="CAA1" s="6"/>
+      <c r="CAD1" s="6"/>
+      <c r="CAG1" s="6"/>
+      <c r="CAJ1" s="6"/>
+      <c r="CAM1" s="6"/>
+      <c r="CAP1" s="6"/>
+      <c r="CAS1" s="6"/>
+      <c r="CAV1" s="6"/>
+      <c r="CAY1" s="6"/>
+      <c r="CBB1" s="6"/>
+      <c r="CBE1" s="6"/>
+      <c r="CBH1" s="6"/>
+      <c r="CBK1" s="6"/>
+      <c r="CBN1" s="6"/>
+      <c r="CBQ1" s="6"/>
+      <c r="CBT1" s="6"/>
+      <c r="CBW1" s="6"/>
+      <c r="CBZ1" s="6"/>
+      <c r="CCC1" s="6"/>
+      <c r="CCF1" s="6"/>
+      <c r="CCI1" s="6"/>
+      <c r="CCL1" s="6"/>
+      <c r="CCO1" s="6"/>
+      <c r="CCR1" s="6"/>
+      <c r="CCU1" s="6"/>
+      <c r="CCX1" s="6"/>
+      <c r="CDA1" s="6"/>
+      <c r="CDD1" s="6"/>
+      <c r="CDG1" s="6"/>
+      <c r="CDJ1" s="6"/>
+      <c r="CDM1" s="6"/>
+      <c r="CDP1" s="6"/>
+      <c r="CDS1" s="6"/>
+      <c r="CDV1" s="6"/>
+      <c r="CDY1" s="6"/>
+      <c r="CEB1" s="6"/>
+      <c r="CEE1" s="6"/>
+      <c r="CEH1" s="6"/>
+      <c r="CEK1" s="6"/>
+      <c r="CEN1" s="6"/>
+      <c r="CEQ1" s="6"/>
+      <c r="CET1" s="6"/>
+      <c r="CEW1" s="6"/>
+      <c r="CEZ1" s="6"/>
+      <c r="CFC1" s="6"/>
+      <c r="CFF1" s="6"/>
+      <c r="CFI1" s="6"/>
+      <c r="CFL1" s="6"/>
+      <c r="CFO1" s="6"/>
+      <c r="CFR1" s="6"/>
+      <c r="CFU1" s="6"/>
+      <c r="CFX1" s="6"/>
+      <c r="CGA1" s="6"/>
+      <c r="CGD1" s="6"/>
+      <c r="CGG1" s="6"/>
+      <c r="CGJ1" s="6"/>
+      <c r="CGM1" s="6"/>
+      <c r="CGP1" s="6"/>
+      <c r="CGS1" s="6"/>
+      <c r="CGV1" s="6"/>
+      <c r="CGY1" s="6"/>
+      <c r="CHB1" s="6"/>
+      <c r="CHE1" s="6"/>
+      <c r="CHH1" s="6"/>
+      <c r="CHK1" s="6"/>
+      <c r="CHN1" s="6"/>
+      <c r="CHQ1" s="6"/>
+      <c r="CHT1" s="6"/>
+      <c r="CHW1" s="6"/>
+      <c r="CHZ1" s="6"/>
+      <c r="CIC1" s="6"/>
+      <c r="CIF1" s="6"/>
+      <c r="CII1" s="6"/>
+      <c r="CIL1" s="6"/>
+      <c r="CIO1" s="6"/>
+      <c r="CIR1" s="6"/>
+      <c r="CIU1" s="6"/>
+      <c r="CIX1" s="6"/>
+      <c r="CJA1" s="6"/>
+      <c r="CJD1" s="6"/>
+      <c r="CJG1" s="6"/>
+      <c r="CJJ1" s="6"/>
+      <c r="CJM1" s="6"/>
+      <c r="CJP1" s="6"/>
+      <c r="CJS1" s="6"/>
+      <c r="CJV1" s="6"/>
+      <c r="CJY1" s="6"/>
+      <c r="CKB1" s="6"/>
+      <c r="CKE1" s="6"/>
+      <c r="CKH1" s="6"/>
+      <c r="CKK1" s="6"/>
+      <c r="CKN1" s="6"/>
+      <c r="CKQ1" s="6"/>
+      <c r="CKT1" s="6"/>
+      <c r="CKW1" s="6"/>
+      <c r="CKZ1" s="6"/>
+      <c r="CLC1" s="6"/>
+      <c r="CLF1" s="6"/>
+      <c r="CLI1" s="6"/>
+      <c r="CLL1" s="6"/>
+      <c r="CLO1" s="6"/>
+      <c r="CLR1" s="6"/>
+      <c r="CLU1" s="6"/>
+      <c r="CLX1" s="6"/>
+      <c r="CMA1" s="6"/>
+      <c r="CMD1" s="6"/>
+      <c r="CMG1" s="6"/>
+      <c r="CMJ1" s="6"/>
+      <c r="CMM1" s="6"/>
+      <c r="CMP1" s="6"/>
+      <c r="CMS1" s="6"/>
+      <c r="CMV1" s="6"/>
+      <c r="CMY1" s="6"/>
+      <c r="CNB1" s="6"/>
+      <c r="CNE1" s="6"/>
+      <c r="CNH1" s="6"/>
+      <c r="CNK1" s="6"/>
+      <c r="CNN1" s="6"/>
+      <c r="CNQ1" s="6"/>
+      <c r="CNT1" s="6"/>
+      <c r="CNW1" s="6"/>
+      <c r="CNZ1" s="6"/>
+      <c r="COC1" s="6"/>
+      <c r="COF1" s="6"/>
+      <c r="COI1" s="6"/>
+      <c r="COL1" s="6"/>
+      <c r="COO1" s="6"/>
+      <c r="COR1" s="6"/>
+      <c r="COU1" s="6"/>
+      <c r="COX1" s="6"/>
+      <c r="CPA1" s="6"/>
+      <c r="CPD1" s="6"/>
+      <c r="CPG1" s="6"/>
+      <c r="CPJ1" s="6"/>
+      <c r="CPM1" s="6"/>
+      <c r="CPP1" s="6"/>
+      <c r="CPS1" s="6"/>
+      <c r="CPV1" s="6"/>
+      <c r="CPY1" s="6"/>
+      <c r="CQB1" s="6"/>
+      <c r="CQE1" s="6"/>
+      <c r="CQH1" s="6"/>
+      <c r="CQK1" s="6"/>
+      <c r="CQN1" s="6"/>
+      <c r="CQQ1" s="6"/>
+      <c r="CQT1" s="6"/>
+      <c r="CQW1" s="6"/>
+      <c r="CQZ1" s="6"/>
+      <c r="CRC1" s="6"/>
+      <c r="CRF1" s="6"/>
+      <c r="CRI1" s="6"/>
+      <c r="CRL1" s="6"/>
+      <c r="CRO1" s="6"/>
+      <c r="CRR1" s="6"/>
+      <c r="CRU1" s="6"/>
+      <c r="CRX1" s="6"/>
+      <c r="CSA1" s="6"/>
+      <c r="CSD1" s="6"/>
+      <c r="CSG1" s="6"/>
+      <c r="CSJ1" s="6"/>
+      <c r="CSM1" s="6"/>
+      <c r="CSP1" s="6"/>
+      <c r="CSS1" s="6"/>
+      <c r="CSV1" s="6"/>
+      <c r="CSY1" s="6"/>
+      <c r="CTB1" s="6"/>
+      <c r="CTE1" s="6"/>
+      <c r="CTH1" s="6"/>
+      <c r="CTK1" s="6"/>
+      <c r="CTN1" s="6"/>
+      <c r="CTQ1" s="6"/>
+      <c r="CTT1" s="6"/>
+      <c r="CTW1" s="6"/>
+      <c r="CTZ1" s="6"/>
+      <c r="CUC1" s="6"/>
+      <c r="CUF1" s="6"/>
+      <c r="CUI1" s="6"/>
+      <c r="CUL1" s="6"/>
+      <c r="CUO1" s="6"/>
+      <c r="CUR1" s="6"/>
+      <c r="CUU1" s="6"/>
+      <c r="CUX1" s="6"/>
+      <c r="CVA1" s="6"/>
+      <c r="CVD1" s="6"/>
+      <c r="CVG1" s="6"/>
+      <c r="CVJ1" s="6"/>
+      <c r="CVM1" s="6"/>
+      <c r="CVP1" s="6"/>
+      <c r="CVS1" s="6"/>
+      <c r="CVV1" s="6"/>
+      <c r="CVY1" s="6"/>
+      <c r="CWB1" s="6"/>
+      <c r="CWE1" s="6"/>
+      <c r="CWH1" s="6"/>
+      <c r="CWK1" s="6"/>
+      <c r="CWN1" s="6"/>
+      <c r="CWQ1" s="6"/>
+      <c r="CWT1" s="6"/>
+      <c r="CWW1" s="6"/>
+      <c r="CWZ1" s="6"/>
+      <c r="CXC1" s="6"/>
+      <c r="CXF1" s="6"/>
+      <c r="CXI1" s="6"/>
+      <c r="CXL1" s="6"/>
+      <c r="CXO1" s="6"/>
+      <c r="CXR1" s="6"/>
+      <c r="CXU1" s="6"/>
+      <c r="CXX1" s="6"/>
+      <c r="CYA1" s="6"/>
+      <c r="CYD1" s="6"/>
+      <c r="CYG1" s="6"/>
+      <c r="CYJ1" s="6"/>
+      <c r="CYM1" s="6"/>
+      <c r="CYP1" s="6"/>
+      <c r="CYS1" s="6"/>
+      <c r="CYV1" s="6"/>
+      <c r="CYY1" s="6"/>
+      <c r="CZB1" s="6"/>
+      <c r="CZE1" s="6"/>
+      <c r="CZH1" s="6"/>
+      <c r="CZK1" s="6"/>
+      <c r="CZN1" s="6"/>
+      <c r="CZQ1" s="6"/>
+      <c r="CZT1" s="6"/>
+      <c r="CZW1" s="6"/>
+      <c r="CZZ1" s="6"/>
+      <c r="DAC1" s="6"/>
+      <c r="DAF1" s="6"/>
+      <c r="DAI1" s="6"/>
+      <c r="DAL1" s="6"/>
+      <c r="DAO1" s="6"/>
+      <c r="DAR1" s="6"/>
+      <c r="DAU1" s="6"/>
+      <c r="DAX1" s="6"/>
+      <c r="DBA1" s="6"/>
+      <c r="DBD1" s="6"/>
+      <c r="DBG1" s="6"/>
+      <c r="DBJ1" s="6"/>
+      <c r="DBM1" s="6"/>
+      <c r="DBP1" s="6"/>
+      <c r="DBS1" s="6"/>
+      <c r="DBV1" s="6"/>
+      <c r="DBY1" s="6"/>
+      <c r="DCB1" s="6"/>
+      <c r="DCE1" s="6"/>
+      <c r="DCH1" s="6"/>
+      <c r="DCK1" s="6"/>
+      <c r="DCN1" s="6"/>
+      <c r="DCQ1" s="6"/>
+      <c r="DCT1" s="6"/>
+      <c r="DCW1" s="6"/>
+      <c r="DCZ1" s="6"/>
+      <c r="DDC1" s="6"/>
+      <c r="DDF1" s="6"/>
+      <c r="DDI1" s="6"/>
+      <c r="DDL1" s="6"/>
+      <c r="DDO1" s="6"/>
+      <c r="DDR1" s="6"/>
+      <c r="DDU1" s="6"/>
+      <c r="DDX1" s="6"/>
+      <c r="DEA1" s="6"/>
+      <c r="DED1" s="6"/>
+      <c r="DEG1" s="6"/>
+      <c r="DEJ1" s="6"/>
+      <c r="DEM1" s="6"/>
+      <c r="DEP1" s="6"/>
+      <c r="DES1" s="6"/>
+      <c r="DEV1" s="6"/>
+      <c r="DEY1" s="6"/>
+      <c r="DFB1" s="6"/>
+      <c r="DFE1" s="6"/>
+      <c r="DFH1" s="6"/>
+      <c r="DFK1" s="6"/>
+      <c r="DFN1" s="6"/>
+      <c r="DFQ1" s="6"/>
+      <c r="DFT1" s="6"/>
+      <c r="DFW1" s="6"/>
+      <c r="DFZ1" s="6"/>
+      <c r="DGC1" s="6"/>
+      <c r="DGF1" s="6"/>
+      <c r="DGI1" s="6"/>
+      <c r="DGL1" s="6"/>
+      <c r="DGO1" s="6"/>
+      <c r="DGR1" s="6"/>
+      <c r="DGU1" s="6"/>
+      <c r="DGX1" s="6"/>
+      <c r="DHA1" s="6"/>
+      <c r="DHD1" s="6"/>
+      <c r="DHG1" s="6"/>
+      <c r="DHJ1" s="6"/>
+      <c r="DHM1" s="6"/>
+      <c r="DHP1" s="6"/>
+      <c r="DHS1" s="6"/>
+      <c r="DHV1" s="6"/>
+      <c r="DHY1" s="6"/>
+      <c r="DIB1" s="6"/>
+      <c r="DIE1" s="6"/>
+      <c r="DIH1" s="6"/>
+      <c r="DIK1" s="6"/>
+      <c r="DIN1" s="6"/>
+      <c r="DIQ1" s="6"/>
+      <c r="DIT1" s="6"/>
+      <c r="DIW1" s="6"/>
+      <c r="DIZ1" s="6"/>
+      <c r="DJC1" s="6"/>
+      <c r="DJF1" s="6"/>
+      <c r="DJI1" s="6"/>
+      <c r="DJL1" s="6"/>
+      <c r="DJO1" s="6"/>
+      <c r="DJR1" s="6"/>
+      <c r="DJU1" s="6"/>
+      <c r="DJX1" s="6"/>
+      <c r="DKA1" s="6"/>
+      <c r="DKD1" s="6"/>
+      <c r="DKG1" s="6"/>
+      <c r="DKJ1" s="6"/>
+      <c r="DKM1" s="6"/>
+      <c r="DKP1" s="6"/>
+      <c r="DKS1" s="6"/>
+      <c r="DKV1" s="6"/>
+      <c r="DKY1" s="6"/>
+      <c r="DLB1" s="6"/>
+      <c r="DLE1" s="6"/>
+      <c r="DLH1" s="6"/>
+      <c r="DLK1" s="6"/>
+      <c r="DLN1" s="6"/>
+      <c r="DLQ1" s="6"/>
+      <c r="DLT1" s="6"/>
+      <c r="DLW1" s="6"/>
+      <c r="DLZ1" s="6"/>
+      <c r="DMC1" s="6"/>
+      <c r="DMF1" s="6"/>
+      <c r="DMI1" s="6"/>
+      <c r="DML1" s="6"/>
+      <c r="DMO1" s="6"/>
+      <c r="DMR1" s="6"/>
+      <c r="DMU1" s="6"/>
+      <c r="DMX1" s="6"/>
+      <c r="DNA1" s="6"/>
+      <c r="DND1" s="6"/>
+      <c r="DNG1" s="6"/>
+      <c r="DNJ1" s="6"/>
+      <c r="DNM1" s="6"/>
+      <c r="DNP1" s="6"/>
+      <c r="DNS1" s="6"/>
+      <c r="DNV1" s="6"/>
+      <c r="DNY1" s="6"/>
+      <c r="DOB1" s="6"/>
+      <c r="DOE1" s="6"/>
+      <c r="DOH1" s="6"/>
+      <c r="DOK1" s="6"/>
+      <c r="DON1" s="6"/>
+      <c r="DOQ1" s="6"/>
+      <c r="DOT1" s="6"/>
+      <c r="DOW1" s="6"/>
+      <c r="DOZ1" s="6"/>
+      <c r="DPC1" s="6"/>
+      <c r="DPF1" s="6"/>
+      <c r="DPI1" s="6"/>
+      <c r="DPL1" s="6"/>
+      <c r="DPO1" s="6"/>
+      <c r="DPR1" s="6"/>
+      <c r="DPU1" s="6"/>
+      <c r="DPX1" s="6"/>
+      <c r="DQA1" s="6"/>
+      <c r="DQD1" s="6"/>
+      <c r="DQG1" s="6"/>
+      <c r="DQJ1" s="6"/>
+      <c r="DQM1" s="6"/>
+      <c r="DQP1" s="6"/>
+      <c r="DQS1" s="6"/>
+      <c r="DQV1" s="6"/>
+      <c r="DQY1" s="6"/>
+      <c r="DRB1" s="6"/>
+      <c r="DRE1" s="6"/>
+      <c r="DRH1" s="6"/>
+      <c r="DRK1" s="6"/>
+      <c r="DRN1" s="6"/>
+      <c r="DRQ1" s="6"/>
+      <c r="DRT1" s="6"/>
+      <c r="DRW1" s="6"/>
+      <c r="DRZ1" s="6"/>
+      <c r="DSC1" s="6"/>
+      <c r="DSF1" s="6"/>
+      <c r="DSI1" s="6"/>
+      <c r="DSL1" s="6"/>
+      <c r="DSO1" s="6"/>
+      <c r="DSR1" s="6"/>
+      <c r="DSU1" s="6"/>
+      <c r="DSX1" s="6"/>
+      <c r="DTA1" s="6"/>
+      <c r="DTD1" s="6"/>
+      <c r="DTG1" s="6"/>
+      <c r="DTJ1" s="6"/>
+      <c r="DTM1" s="6"/>
+      <c r="DTP1" s="6"/>
+      <c r="DTS1" s="6"/>
+      <c r="DTV1" s="6"/>
+      <c r="DTY1" s="6"/>
+      <c r="DUB1" s="6"/>
+      <c r="DUE1" s="6"/>
+      <c r="DUH1" s="6"/>
+      <c r="DUK1" s="6"/>
+      <c r="DUN1" s="6"/>
+      <c r="DUQ1" s="6"/>
+      <c r="DUT1" s="6"/>
+      <c r="DUW1" s="6"/>
+      <c r="DUZ1" s="6"/>
+      <c r="DVC1" s="6"/>
+      <c r="DVF1" s="6"/>
+      <c r="DVI1" s="6"/>
+      <c r="DVL1" s="6"/>
+      <c r="DVO1" s="6"/>
+      <c r="DVR1" s="6"/>
+      <c r="DVU1" s="6"/>
+      <c r="DVX1" s="6"/>
+      <c r="DWA1" s="6"/>
+      <c r="DWD1" s="6"/>
+      <c r="DWG1" s="6"/>
+      <c r="DWJ1" s="6"/>
+      <c r="DWM1" s="6"/>
+      <c r="DWP1" s="6"/>
+      <c r="DWS1" s="6"/>
+      <c r="DWV1" s="6"/>
+      <c r="DWY1" s="6"/>
+      <c r="DXB1" s="6"/>
+      <c r="DXE1" s="6"/>
+      <c r="DXH1" s="6"/>
+      <c r="DXK1" s="6"/>
+      <c r="DXN1" s="6"/>
+      <c r="DXQ1" s="6"/>
+      <c r="DXT1" s="6"/>
+      <c r="DXW1" s="6"/>
+      <c r="DXZ1" s="6"/>
+      <c r="DYC1" s="6"/>
+      <c r="DYF1" s="6"/>
+      <c r="DYI1" s="6"/>
+      <c r="DYL1" s="6"/>
+      <c r="DYO1" s="6"/>
+      <c r="DYR1" s="6"/>
+      <c r="DYU1" s="6"/>
+      <c r="DYX1" s="6"/>
+      <c r="DZA1" s="6"/>
+      <c r="DZD1" s="6"/>
+      <c r="DZG1" s="6"/>
+      <c r="DZJ1" s="6"/>
+      <c r="DZM1" s="6"/>
+      <c r="DZP1" s="6"/>
+      <c r="DZS1" s="6"/>
+      <c r="DZV1" s="6"/>
+      <c r="DZY1" s="6"/>
+      <c r="EAB1" s="6"/>
+      <c r="EAE1" s="6"/>
+      <c r="EAH1" s="6"/>
+      <c r="EAK1" s="6"/>
+      <c r="EAN1" s="6"/>
+      <c r="EAQ1" s="6"/>
+      <c r="EAT1" s="6"/>
+      <c r="EAW1" s="6"/>
+      <c r="EAZ1" s="6"/>
+      <c r="EBC1" s="6"/>
+      <c r="EBF1" s="6"/>
+      <c r="EBI1" s="6"/>
+      <c r="EBL1" s="6"/>
+      <c r="EBO1" s="6"/>
+      <c r="EBR1" s="6"/>
+      <c r="EBU1" s="6"/>
+      <c r="EBX1" s="6"/>
+      <c r="ECA1" s="6"/>
+      <c r="ECD1" s="6"/>
+      <c r="ECG1" s="6"/>
+      <c r="ECJ1" s="6"/>
+      <c r="ECM1" s="6"/>
+      <c r="ECP1" s="6"/>
+      <c r="ECS1" s="6"/>
+      <c r="ECV1" s="6"/>
+      <c r="ECY1" s="6"/>
+      <c r="EDB1" s="6"/>
+      <c r="EDE1" s="6"/>
+      <c r="EDH1" s="6"/>
+      <c r="EDK1" s="6"/>
+      <c r="EDN1" s="6"/>
+      <c r="EDQ1" s="6"/>
+      <c r="EDT1" s="6"/>
+      <c r="EDW1" s="6"/>
+      <c r="EDZ1" s="6"/>
+      <c r="EEC1" s="6"/>
+      <c r="EEF1" s="6"/>
+      <c r="EEI1" s="6"/>
+      <c r="EEL1" s="6"/>
+      <c r="EEO1" s="6"/>
+      <c r="EER1" s="6"/>
+      <c r="EEU1" s="6"/>
+      <c r="EEX1" s="6"/>
+      <c r="EFA1" s="6"/>
+      <c r="EFD1" s="6"/>
+      <c r="EFG1" s="6"/>
+      <c r="EFJ1" s="6"/>
+      <c r="EFM1" s="6"/>
+      <c r="EFP1" s="6"/>
+      <c r="EFS1" s="6"/>
+      <c r="EFV1" s="6"/>
+      <c r="EFY1" s="6"/>
+      <c r="EGB1" s="6"/>
+      <c r="EGE1" s="6"/>
+      <c r="EGH1" s="6"/>
+      <c r="EGK1" s="6"/>
+      <c r="EGN1" s="6"/>
+      <c r="EGQ1" s="6"/>
+      <c r="EGT1" s="6"/>
+      <c r="EGW1" s="6"/>
+      <c r="EGZ1" s="6"/>
+      <c r="EHC1" s="6"/>
+      <c r="EHF1" s="6"/>
+      <c r="EHI1" s="6"/>
+      <c r="EHL1" s="6"/>
+      <c r="EHO1" s="6"/>
+      <c r="EHR1" s="6"/>
+      <c r="EHU1" s="6"/>
+      <c r="EHX1" s="6"/>
+      <c r="EIA1" s="6"/>
+      <c r="EID1" s="6"/>
+      <c r="EIG1" s="6"/>
+      <c r="EIJ1" s="6"/>
+      <c r="EIM1" s="6"/>
+      <c r="EIP1" s="6"/>
+      <c r="EIS1" s="6"/>
+      <c r="EIV1" s="6"/>
+      <c r="EIY1" s="6"/>
+      <c r="EJB1" s="6"/>
+      <c r="EJE1" s="6"/>
+      <c r="EJH1" s="6"/>
+      <c r="EJK1" s="6"/>
+      <c r="EJN1" s="6"/>
+      <c r="EJQ1" s="6"/>
+      <c r="EJT1" s="6"/>
+      <c r="EJW1" s="6"/>
+      <c r="EJZ1" s="6"/>
+      <c r="EKC1" s="6"/>
+      <c r="EKF1" s="6"/>
+      <c r="EKI1" s="6"/>
+      <c r="EKL1" s="6"/>
+      <c r="EKO1" s="6"/>
+      <c r="EKR1" s="6"/>
+      <c r="EKU1" s="6"/>
+      <c r="EKX1" s="6"/>
+      <c r="ELA1" s="6"/>
+      <c r="ELD1" s="6"/>
+      <c r="ELG1" s="6"/>
+      <c r="ELJ1" s="6"/>
+      <c r="ELM1" s="6"/>
+      <c r="ELP1" s="6"/>
+      <c r="ELS1" s="6"/>
+      <c r="ELV1" s="6"/>
+      <c r="ELY1" s="6"/>
+      <c r="EMB1" s="6"/>
+      <c r="EME1" s="6"/>
+      <c r="EMH1" s="6"/>
+      <c r="EMK1" s="6"/>
+      <c r="EMN1" s="6"/>
+      <c r="EMQ1" s="6"/>
+      <c r="EMT1" s="6"/>
+      <c r="EMW1" s="6"/>
+      <c r="EMZ1" s="6"/>
+      <c r="ENC1" s="6"/>
+      <c r="ENF1" s="6"/>
+      <c r="ENI1" s="6"/>
+      <c r="ENL1" s="6"/>
+      <c r="ENO1" s="6"/>
+      <c r="ENR1" s="6"/>
+      <c r="ENU1" s="6"/>
+      <c r="ENX1" s="6"/>
+      <c r="EOA1" s="6"/>
+      <c r="EOD1" s="6"/>
+      <c r="EOG1" s="6"/>
+      <c r="EOJ1" s="6"/>
+      <c r="EOM1" s="6"/>
+      <c r="EOP1" s="6"/>
+      <c r="EOS1" s="6"/>
+      <c r="EOV1" s="6"/>
+      <c r="EOY1" s="6"/>
+      <c r="EPB1" s="6"/>
+      <c r="EPE1" s="6"/>
+      <c r="EPH1" s="6"/>
+      <c r="EPK1" s="6"/>
+      <c r="EPN1" s="6"/>
+      <c r="EPQ1" s="6"/>
+      <c r="EPT1" s="6"/>
+      <c r="EPW1" s="6"/>
+      <c r="EPZ1" s="6"/>
+      <c r="EQC1" s="6"/>
+      <c r="EQF1" s="6"/>
+      <c r="EQI1" s="6"/>
+      <c r="EQL1" s="6"/>
+      <c r="EQO1" s="6"/>
+      <c r="EQR1" s="6"/>
+      <c r="EQU1" s="6"/>
+      <c r="EQX1" s="6"/>
+      <c r="ERA1" s="6"/>
+      <c r="ERD1" s="6"/>
+      <c r="ERG1" s="6"/>
+      <c r="ERJ1" s="6"/>
+      <c r="ERM1" s="6"/>
+      <c r="ERP1" s="6"/>
+      <c r="ERS1" s="6"/>
+      <c r="ERV1" s="6"/>
+      <c r="ERY1" s="6"/>
+      <c r="ESB1" s="6"/>
+      <c r="ESE1" s="6"/>
+      <c r="ESH1" s="6"/>
+      <c r="ESK1" s="6"/>
+      <c r="ESN1" s="6"/>
+      <c r="ESQ1" s="6"/>
+      <c r="EST1" s="6"/>
+      <c r="ESW1" s="6"/>
+      <c r="ESZ1" s="6"/>
+      <c r="ETC1" s="6"/>
+      <c r="ETF1" s="6"/>
+      <c r="ETI1" s="6"/>
+      <c r="ETL1" s="6"/>
+      <c r="ETO1" s="6"/>
+      <c r="ETR1" s="6"/>
+      <c r="ETU1" s="6"/>
+      <c r="ETX1" s="6"/>
+      <c r="EUA1" s="6"/>
+      <c r="EUD1" s="6"/>
+      <c r="EUG1" s="6"/>
+      <c r="EUJ1" s="6"/>
+      <c r="EUM1" s="6"/>
+      <c r="EUP1" s="6"/>
+      <c r="EUS1" s="6"/>
+      <c r="EUV1" s="6"/>
+      <c r="EUY1" s="6"/>
+      <c r="EVB1" s="6"/>
+      <c r="EVE1" s="6"/>
+      <c r="EVH1" s="6"/>
+      <c r="EVK1" s="6"/>
+      <c r="EVN1" s="6"/>
+      <c r="EVQ1" s="6"/>
+      <c r="EVT1" s="6"/>
+      <c r="EVW1" s="6"/>
+      <c r="EVZ1" s="6"/>
+      <c r="EWC1" s="6"/>
+      <c r="EWF1" s="6"/>
+      <c r="EWI1" s="6"/>
+      <c r="EWL1" s="6"/>
+      <c r="EWO1" s="6"/>
+      <c r="EWR1" s="6"/>
+      <c r="EWU1" s="6"/>
+      <c r="EWX1" s="6"/>
+      <c r="EXA1" s="6"/>
+      <c r="EXD1" s="6"/>
+      <c r="EXG1" s="6"/>
+      <c r="EXJ1" s="6"/>
+      <c r="EXM1" s="6"/>
+      <c r="EXP1" s="6"/>
+      <c r="EXS1" s="6"/>
+      <c r="EXV1" s="6"/>
+      <c r="EXY1" s="6"/>
+      <c r="EYB1" s="6"/>
+      <c r="EYE1" s="6"/>
+      <c r="EYH1" s="6"/>
+      <c r="EYK1" s="6"/>
+      <c r="EYN1" s="6"/>
+      <c r="EYQ1" s="6"/>
+      <c r="EYT1" s="6"/>
+      <c r="EYW1" s="6"/>
+      <c r="EYZ1" s="6"/>
+      <c r="EZC1" s="6"/>
+      <c r="EZF1" s="6"/>
+      <c r="EZI1" s="6"/>
+      <c r="EZL1" s="6"/>
+      <c r="EZO1" s="6"/>
+      <c r="EZR1" s="6"/>
+      <c r="EZU1" s="6"/>
+      <c r="EZX1" s="6"/>
+      <c r="FAA1" s="6"/>
+      <c r="FAD1" s="6"/>
+      <c r="FAG1" s="6"/>
+      <c r="FAJ1" s="6"/>
+      <c r="FAM1" s="6"/>
+      <c r="FAP1" s="6"/>
+      <c r="FAS1" s="6"/>
+      <c r="FAV1" s="6"/>
+      <c r="FAY1" s="6"/>
+      <c r="FBB1" s="6"/>
+      <c r="FBE1" s="6"/>
+      <c r="FBH1" s="6"/>
+      <c r="FBK1" s="6"/>
+      <c r="FBN1" s="6"/>
+      <c r="FBQ1" s="6"/>
+      <c r="FBT1" s="6"/>
+      <c r="FBW1" s="6"/>
+      <c r="FBZ1" s="6"/>
+      <c r="FCC1" s="6"/>
+      <c r="FCF1" s="6"/>
+      <c r="FCI1" s="6"/>
+      <c r="FCL1" s="6"/>
+      <c r="FCO1" s="6"/>
+      <c r="FCR1" s="6"/>
+      <c r="FCU1" s="6"/>
+      <c r="FCX1" s="6"/>
+      <c r="FDA1" s="6"/>
+      <c r="FDD1" s="6"/>
+      <c r="FDG1" s="6"/>
+      <c r="FDJ1" s="6"/>
+      <c r="FDM1" s="6"/>
+      <c r="FDP1" s="6"/>
+      <c r="FDS1" s="6"/>
+      <c r="FDV1" s="6"/>
+      <c r="FDY1" s="6"/>
+      <c r="FEB1" s="6"/>
+      <c r="FEE1" s="6"/>
+      <c r="FEH1" s="6"/>
+      <c r="FEK1" s="6"/>
+      <c r="FEN1" s="6"/>
+      <c r="FEQ1" s="6"/>
+      <c r="FET1" s="6"/>
+      <c r="FEW1" s="6"/>
+      <c r="FEZ1" s="6"/>
+      <c r="FFC1" s="6"/>
+      <c r="FFF1" s="6"/>
+      <c r="FFI1" s="6"/>
+      <c r="FFL1" s="6"/>
+      <c r="FFO1" s="6"/>
+      <c r="FFR1" s="6"/>
+      <c r="FFU1" s="6"/>
+      <c r="FFX1" s="6"/>
+      <c r="FGA1" s="6"/>
+      <c r="FGD1" s="6"/>
+      <c r="FGG1" s="6"/>
+      <c r="FGJ1" s="6"/>
+      <c r="FGM1" s="6"/>
+      <c r="FGP1" s="6"/>
+      <c r="FGS1" s="6"/>
+      <c r="FGV1" s="6"/>
+      <c r="FGY1" s="6"/>
+      <c r="FHB1" s="6"/>
+      <c r="FHE1" s="6"/>
+      <c r="FHH1" s="6"/>
+      <c r="FHK1" s="6"/>
+      <c r="FHN1" s="6"/>
+      <c r="FHQ1" s="6"/>
+      <c r="FHT1" s="6"/>
+      <c r="FHW1" s="6"/>
+      <c r="FHZ1" s="6"/>
+      <c r="FIC1" s="6"/>
+      <c r="FIF1" s="6"/>
+      <c r="FII1" s="6"/>
+      <c r="FIL1" s="6"/>
+      <c r="FIO1" s="6"/>
+      <c r="FIR1" s="6"/>
+      <c r="FIU1" s="6"/>
+      <c r="FIX1" s="6"/>
+      <c r="FJA1" s="6"/>
+      <c r="FJD1" s="6"/>
+      <c r="FJG1" s="6"/>
+      <c r="FJJ1" s="6"/>
+      <c r="FJM1" s="6"/>
+      <c r="FJP1" s="6"/>
+      <c r="FJS1" s="6"/>
+      <c r="FJV1" s="6"/>
+      <c r="FJY1" s="6"/>
+      <c r="FKB1" s="6"/>
+      <c r="FKE1" s="6"/>
+      <c r="FKH1" s="6"/>
+      <c r="FKK1" s="6"/>
+      <c r="FKN1" s="6"/>
+      <c r="FKQ1" s="6"/>
+      <c r="FKT1" s="6"/>
+      <c r="FKW1" s="6"/>
+      <c r="FKZ1" s="6"/>
+      <c r="FLC1" s="6"/>
+      <c r="FLF1" s="6"/>
+      <c r="FLI1" s="6"/>
+      <c r="FLL1" s="6"/>
+      <c r="FLO1" s="6"/>
+      <c r="FLR1" s="6"/>
+      <c r="FLU1" s="6"/>
+      <c r="FLX1" s="6"/>
+      <c r="FMA1" s="6"/>
+      <c r="FMD1" s="6"/>
+      <c r="FMG1" s="6"/>
+      <c r="FMJ1" s="6"/>
+      <c r="FMM1" s="6"/>
+      <c r="FMP1" s="6"/>
+      <c r="FMS1" s="6"/>
+      <c r="FMV1" s="6"/>
+      <c r="FMY1" s="6"/>
+      <c r="FNB1" s="6"/>
+      <c r="FNE1" s="6"/>
+      <c r="FNH1" s="6"/>
+      <c r="FNK1" s="6"/>
+      <c r="FNN1" s="6"/>
+      <c r="FNQ1" s="6"/>
+      <c r="FNT1" s="6"/>
+      <c r="FNW1" s="6"/>
+      <c r="FNZ1" s="6"/>
+      <c r="FOC1" s="6"/>
+      <c r="FOF1" s="6"/>
+      <c r="FOI1" s="6"/>
+      <c r="FOL1" s="6"/>
+      <c r="FOO1" s="6"/>
+      <c r="FOR1" s="6"/>
+      <c r="FOU1" s="6"/>
+      <c r="FOX1" s="6"/>
+      <c r="FPA1" s="6"/>
+      <c r="FPD1" s="6"/>
+      <c r="FPG1" s="6"/>
+      <c r="FPJ1" s="6"/>
+      <c r="FPM1" s="6"/>
+      <c r="FPP1" s="6"/>
+      <c r="FPS1" s="6"/>
+      <c r="FPV1" s="6"/>
+      <c r="FPY1" s="6"/>
+      <c r="FQB1" s="6"/>
+      <c r="FQE1" s="6"/>
+      <c r="FQH1" s="6"/>
+      <c r="FQK1" s="6"/>
+      <c r="FQN1" s="6"/>
+      <c r="FQQ1" s="6"/>
+      <c r="FQT1" s="6"/>
+      <c r="FQW1" s="6"/>
+      <c r="FQZ1" s="6"/>
+      <c r="FRC1" s="6"/>
+      <c r="FRF1" s="6"/>
+      <c r="FRI1" s="6"/>
+      <c r="FRL1" s="6"/>
+      <c r="FRO1" s="6"/>
+      <c r="FRR1" s="6"/>
+      <c r="FRU1" s="6"/>
+      <c r="FRX1" s="6"/>
+      <c r="FSA1" s="6"/>
+      <c r="FSD1" s="6"/>
+      <c r="FSG1" s="6"/>
+      <c r="FSJ1" s="6"/>
+      <c r="FSM1" s="6"/>
+      <c r="FSP1" s="6"/>
+      <c r="FSS1" s="6"/>
+      <c r="FSV1" s="6"/>
+      <c r="FSY1" s="6"/>
+      <c r="FTB1" s="6"/>
+      <c r="FTE1" s="6"/>
+      <c r="FTH1" s="6"/>
+      <c r="FTK1" s="6"/>
+      <c r="FTN1" s="6"/>
+      <c r="FTQ1" s="6"/>
+      <c r="FTT1" s="6"/>
+      <c r="FTW1" s="6"/>
+      <c r="FTZ1" s="6"/>
+      <c r="FUC1" s="6"/>
+      <c r="FUF1" s="6"/>
+      <c r="FUI1" s="6"/>
+      <c r="FUL1" s="6"/>
+      <c r="FUO1" s="6"/>
+      <c r="FUR1" s="6"/>
+      <c r="FUU1" s="6"/>
+      <c r="FUX1" s="6"/>
+      <c r="FVA1" s="6"/>
+      <c r="FVD1" s="6"/>
+      <c r="FVG1" s="6"/>
+      <c r="FVJ1" s="6"/>
+      <c r="FVM1" s="6"/>
+      <c r="FVP1" s="6"/>
+      <c r="FVS1" s="6"/>
+      <c r="FVV1" s="6"/>
+      <c r="FVY1" s="6"/>
+      <c r="FWB1" s="6"/>
+      <c r="FWE1" s="6"/>
+      <c r="FWH1" s="6"/>
+      <c r="FWK1" s="6"/>
+      <c r="FWN1" s="6"/>
+      <c r="FWQ1" s="6"/>
+      <c r="FWT1" s="6"/>
+      <c r="FWW1" s="6"/>
+      <c r="FWZ1" s="6"/>
+      <c r="FXC1" s="6"/>
+      <c r="FXF1" s="6"/>
+      <c r="FXI1" s="6"/>
+      <c r="FXL1" s="6"/>
+      <c r="FXO1" s="6"/>
+      <c r="FXR1" s="6"/>
+      <c r="FXU1" s="6"/>
+      <c r="FXX1" s="6"/>
+      <c r="FYA1" s="6"/>
+      <c r="FYD1" s="6"/>
+      <c r="FYG1" s="6"/>
+      <c r="FYJ1" s="6"/>
+      <c r="FYM1" s="6"/>
+      <c r="FYP1" s="6"/>
+      <c r="FYS1" s="6"/>
+      <c r="FYV1" s="6"/>
+      <c r="FYY1" s="6"/>
+      <c r="FZB1" s="6"/>
+      <c r="FZE1" s="6"/>
+      <c r="FZH1" s="6"/>
+      <c r="FZK1" s="6"/>
+      <c r="FZN1" s="6"/>
+      <c r="FZQ1" s="6"/>
+      <c r="FZT1" s="6"/>
+      <c r="FZW1" s="6"/>
+      <c r="FZZ1" s="6"/>
+      <c r="GAC1" s="6"/>
+      <c r="GAF1" s="6"/>
+      <c r="GAI1" s="6"/>
+      <c r="GAL1" s="6"/>
+      <c r="GAO1" s="6"/>
+      <c r="GAR1" s="6"/>
+      <c r="GAU1" s="6"/>
+      <c r="GAX1" s="6"/>
+      <c r="GBA1" s="6"/>
+      <c r="GBD1" s="6"/>
+      <c r="GBG1" s="6"/>
+      <c r="GBJ1" s="6"/>
+      <c r="GBM1" s="6"/>
+      <c r="GBP1" s="6"/>
+      <c r="GBS1" s="6"/>
+      <c r="GBV1" s="6"/>
+      <c r="GBY1" s="6"/>
+      <c r="GCB1" s="6"/>
+      <c r="GCE1" s="6"/>
+      <c r="GCH1" s="6"/>
+      <c r="GCK1" s="6"/>
+      <c r="GCN1" s="6"/>
+      <c r="GCQ1" s="6"/>
+      <c r="GCT1" s="6"/>
+      <c r="GCW1" s="6"/>
+      <c r="GCZ1" s="6"/>
+      <c r="GDC1" s="6"/>
+      <c r="GDF1" s="6"/>
+      <c r="GDI1" s="6"/>
+      <c r="GDL1" s="6"/>
+      <c r="GDO1" s="6"/>
+      <c r="GDR1" s="6"/>
+      <c r="GDU1" s="6"/>
+      <c r="GDX1" s="6"/>
+      <c r="GEA1" s="6"/>
+      <c r="GED1" s="6"/>
+      <c r="GEG1" s="6"/>
+      <c r="GEJ1" s="6"/>
+      <c r="GEM1" s="6"/>
+      <c r="GEP1" s="6"/>
+      <c r="GES1" s="6"/>
+      <c r="GEV1" s="6"/>
+      <c r="GEY1" s="6"/>
+      <c r="GFB1" s="6"/>
+      <c r="GFE1" s="6"/>
+      <c r="GFH1" s="6"/>
+      <c r="GFK1" s="6"/>
+      <c r="GFN1" s="6"/>
+      <c r="GFQ1" s="6"/>
+      <c r="GFT1" s="6"/>
+      <c r="GFW1" s="6"/>
+      <c r="GFZ1" s="6"/>
+      <c r="GGC1" s="6"/>
+      <c r="GGF1" s="6"/>
+      <c r="GGI1" s="6"/>
+      <c r="GGL1" s="6"/>
+      <c r="GGO1" s="6"/>
+      <c r="GGR1" s="6"/>
+      <c r="GGU1" s="6"/>
+      <c r="GGX1" s="6"/>
+      <c r="GHA1" s="6"/>
+      <c r="GHD1" s="6"/>
+      <c r="GHG1" s="6"/>
+      <c r="GHJ1" s="6"/>
+      <c r="GHM1" s="6"/>
+      <c r="GHP1" s="6"/>
+      <c r="GHS1" s="6"/>
+      <c r="GHV1" s="6"/>
+      <c r="GHY1" s="6"/>
+      <c r="GIB1" s="6"/>
+      <c r="GIE1" s="6"/>
+      <c r="GIH1" s="6"/>
+      <c r="GIK1" s="6"/>
+      <c r="GIN1" s="6"/>
+      <c r="GIQ1" s="6"/>
+      <c r="GIT1" s="6"/>
+      <c r="GIW1" s="6"/>
+      <c r="GIZ1" s="6"/>
+      <c r="GJC1" s="6"/>
+      <c r="GJF1" s="6"/>
+      <c r="GJI1" s="6"/>
+      <c r="GJL1" s="6"/>
+      <c r="GJO1" s="6"/>
+      <c r="GJR1" s="6"/>
+      <c r="GJU1" s="6"/>
+      <c r="GJX1" s="6"/>
+      <c r="GKA1" s="6"/>
+      <c r="GKD1" s="6"/>
+      <c r="GKG1" s="6"/>
+      <c r="GKJ1" s="6"/>
+      <c r="GKM1" s="6"/>
+      <c r="GKP1" s="6"/>
+      <c r="GKS1" s="6"/>
+      <c r="GKV1" s="6"/>
+      <c r="GKY1" s="6"/>
+      <c r="GLB1" s="6"/>
+      <c r="GLE1" s="6"/>
+      <c r="GLH1" s="6"/>
+      <c r="GLK1" s="6"/>
+      <c r="GLN1" s="6"/>
+      <c r="GLQ1" s="6"/>
+      <c r="GLT1" s="6"/>
+      <c r="GLW1" s="6"/>
+      <c r="GLZ1" s="6"/>
+      <c r="GMC1" s="6"/>
+      <c r="GMF1" s="6"/>
+      <c r="GMI1" s="6"/>
+      <c r="GML1" s="6"/>
+      <c r="GMO1" s="6"/>
+      <c r="GMR1" s="6"/>
+      <c r="GMU1" s="6"/>
+      <c r="GMX1" s="6"/>
+      <c r="GNA1" s="6"/>
+      <c r="GND1" s="6"/>
+      <c r="GNG1" s="6"/>
+      <c r="GNJ1" s="6"/>
+      <c r="GNM1" s="6"/>
+      <c r="GNP1" s="6"/>
+      <c r="GNS1" s="6"/>
+      <c r="GNV1" s="6"/>
+      <c r="GNY1" s="6"/>
+      <c r="GOB1" s="6"/>
+      <c r="GOE1" s="6"/>
+      <c r="GOH1" s="6"/>
+      <c r="GOK1" s="6"/>
+      <c r="GON1" s="6"/>
+      <c r="GOQ1" s="6"/>
+      <c r="GOT1" s="6"/>
+      <c r="GOW1" s="6"/>
+      <c r="GOZ1" s="6"/>
+      <c r="GPC1" s="6"/>
+      <c r="GPF1" s="6"/>
+      <c r="GPI1" s="6"/>
+      <c r="GPL1" s="6"/>
+      <c r="GPO1" s="6"/>
+      <c r="GPR1" s="6"/>
+      <c r="GPU1" s="6"/>
+      <c r="GPX1" s="6"/>
+      <c r="GQA1" s="6"/>
+      <c r="GQD1" s="6"/>
+      <c r="GQG1" s="6"/>
+      <c r="GQJ1" s="6"/>
+      <c r="GQM1" s="6"/>
+      <c r="GQP1" s="6"/>
+      <c r="GQS1" s="6"/>
+      <c r="GQV1" s="6"/>
+      <c r="GQY1" s="6"/>
+      <c r="GRB1" s="6"/>
+      <c r="GRE1" s="6"/>
+      <c r="GRH1" s="6"/>
+      <c r="GRK1" s="6"/>
+      <c r="GRN1" s="6"/>
+      <c r="GRQ1" s="6"/>
+      <c r="GRT1" s="6"/>
+      <c r="GRW1" s="6"/>
+      <c r="GRZ1" s="6"/>
+      <c r="GSC1" s="6"/>
+      <c r="GSF1" s="6"/>
+      <c r="GSI1" s="6"/>
+      <c r="GSL1" s="6"/>
+      <c r="GSO1" s="6"/>
+      <c r="GSR1" s="6"/>
+      <c r="GSU1" s="6"/>
+      <c r="GSX1" s="6"/>
+      <c r="GTA1" s="6"/>
+      <c r="GTD1" s="6"/>
+      <c r="GTG1" s="6"/>
+      <c r="GTJ1" s="6"/>
+      <c r="GTM1" s="6"/>
+      <c r="GTP1" s="6"/>
+      <c r="GTS1" s="6"/>
+      <c r="GTV1" s="6"/>
+      <c r="GTY1" s="6"/>
+      <c r="GUB1" s="6"/>
+      <c r="GUE1" s="6"/>
+      <c r="GUH1" s="6"/>
+      <c r="GUK1" s="6"/>
+      <c r="GUN1" s="6"/>
+      <c r="GUQ1" s="6"/>
+      <c r="GUT1" s="6"/>
+      <c r="GUW1" s="6"/>
+      <c r="GUZ1" s="6"/>
+      <c r="GVC1" s="6"/>
+      <c r="GVF1" s="6"/>
+      <c r="GVI1" s="6"/>
+      <c r="GVL1" s="6"/>
+      <c r="GVO1" s="6"/>
+      <c r="GVR1" s="6"/>
+      <c r="GVU1" s="6"/>
+      <c r="GVX1" s="6"/>
+      <c r="GWA1" s="6"/>
+      <c r="GWD1" s="6"/>
+      <c r="GWG1" s="6"/>
+      <c r="GWJ1" s="6"/>
+      <c r="GWM1" s="6"/>
+      <c r="GWP1" s="6"/>
+      <c r="GWS1" s="6"/>
+      <c r="GWV1" s="6"/>
+      <c r="GWY1" s="6"/>
+      <c r="GXB1" s="6"/>
+      <c r="GXE1" s="6"/>
+      <c r="GXH1" s="6"/>
+      <c r="GXK1" s="6"/>
+      <c r="GXN1" s="6"/>
+      <c r="GXQ1" s="6"/>
+      <c r="GXT1" s="6"/>
+      <c r="GXW1" s="6"/>
+      <c r="GXZ1" s="6"/>
+      <c r="GYC1" s="6"/>
+      <c r="GYF1" s="6"/>
+      <c r="GYI1" s="6"/>
+      <c r="GYL1" s="6"/>
+      <c r="GYO1" s="6"/>
+      <c r="GYR1" s="6"/>
+      <c r="GYU1" s="6"/>
+      <c r="GYX1" s="6"/>
+      <c r="GZA1" s="6"/>
+      <c r="GZD1" s="6"/>
+      <c r="GZG1" s="6"/>
+      <c r="GZJ1" s="6"/>
+      <c r="GZM1" s="6"/>
+      <c r="GZP1" s="6"/>
+      <c r="GZS1" s="6"/>
+      <c r="GZV1" s="6"/>
+      <c r="GZY1" s="6"/>
+      <c r="HAB1" s="6"/>
+      <c r="HAE1" s="6"/>
+      <c r="HAH1" s="6"/>
+      <c r="HAK1" s="6"/>
+      <c r="HAN1" s="6"/>
+      <c r="HAQ1" s="6"/>
+      <c r="HAT1" s="6"/>
+      <c r="HAW1" s="6"/>
+      <c r="HAZ1" s="6"/>
+      <c r="HBC1" s="6"/>
+      <c r="HBF1" s="6"/>
+      <c r="HBI1" s="6"/>
+      <c r="HBL1" s="6"/>
+      <c r="HBO1" s="6"/>
+      <c r="HBR1" s="6"/>
+      <c r="HBU1" s="6"/>
+      <c r="HBX1" s="6"/>
+      <c r="HCA1" s="6"/>
+      <c r="HCD1" s="6"/>
+      <c r="HCG1" s="6"/>
+      <c r="HCJ1" s="6"/>
+      <c r="HCM1" s="6"/>
+      <c r="HCP1" s="6"/>
+      <c r="HCS1" s="6"/>
+      <c r="HCV1" s="6"/>
+      <c r="HCY1" s="6"/>
+      <c r="HDB1" s="6"/>
+      <c r="HDE1" s="6"/>
+      <c r="HDH1" s="6"/>
+      <c r="HDK1" s="6"/>
+      <c r="HDN1" s="6"/>
+      <c r="HDQ1" s="6"/>
+      <c r="HDT1" s="6"/>
+      <c r="HDW1" s="6"/>
+      <c r="HDZ1" s="6"/>
+      <c r="HEC1" s="6"/>
+      <c r="HEF1" s="6"/>
+      <c r="HEI1" s="6"/>
+      <c r="HEL1" s="6"/>
+      <c r="HEO1" s="6"/>
+      <c r="HER1" s="6"/>
+      <c r="HEU1" s="6"/>
+      <c r="HEX1" s="6"/>
+      <c r="HFA1" s="6"/>
+      <c r="HFD1" s="6"/>
+      <c r="HFG1" s="6"/>
+      <c r="HFJ1" s="6"/>
+      <c r="HFM1" s="6"/>
+      <c r="HFP1" s="6"/>
+      <c r="HFS1" s="6"/>
+      <c r="HFV1" s="6"/>
+      <c r="HFY1" s="6"/>
+      <c r="HGB1" s="6"/>
+      <c r="HGE1" s="6"/>
+      <c r="HGH1" s="6"/>
+      <c r="HGK1" s="6"/>
+      <c r="HGN1" s="6"/>
+      <c r="HGQ1" s="6"/>
+      <c r="HGT1" s="6"/>
+      <c r="HGW1" s="6"/>
+      <c r="HGZ1" s="6"/>
+      <c r="HHC1" s="6"/>
+      <c r="HHF1" s="6"/>
+      <c r="HHI1" s="6"/>
+      <c r="HHL1" s="6"/>
+      <c r="HHO1" s="6"/>
+      <c r="HHR1" s="6"/>
+      <c r="HHU1" s="6"/>
+      <c r="HHX1" s="6"/>
+      <c r="HIA1" s="6"/>
+      <c r="HID1" s="6"/>
+      <c r="HIG1" s="6"/>
+      <c r="HIJ1" s="6"/>
+      <c r="HIM1" s="6"/>
+      <c r="HIP1" s="6"/>
+      <c r="HIS1" s="6"/>
+      <c r="HIV1" s="6"/>
+      <c r="HIY1" s="6"/>
+      <c r="HJB1" s="6"/>
+      <c r="HJE1" s="6"/>
+      <c r="HJH1" s="6"/>
+      <c r="HJK1" s="6"/>
+      <c r="HJN1" s="6"/>
+      <c r="HJQ1" s="6"/>
+      <c r="HJT1" s="6"/>
+      <c r="HJW1" s="6"/>
+      <c r="HJZ1" s="6"/>
+      <c r="HKC1" s="6"/>
+      <c r="HKF1" s="6"/>
+      <c r="HKI1" s="6"/>
+      <c r="HKL1" s="6"/>
+      <c r="HKO1" s="6"/>
+      <c r="HKR1" s="6"/>
+      <c r="HKU1" s="6"/>
+      <c r="HKX1" s="6"/>
+      <c r="HLA1" s="6"/>
+      <c r="HLD1" s="6"/>
+      <c r="HLG1" s="6"/>
+      <c r="HLJ1" s="6"/>
+      <c r="HLM1" s="6"/>
+      <c r="HLP1" s="6"/>
+      <c r="HLS1" s="6"/>
+      <c r="HLV1" s="6"/>
+      <c r="HLY1" s="6"/>
+      <c r="HMB1" s="6"/>
+      <c r="HME1" s="6"/>
+      <c r="HMH1" s="6"/>
+      <c r="HMK1" s="6"/>
+      <c r="HMN1" s="6"/>
+      <c r="HMQ1" s="6"/>
+      <c r="HMT1" s="6"/>
+      <c r="HMW1" s="6"/>
+      <c r="HMZ1" s="6"/>
+      <c r="HNC1" s="6"/>
+      <c r="HNF1" s="6"/>
+      <c r="HNI1" s="6"/>
+      <c r="HNL1" s="6"/>
+      <c r="HNO1" s="6"/>
+      <c r="HNR1" s="6"/>
+      <c r="HNU1" s="6"/>
+      <c r="HNX1" s="6"/>
+      <c r="HOA1" s="6"/>
+      <c r="HOD1" s="6"/>
+      <c r="HOG1" s="6"/>
+      <c r="HOJ1" s="6"/>
+      <c r="HOM1" s="6"/>
+      <c r="HOP1" s="6"/>
+      <c r="HOS1" s="6"/>
+      <c r="HOV1" s="6"/>
+      <c r="HOY1" s="6"/>
+      <c r="HPB1" s="6"/>
+      <c r="HPE1" s="6"/>
+      <c r="HPH1" s="6"/>
+      <c r="HPK1" s="6"/>
+      <c r="HPN1" s="6"/>
+      <c r="HPQ1" s="6"/>
+      <c r="HPT1" s="6"/>
+      <c r="HPW1" s="6"/>
+      <c r="HPZ1" s="6"/>
+      <c r="HQC1" s="6"/>
+      <c r="HQF1" s="6"/>
+      <c r="HQI1" s="6"/>
+      <c r="HQL1" s="6"/>
+      <c r="HQO1" s="6"/>
+      <c r="HQR1" s="6"/>
+      <c r="HQU1" s="6"/>
+      <c r="HQX1" s="6"/>
+      <c r="HRA1" s="6"/>
+      <c r="HRD1" s="6"/>
+      <c r="HRG1" s="6"/>
+      <c r="HRJ1" s="6"/>
+      <c r="HRM1" s="6"/>
+      <c r="HRP1" s="6"/>
+      <c r="HRS1" s="6"/>
+      <c r="HRV1" s="6"/>
+      <c r="HRY1" s="6"/>
+      <c r="HSB1" s="6"/>
+      <c r="HSE1" s="6"/>
+      <c r="HSH1" s="6"/>
+      <c r="HSK1" s="6"/>
+      <c r="HSN1" s="6"/>
+      <c r="HSQ1" s="6"/>
+      <c r="HST1" s="6"/>
+      <c r="HSW1" s="6"/>
+      <c r="HSZ1" s="6"/>
+      <c r="HTC1" s="6"/>
+      <c r="HTF1" s="6"/>
+      <c r="HTI1" s="6"/>
+      <c r="HTL1" s="6"/>
+      <c r="HTO1" s="6"/>
+      <c r="HTR1" s="6"/>
+      <c r="HTU1" s="6"/>
+      <c r="HTX1" s="6"/>
+      <c r="HUA1" s="6"/>
+      <c r="HUD1" s="6"/>
+      <c r="HUG1" s="6"/>
+      <c r="HUJ1" s="6"/>
+      <c r="HUM1" s="6"/>
+      <c r="HUP1" s="6"/>
+      <c r="HUS1" s="6"/>
+      <c r="HUV1" s="6"/>
+      <c r="HUY1" s="6"/>
+      <c r="HVB1" s="6"/>
+      <c r="HVE1" s="6"/>
+      <c r="HVH1" s="6"/>
+      <c r="HVK1" s="6"/>
+      <c r="HVN1" s="6"/>
+      <c r="HVQ1" s="6"/>
+      <c r="HVT1" s="6"/>
+      <c r="HVW1" s="6"/>
+      <c r="HVZ1" s="6"/>
+      <c r="HWC1" s="6"/>
+      <c r="HWF1" s="6"/>
+      <c r="HWI1" s="6"/>
+      <c r="HWL1" s="6"/>
+      <c r="HWO1" s="6"/>
+      <c r="HWR1" s="6"/>
+      <c r="HWU1" s="6"/>
+      <c r="HWX1" s="6"/>
+      <c r="HXA1" s="6"/>
+      <c r="HXD1" s="6"/>
+      <c r="HXG1" s="6"/>
+      <c r="HXJ1" s="6"/>
+      <c r="HXM1" s="6"/>
+      <c r="HXP1" s="6"/>
+      <c r="HXS1" s="6"/>
+      <c r="HXV1" s="6"/>
+      <c r="HXY1" s="6"/>
+      <c r="HYB1" s="6"/>
+      <c r="HYE1" s="6"/>
+      <c r="HYH1" s="6"/>
+      <c r="HYK1" s="6"/>
+      <c r="HYN1" s="6"/>
+      <c r="HYQ1" s="6"/>
+      <c r="HYT1" s="6"/>
+      <c r="HYW1" s="6"/>
+      <c r="HYZ1" s="6"/>
+      <c r="HZC1" s="6"/>
+      <c r="HZF1" s="6"/>
+      <c r="HZI1" s="6"/>
+      <c r="HZL1" s="6"/>
+      <c r="HZO1" s="6"/>
+      <c r="HZR1" s="6"/>
+      <c r="HZU1" s="6"/>
+      <c r="HZX1" s="6"/>
+      <c r="IAA1" s="6"/>
+      <c r="IAD1" s="6"/>
+      <c r="IAG1" s="6"/>
+      <c r="IAJ1" s="6"/>
+      <c r="IAM1" s="6"/>
+      <c r="IAP1" s="6"/>
+      <c r="IAS1" s="6"/>
+      <c r="IAV1" s="6"/>
+      <c r="IAY1" s="6"/>
+      <c r="IBB1" s="6"/>
+      <c r="IBE1" s="6"/>
+      <c r="IBH1" s="6"/>
+      <c r="IBK1" s="6"/>
+      <c r="IBN1" s="6"/>
+      <c r="IBQ1" s="6"/>
+      <c r="IBT1" s="6"/>
+      <c r="IBW1" s="6"/>
+      <c r="IBZ1" s="6"/>
+      <c r="ICC1" s="6"/>
+      <c r="ICF1" s="6"/>
+      <c r="ICI1" s="6"/>
+      <c r="ICL1" s="6"/>
+      <c r="ICO1" s="6"/>
+      <c r="ICR1" s="6"/>
+      <c r="ICU1" s="6"/>
+      <c r="ICX1" s="6"/>
+      <c r="IDA1" s="6"/>
+      <c r="IDD1" s="6"/>
+      <c r="IDG1" s="6"/>
+      <c r="IDJ1" s="6"/>
+      <c r="IDM1" s="6"/>
+      <c r="IDP1" s="6"/>
+      <c r="IDS1" s="6"/>
+      <c r="IDV1" s="6"/>
+      <c r="IDY1" s="6"/>
+      <c r="IEB1" s="6"/>
+      <c r="IEE1" s="6"/>
+      <c r="IEH1" s="6"/>
+      <c r="IEK1" s="6"/>
+      <c r="IEN1" s="6"/>
+      <c r="IEQ1" s="6"/>
+      <c r="IET1" s="6"/>
+      <c r="IEW1" s="6"/>
+      <c r="IEZ1" s="6"/>
+      <c r="IFC1" s="6"/>
+      <c r="IFF1" s="6"/>
+      <c r="IFI1" s="6"/>
+      <c r="IFL1" s="6"/>
+      <c r="IFO1" s="6"/>
+      <c r="IFR1" s="6"/>
+      <c r="IFU1" s="6"/>
+      <c r="IFX1" s="6"/>
+      <c r="IGA1" s="6"/>
+      <c r="IGD1" s="6"/>
+      <c r="IGG1" s="6"/>
+      <c r="IGJ1" s="6"/>
+      <c r="IGM1" s="6"/>
+      <c r="IGP1" s="6"/>
+      <c r="IGS1" s="6"/>
+      <c r="IGV1" s="6"/>
+      <c r="IGY1" s="6"/>
+      <c r="IHB1" s="6"/>
+      <c r="IHE1" s="6"/>
+      <c r="IHH1" s="6"/>
+      <c r="IHK1" s="6"/>
+      <c r="IHN1" s="6"/>
+      <c r="IHQ1" s="6"/>
+      <c r="IHT1" s="6"/>
+      <c r="IHW1" s="6"/>
+      <c r="IHZ1" s="6"/>
+      <c r="IIC1" s="6"/>
+      <c r="IIF1" s="6"/>
+      <c r="III1" s="6"/>
+      <c r="IIL1" s="6"/>
+      <c r="IIO1" s="6"/>
+      <c r="IIR1" s="6"/>
+      <c r="IIU1" s="6"/>
+      <c r="IIX1" s="6"/>
+      <c r="IJA1" s="6"/>
+      <c r="IJD1" s="6"/>
+      <c r="IJG1" s="6"/>
+      <c r="IJJ1" s="6"/>
+      <c r="IJM1" s="6"/>
+      <c r="IJP1" s="6"/>
+      <c r="IJS1" s="6"/>
+      <c r="IJV1" s="6"/>
+      <c r="IJY1" s="6"/>
+      <c r="IKB1" s="6"/>
+      <c r="IKE1" s="6"/>
+      <c r="IKH1" s="6"/>
+      <c r="IKK1" s="6"/>
+      <c r="IKN1" s="6"/>
+      <c r="IKQ1" s="6"/>
+      <c r="IKT1" s="6"/>
+      <c r="IKW1" s="6"/>
+      <c r="IKZ1" s="6"/>
+      <c r="ILC1" s="6"/>
+      <c r="ILF1" s="6"/>
+      <c r="ILI1" s="6"/>
+      <c r="ILL1" s="6"/>
+      <c r="ILO1" s="6"/>
+      <c r="ILR1" s="6"/>
+      <c r="ILU1" s="6"/>
+      <c r="ILX1" s="6"/>
+      <c r="IMA1" s="6"/>
+      <c r="IMD1" s="6"/>
+      <c r="IMG1" s="6"/>
+      <c r="IMJ1" s="6"/>
+      <c r="IMM1" s="6"/>
+      <c r="IMP1" s="6"/>
+      <c r="IMS1" s="6"/>
+      <c r="IMV1" s="6"/>
+      <c r="IMY1" s="6"/>
+      <c r="INB1" s="6"/>
+      <c r="INE1" s="6"/>
+      <c r="INH1" s="6"/>
+      <c r="INK1" s="6"/>
+      <c r="INN1" s="6"/>
+      <c r="INQ1" s="6"/>
+      <c r="INT1" s="6"/>
+      <c r="INW1" s="6"/>
+      <c r="INZ1" s="6"/>
+      <c r="IOC1" s="6"/>
+      <c r="IOF1" s="6"/>
+      <c r="IOI1" s="6"/>
+      <c r="IOL1" s="6"/>
+      <c r="IOO1" s="6"/>
+      <c r="IOR1" s="6"/>
+      <c r="IOU1" s="6"/>
+      <c r="IOX1" s="6"/>
+      <c r="IPA1" s="6"/>
+      <c r="IPD1" s="6"/>
+      <c r="IPG1" s="6"/>
+      <c r="IPJ1" s="6"/>
+      <c r="IPM1" s="6"/>
+      <c r="IPP1" s="6"/>
+      <c r="IPS1" s="6"/>
+      <c r="IPV1" s="6"/>
+      <c r="IPY1" s="6"/>
+      <c r="IQB1" s="6"/>
+      <c r="IQE1" s="6"/>
+      <c r="IQH1" s="6"/>
+      <c r="IQK1" s="6"/>
+      <c r="IQN1" s="6"/>
+      <c r="IQQ1" s="6"/>
+      <c r="IQT1" s="6"/>
+      <c r="IQW1" s="6"/>
+      <c r="IQZ1" s="6"/>
+      <c r="IRC1" s="6"/>
+      <c r="IRF1" s="6"/>
+      <c r="IRI1" s="6"/>
+      <c r="IRL1" s="6"/>
+      <c r="IRO1" s="6"/>
+      <c r="IRR1" s="6"/>
+      <c r="IRU1" s="6"/>
+      <c r="IRX1" s="6"/>
+      <c r="ISA1" s="6"/>
+      <c r="ISD1" s="6"/>
+      <c r="ISG1" s="6"/>
+      <c r="ISJ1" s="6"/>
+      <c r="ISM1" s="6"/>
+      <c r="ISP1" s="6"/>
+      <c r="ISS1" s="6"/>
+      <c r="ISV1" s="6"/>
+      <c r="ISY1" s="6"/>
+      <c r="ITB1" s="6"/>
+      <c r="ITE1" s="6"/>
+      <c r="ITH1" s="6"/>
+      <c r="ITK1" s="6"/>
+      <c r="ITN1" s="6"/>
+      <c r="ITQ1" s="6"/>
+      <c r="ITT1" s="6"/>
+      <c r="ITW1" s="6"/>
+      <c r="ITZ1" s="6"/>
+      <c r="IUC1" s="6"/>
+      <c r="IUF1" s="6"/>
+      <c r="IUI1" s="6"/>
+      <c r="IUL1" s="6"/>
+      <c r="IUO1" s="6"/>
+      <c r="IUR1" s="6"/>
+      <c r="IUU1" s="6"/>
+      <c r="IUX1" s="6"/>
+      <c r="IVA1" s="6"/>
+      <c r="IVD1" s="6"/>
+      <c r="IVG1" s="6"/>
+      <c r="IVJ1" s="6"/>
+      <c r="IVM1" s="6"/>
+      <c r="IVP1" s="6"/>
+      <c r="IVS1" s="6"/>
+      <c r="IVV1" s="6"/>
+      <c r="IVY1" s="6"/>
+      <c r="IWB1" s="6"/>
+      <c r="IWE1" s="6"/>
+      <c r="IWH1" s="6"/>
+      <c r="IWK1" s="6"/>
+      <c r="IWN1" s="6"/>
+      <c r="IWQ1" s="6"/>
+      <c r="IWT1" s="6"/>
+      <c r="IWW1" s="6"/>
+      <c r="IWZ1" s="6"/>
+      <c r="IXC1" s="6"/>
+      <c r="IXF1" s="6"/>
+      <c r="IXI1" s="6"/>
+      <c r="IXL1" s="6"/>
+      <c r="IXO1" s="6"/>
+      <c r="IXR1" s="6"/>
+      <c r="IXU1" s="6"/>
+      <c r="IXX1" s="6"/>
+      <c r="IYA1" s="6"/>
+      <c r="IYD1" s="6"/>
+      <c r="IYG1" s="6"/>
+      <c r="IYJ1" s="6"/>
+      <c r="IYM1" s="6"/>
+      <c r="IYP1" s="6"/>
+      <c r="IYS1" s="6"/>
+      <c r="IYV1" s="6"/>
+      <c r="IYY1" s="6"/>
+      <c r="IZB1" s="6"/>
+      <c r="IZE1" s="6"/>
+      <c r="IZH1" s="6"/>
+      <c r="IZK1" s="6"/>
+      <c r="IZN1" s="6"/>
+      <c r="IZQ1" s="6"/>
+      <c r="IZT1" s="6"/>
+      <c r="IZW1" s="6"/>
+      <c r="IZZ1" s="6"/>
+      <c r="JAC1" s="6"/>
+      <c r="JAF1" s="6"/>
+      <c r="JAI1" s="6"/>
+      <c r="JAL1" s="6"/>
+      <c r="JAO1" s="6"/>
+      <c r="JAR1" s="6"/>
+      <c r="JAU1" s="6"/>
+      <c r="JAX1" s="6"/>
+      <c r="JBA1" s="6"/>
+      <c r="JBD1" s="6"/>
+      <c r="JBG1" s="6"/>
+      <c r="JBJ1" s="6"/>
+      <c r="JBM1" s="6"/>
+      <c r="JBP1" s="6"/>
+      <c r="JBS1" s="6"/>
+      <c r="JBV1" s="6"/>
+      <c r="JBY1" s="6"/>
+      <c r="JCB1" s="6"/>
+      <c r="JCE1" s="6"/>
+      <c r="JCH1" s="6"/>
+      <c r="JCK1" s="6"/>
+      <c r="JCN1" s="6"/>
+      <c r="JCQ1" s="6"/>
+      <c r="JCT1" s="6"/>
+      <c r="JCW1" s="6"/>
+      <c r="JCZ1" s="6"/>
+      <c r="JDC1" s="6"/>
+      <c r="JDF1" s="6"/>
+      <c r="JDI1" s="6"/>
+      <c r="JDL1" s="6"/>
+      <c r="JDO1" s="6"/>
+      <c r="JDR1" s="6"/>
+      <c r="JDU1" s="6"/>
+      <c r="JDX1" s="6"/>
+      <c r="JEA1" s="6"/>
+      <c r="JED1" s="6"/>
+      <c r="JEG1" s="6"/>
+      <c r="JEJ1" s="6"/>
+      <c r="JEM1" s="6"/>
+      <c r="JEP1" s="6"/>
+      <c r="JES1" s="6"/>
+      <c r="JEV1" s="6"/>
+      <c r="JEY1" s="6"/>
+      <c r="JFB1" s="6"/>
+      <c r="JFE1" s="6"/>
+      <c r="JFH1" s="6"/>
+      <c r="JFK1" s="6"/>
+      <c r="JFN1" s="6"/>
+      <c r="JFQ1" s="6"/>
+      <c r="JFT1" s="6"/>
+      <c r="JFW1" s="6"/>
+      <c r="JFZ1" s="6"/>
+      <c r="JGC1" s="6"/>
+      <c r="JGF1" s="6"/>
+      <c r="JGI1" s="6"/>
+      <c r="JGL1" s="6"/>
+      <c r="JGO1" s="6"/>
+      <c r="JGR1" s="6"/>
+      <c r="JGU1" s="6"/>
+      <c r="JGX1" s="6"/>
+      <c r="JHA1" s="6"/>
+      <c r="JHD1" s="6"/>
+      <c r="JHG1" s="6"/>
+      <c r="JHJ1" s="6"/>
+      <c r="JHM1" s="6"/>
+      <c r="JHP1" s="6"/>
+      <c r="JHS1" s="6"/>
+      <c r="JHV1" s="6"/>
+      <c r="JHY1" s="6"/>
+      <c r="JIB1" s="6"/>
+      <c r="JIE1" s="6"/>
+      <c r="JIH1" s="6"/>
+      <c r="JIK1" s="6"/>
+      <c r="JIN1" s="6"/>
+      <c r="JIQ1" s="6"/>
+      <c r="JIT1" s="6"/>
+      <c r="JIW1" s="6"/>
+      <c r="JIZ1" s="6"/>
+      <c r="JJC1" s="6"/>
+      <c r="JJF1" s="6"/>
+      <c r="JJI1" s="6"/>
+      <c r="JJL1" s="6"/>
+      <c r="JJO1" s="6"/>
+      <c r="JJR1" s="6"/>
+      <c r="JJU1" s="6"/>
+      <c r="JJX1" s="6"/>
+      <c r="JKA1" s="6"/>
+      <c r="JKD1" s="6"/>
+      <c r="JKG1" s="6"/>
+      <c r="JKJ1" s="6"/>
+      <c r="JKM1" s="6"/>
+      <c r="JKP1" s="6"/>
+      <c r="JKS1" s="6"/>
+      <c r="JKV1" s="6"/>
+      <c r="JKY1" s="6"/>
+      <c r="JLB1" s="6"/>
+      <c r="JLE1" s="6"/>
+      <c r="JLH1" s="6"/>
+      <c r="JLK1" s="6"/>
+      <c r="JLN1" s="6"/>
+      <c r="JLQ1" s="6"/>
+      <c r="JLT1" s="6"/>
+      <c r="JLW1" s="6"/>
+      <c r="JLZ1" s="6"/>
+      <c r="JMC1" s="6"/>
+      <c r="JMF1" s="6"/>
+      <c r="JMI1" s="6"/>
+      <c r="JML1" s="6"/>
+      <c r="JMO1" s="6"/>
+      <c r="JMR1" s="6"/>
+      <c r="JMU1" s="6"/>
+      <c r="JMX1" s="6"/>
+      <c r="JNA1" s="6"/>
+      <c r="JND1" s="6"/>
+      <c r="JNG1" s="6"/>
+      <c r="JNJ1" s="6"/>
+      <c r="JNM1" s="6"/>
+      <c r="JNP1" s="6"/>
+      <c r="JNS1" s="6"/>
+      <c r="JNV1" s="6"/>
+      <c r="JNY1" s="6"/>
+      <c r="JOB1" s="6"/>
+      <c r="JOE1" s="6"/>
+      <c r="JOH1" s="6"/>
+      <c r="JOK1" s="6"/>
+      <c r="JON1" s="6"/>
+      <c r="JOQ1" s="6"/>
+      <c r="JOT1" s="6"/>
+      <c r="JOW1" s="6"/>
+      <c r="JOZ1" s="6"/>
+      <c r="JPC1" s="6"/>
+      <c r="JPF1" s="6"/>
+      <c r="JPI1" s="6"/>
+      <c r="JPL1" s="6"/>
+      <c r="JPO1" s="6"/>
+      <c r="JPR1" s="6"/>
+      <c r="JPU1" s="6"/>
+      <c r="JPX1" s="6"/>
+      <c r="JQA1" s="6"/>
+      <c r="JQD1" s="6"/>
+      <c r="JQG1" s="6"/>
+      <c r="JQJ1" s="6"/>
+      <c r="JQM1" s="6"/>
+      <c r="JQP1" s="6"/>
+      <c r="JQS1" s="6"/>
+      <c r="JQV1" s="6"/>
+      <c r="JQY1" s="6"/>
+      <c r="JRB1" s="6"/>
+      <c r="JRE1" s="6"/>
+      <c r="JRH1" s="6"/>
+      <c r="JRK1" s="6"/>
+      <c r="JRN1" s="6"/>
+      <c r="JRQ1" s="6"/>
+      <c r="JRT1" s="6"/>
+      <c r="JRW1" s="6"/>
+      <c r="JRZ1" s="6"/>
+      <c r="JSC1" s="6"/>
+      <c r="JSF1" s="6"/>
+      <c r="JSI1" s="6"/>
+      <c r="JSL1" s="6"/>
+      <c r="JSO1" s="6"/>
+      <c r="JSR1" s="6"/>
+      <c r="JSU1" s="6"/>
+      <c r="JSX1" s="6"/>
+      <c r="JTA1" s="6"/>
+      <c r="JTD1" s="6"/>
+      <c r="JTG1" s="6"/>
+      <c r="JTJ1" s="6"/>
+      <c r="JTM1" s="6"/>
+      <c r="JTP1" s="6"/>
+      <c r="JTS1" s="6"/>
+      <c r="JTV1" s="6"/>
+      <c r="JTY1" s="6"/>
+      <c r="JUB1" s="6"/>
+      <c r="JUE1" s="6"/>
+      <c r="JUH1" s="6"/>
+      <c r="JUK1" s="6"/>
+      <c r="JUN1" s="6"/>
+      <c r="JUQ1" s="6"/>
+      <c r="JUT1" s="6"/>
+      <c r="JUW1" s="6"/>
+      <c r="JUZ1" s="6"/>
+      <c r="JVC1" s="6"/>
+      <c r="JVF1" s="6"/>
+      <c r="JVI1" s="6"/>
+      <c r="JVL1" s="6"/>
+      <c r="JVO1" s="6"/>
+      <c r="JVR1" s="6"/>
+      <c r="JVU1" s="6"/>
+      <c r="JVX1" s="6"/>
+      <c r="JWA1" s="6"/>
+      <c r="JWD1" s="6"/>
+      <c r="JWG1" s="6"/>
+      <c r="JWJ1" s="6"/>
+      <c r="JWM1" s="6"/>
+      <c r="JWP1" s="6"/>
+      <c r="JWS1" s="6"/>
+      <c r="JWV1" s="6"/>
+      <c r="JWY1" s="6"/>
+      <c r="JXB1" s="6"/>
+      <c r="JXE1" s="6"/>
+      <c r="JXH1" s="6"/>
+      <c r="JXK1" s="6"/>
+      <c r="JXN1" s="6"/>
+      <c r="JXQ1" s="6"/>
+      <c r="JXT1" s="6"/>
+      <c r="JXW1" s="6"/>
+      <c r="JXZ1" s="6"/>
+      <c r="JYC1" s="6"/>
+      <c r="JYF1" s="6"/>
+      <c r="JYI1" s="6"/>
+      <c r="JYL1" s="6"/>
+      <c r="JYO1" s="6"/>
+      <c r="JYR1" s="6"/>
+      <c r="JYU1" s="6"/>
+      <c r="JYX1" s="6"/>
+      <c r="JZA1" s="6"/>
+      <c r="JZD1" s="6"/>
+      <c r="JZG1" s="6"/>
+      <c r="JZJ1" s="6"/>
+      <c r="JZM1" s="6"/>
+      <c r="JZP1" s="6"/>
+      <c r="JZS1" s="6"/>
+      <c r="JZV1" s="6"/>
+      <c r="JZY1" s="6"/>
+      <c r="KAB1" s="6"/>
+      <c r="KAE1" s="6"/>
+      <c r="KAH1" s="6"/>
+      <c r="KAK1" s="6"/>
+      <c r="KAN1" s="6"/>
+      <c r="KAQ1" s="6"/>
+      <c r="KAT1" s="6"/>
+      <c r="KAW1" s="6"/>
+      <c r="KAZ1" s="6"/>
+      <c r="KBC1" s="6"/>
+      <c r="KBF1" s="6"/>
+      <c r="KBI1" s="6"/>
+      <c r="KBL1" s="6"/>
+      <c r="KBO1" s="6"/>
+      <c r="KBR1" s="6"/>
+      <c r="KBU1" s="6"/>
+      <c r="KBX1" s="6"/>
+      <c r="KCA1" s="6"/>
+      <c r="KCD1" s="6"/>
+      <c r="KCG1" s="6"/>
+      <c r="KCJ1" s="6"/>
+      <c r="KCM1" s="6"/>
+      <c r="KCP1" s="6"/>
+      <c r="KCS1" s="6"/>
+      <c r="KCV1" s="6"/>
+      <c r="KCY1" s="6"/>
+      <c r="KDB1" s="6"/>
+      <c r="KDE1" s="6"/>
+      <c r="KDH1" s="6"/>
+      <c r="KDK1" s="6"/>
+      <c r="KDN1" s="6"/>
+      <c r="KDQ1" s="6"/>
+      <c r="KDT1" s="6"/>
+      <c r="KDW1" s="6"/>
+      <c r="KDZ1" s="6"/>
+      <c r="KEC1" s="6"/>
+      <c r="KEF1" s="6"/>
+      <c r="KEI1" s="6"/>
+      <c r="KEL1" s="6"/>
+      <c r="KEO1" s="6"/>
+      <c r="KER1" s="6"/>
+      <c r="KEU1" s="6"/>
+      <c r="KEX1" s="6"/>
+      <c r="KFA1" s="6"/>
+      <c r="KFD1" s="6"/>
+      <c r="KFG1" s="6"/>
+      <c r="KFJ1" s="6"/>
+      <c r="KFM1" s="6"/>
+      <c r="KFP1" s="6"/>
+      <c r="KFS1" s="6"/>
+      <c r="KFV1" s="6"/>
+      <c r="KFY1" s="6"/>
+      <c r="KGB1" s="6"/>
+      <c r="KGE1" s="6"/>
+      <c r="KGH1" s="6"/>
+      <c r="KGK1" s="6"/>
+      <c r="KGN1" s="6"/>
+      <c r="KGQ1" s="6"/>
+      <c r="KGT1" s="6"/>
+      <c r="KGW1" s="6"/>
+      <c r="KGZ1" s="6"/>
+      <c r="KHC1" s="6"/>
+      <c r="KHF1" s="6"/>
+      <c r="KHI1" s="6"/>
+      <c r="KHL1" s="6"/>
+      <c r="KHO1" s="6"/>
+      <c r="KHR1" s="6"/>
+      <c r="KHU1" s="6"/>
+      <c r="KHX1" s="6"/>
+      <c r="KIA1" s="6"/>
+      <c r="KID1" s="6"/>
+      <c r="KIG1" s="6"/>
+      <c r="KIJ1" s="6"/>
+      <c r="KIM1" s="6"/>
+      <c r="KIP1" s="6"/>
+      <c r="KIS1" s="6"/>
+      <c r="KIV1" s="6"/>
+      <c r="KIY1" s="6"/>
+      <c r="KJB1" s="6"/>
+      <c r="KJE1" s="6"/>
+      <c r="KJH1" s="6"/>
+      <c r="KJK1" s="6"/>
+      <c r="KJN1" s="6"/>
+      <c r="KJQ1" s="6"/>
+      <c r="KJT1" s="6"/>
+      <c r="KJW1" s="6"/>
+      <c r="KJZ1" s="6"/>
+      <c r="KKC1" s="6"/>
+      <c r="KKF1" s="6"/>
+      <c r="KKI1" s="6"/>
+      <c r="KKL1" s="6"/>
+      <c r="KKO1" s="6"/>
+      <c r="KKR1" s="6"/>
+      <c r="KKU1" s="6"/>
+      <c r="KKX1" s="6"/>
+      <c r="KLA1" s="6"/>
+      <c r="KLD1" s="6"/>
+      <c r="KLG1" s="6"/>
+      <c r="KLJ1" s="6"/>
+      <c r="KLM1" s="6"/>
+      <c r="KLP1" s="6"/>
+      <c r="KLS1" s="6"/>
+      <c r="KLV1" s="6"/>
+      <c r="KLY1" s="6"/>
+      <c r="KMB1" s="6"/>
+      <c r="KME1" s="6"/>
+      <c r="KMH1" s="6"/>
+      <c r="KMK1" s="6"/>
+      <c r="KMN1" s="6"/>
+      <c r="KMQ1" s="6"/>
+      <c r="KMT1" s="6"/>
+      <c r="KMW1" s="6"/>
+      <c r="KMZ1" s="6"/>
+      <c r="KNC1" s="6"/>
+      <c r="KNF1" s="6"/>
+      <c r="KNI1" s="6"/>
+      <c r="KNL1" s="6"/>
+      <c r="KNO1" s="6"/>
+      <c r="KNR1" s="6"/>
+      <c r="KNU1" s="6"/>
+      <c r="KNX1" s="6"/>
+      <c r="KOA1" s="6"/>
+      <c r="KOD1" s="6"/>
+      <c r="KOG1" s="6"/>
+      <c r="KOJ1" s="6"/>
+      <c r="KOM1" s="6"/>
+      <c r="KOP1" s="6"/>
+      <c r="KOS1" s="6"/>
+      <c r="KOV1" s="6"/>
+      <c r="KOY1" s="6"/>
+      <c r="KPB1" s="6"/>
+      <c r="KPE1" s="6"/>
+      <c r="KPH1" s="6"/>
+      <c r="KPK1" s="6"/>
+      <c r="KPN1" s="6"/>
+      <c r="KPQ1" s="6"/>
+      <c r="KPT1" s="6"/>
+      <c r="KPW1" s="6"/>
+      <c r="KPZ1" s="6"/>
+      <c r="KQC1" s="6"/>
+      <c r="KQF1" s="6"/>
+      <c r="KQI1" s="6"/>
+      <c r="KQL1" s="6"/>
+      <c r="KQO1" s="6"/>
+      <c r="KQR1" s="6"/>
+      <c r="KQU1" s="6"/>
+      <c r="KQX1" s="6"/>
+      <c r="KRA1" s="6"/>
+      <c r="KRD1" s="6"/>
+      <c r="KRG1" s="6"/>
+      <c r="KRJ1" s="6"/>
+      <c r="KRM1" s="6"/>
+      <c r="KRP1" s="6"/>
+      <c r="KRS1" s="6"/>
+      <c r="KRV1" s="6"/>
+      <c r="KRY1" s="6"/>
+      <c r="KSB1" s="6"/>
+      <c r="KSE1" s="6"/>
+      <c r="KSH1" s="6"/>
+      <c r="KSK1" s="6"/>
+      <c r="KSN1" s="6"/>
+      <c r="KSQ1" s="6"/>
+      <c r="KST1" s="6"/>
+      <c r="KSW1" s="6"/>
+      <c r="KSZ1" s="6"/>
+      <c r="KTC1" s="6"/>
+      <c r="KTF1" s="6"/>
+      <c r="KTI1" s="6"/>
+      <c r="KTL1" s="6"/>
+      <c r="KTO1" s="6"/>
+      <c r="KTR1" s="6"/>
+      <c r="KTU1" s="6"/>
+      <c r="KTX1" s="6"/>
+      <c r="KUA1" s="6"/>
+      <c r="KUD1" s="6"/>
+      <c r="KUG1" s="6"/>
+      <c r="KUJ1" s="6"/>
+      <c r="KUM1" s="6"/>
+      <c r="KUP1" s="6"/>
+      <c r="KUS1" s="6"/>
+      <c r="KUV1" s="6"/>
+      <c r="KUY1" s="6"/>
+      <c r="KVB1" s="6"/>
+      <c r="KVE1" s="6"/>
+      <c r="KVH1" s="6"/>
+      <c r="KVK1" s="6"/>
+      <c r="KVN1" s="6"/>
+      <c r="KVQ1" s="6"/>
+      <c r="KVT1" s="6"/>
+      <c r="KVW1" s="6"/>
+      <c r="KVZ1" s="6"/>
+      <c r="KWC1" s="6"/>
+      <c r="KWF1" s="6"/>
+      <c r="KWI1" s="6"/>
+      <c r="KWL1" s="6"/>
+      <c r="KWO1" s="6"/>
+      <c r="KWR1" s="6"/>
+      <c r="KWU1" s="6"/>
+      <c r="KWX1" s="6"/>
+      <c r="KXA1" s="6"/>
+      <c r="KXD1" s="6"/>
+      <c r="KXG1" s="6"/>
+      <c r="KXJ1" s="6"/>
+      <c r="KXM1" s="6"/>
+      <c r="KXP1" s="6"/>
+      <c r="KXS1" s="6"/>
+      <c r="KXV1" s="6"/>
+      <c r="KXY1" s="6"/>
+      <c r="KYB1" s="6"/>
+      <c r="KYE1" s="6"/>
+      <c r="KYH1" s="6"/>
+      <c r="KYK1" s="6"/>
+      <c r="KYN1" s="6"/>
+      <c r="KYQ1" s="6"/>
+      <c r="KYT1" s="6"/>
+      <c r="KYW1" s="6"/>
+      <c r="KYZ1" s="6"/>
+      <c r="KZC1" s="6"/>
+      <c r="KZF1" s="6"/>
+      <c r="KZI1" s="6"/>
+      <c r="KZL1" s="6"/>
+      <c r="KZO1" s="6"/>
+      <c r="KZR1" s="6"/>
+      <c r="KZU1" s="6"/>
+      <c r="KZX1" s="6"/>
+      <c r="LAA1" s="6"/>
+      <c r="LAD1" s="6"/>
+      <c r="LAG1" s="6"/>
+      <c r="LAJ1" s="6"/>
+      <c r="LAM1" s="6"/>
+      <c r="LAP1" s="6"/>
+      <c r="LAS1" s="6"/>
+      <c r="LAV1" s="6"/>
+      <c r="LAY1" s="6"/>
+      <c r="LBB1" s="6"/>
+      <c r="LBE1" s="6"/>
+      <c r="LBH1" s="6"/>
+      <c r="LBK1" s="6"/>
+      <c r="LBN1" s="6"/>
+      <c r="LBQ1" s="6"/>
+      <c r="LBT1" s="6"/>
+      <c r="LBW1" s="6"/>
+      <c r="LBZ1" s="6"/>
+      <c r="LCC1" s="6"/>
+      <c r="LCF1" s="6"/>
+      <c r="LCI1" s="6"/>
+      <c r="LCL1" s="6"/>
+      <c r="LCO1" s="6"/>
+      <c r="LCR1" s="6"/>
+      <c r="LCU1" s="6"/>
+      <c r="LCX1" s="6"/>
+      <c r="LDA1" s="6"/>
+      <c r="LDD1" s="6"/>
+      <c r="LDG1" s="6"/>
+      <c r="LDJ1" s="6"/>
+      <c r="LDM1" s="6"/>
+      <c r="LDP1" s="6"/>
+      <c r="LDS1" s="6"/>
+      <c r="LDV1" s="6"/>
+      <c r="LDY1" s="6"/>
+      <c r="LEB1" s="6"/>
+      <c r="LEE1" s="6"/>
+      <c r="LEH1" s="6"/>
+      <c r="LEK1" s="6"/>
+      <c r="LEN1" s="6"/>
+      <c r="LEQ1" s="6"/>
+      <c r="LET1" s="6"/>
+      <c r="LEW1" s="6"/>
+      <c r="LEZ1" s="6"/>
+      <c r="LFC1" s="6"/>
+      <c r="LFF1" s="6"/>
+      <c r="LFI1" s="6"/>
+      <c r="LFL1" s="6"/>
+      <c r="LFO1" s="6"/>
+      <c r="LFR1" s="6"/>
+      <c r="LFU1" s="6"/>
+      <c r="LFX1" s="6"/>
+      <c r="LGA1" s="6"/>
+      <c r="LGD1" s="6"/>
+      <c r="LGG1" s="6"/>
+      <c r="LGJ1" s="6"/>
+      <c r="LGM1" s="6"/>
+      <c r="LGP1" s="6"/>
+      <c r="LGS1" s="6"/>
+      <c r="LGV1" s="6"/>
+      <c r="LGY1" s="6"/>
+      <c r="LHB1" s="6"/>
+      <c r="LHE1" s="6"/>
+      <c r="LHH1" s="6"/>
+      <c r="LHK1" s="6"/>
+      <c r="LHN1" s="6"/>
+      <c r="LHQ1" s="6"/>
+      <c r="LHT1" s="6"/>
+      <c r="LHW1" s="6"/>
+      <c r="LHZ1" s="6"/>
+      <c r="LIC1" s="6"/>
+      <c r="LIF1" s="6"/>
+      <c r="LII1" s="6"/>
+      <c r="LIL1" s="6"/>
+      <c r="LIO1" s="6"/>
+      <c r="LIR1" s="6"/>
+      <c r="LIU1" s="6"/>
+      <c r="LIX1" s="6"/>
+      <c r="LJA1" s="6"/>
+      <c r="LJD1" s="6"/>
+      <c r="LJG1" s="6"/>
+      <c r="LJJ1" s="6"/>
+      <c r="LJM1" s="6"/>
+      <c r="LJP1" s="6"/>
+      <c r="LJS1" s="6"/>
+      <c r="LJV1" s="6"/>
+      <c r="LJY1" s="6"/>
+      <c r="LKB1" s="6"/>
+      <c r="LKE1" s="6"/>
+      <c r="LKH1" s="6"/>
+      <c r="LKK1" s="6"/>
+      <c r="LKN1" s="6"/>
+      <c r="LKQ1" s="6"/>
+      <c r="LKT1" s="6"/>
+      <c r="LKW1" s="6"/>
+      <c r="LKZ1" s="6"/>
+      <c r="LLC1" s="6"/>
+      <c r="LLF1" s="6"/>
+      <c r="LLI1" s="6"/>
+      <c r="LLL1" s="6"/>
+      <c r="LLO1" s="6"/>
+      <c r="LLR1" s="6"/>
+      <c r="LLU1" s="6"/>
+      <c r="LLX1" s="6"/>
+      <c r="LMA1" s="6"/>
+      <c r="LMD1" s="6"/>
+      <c r="LMG1" s="6"/>
+      <c r="LMJ1" s="6"/>
+      <c r="LMM1" s="6"/>
+      <c r="LMP1" s="6"/>
+      <c r="LMS1" s="6"/>
+      <c r="LMV1" s="6"/>
+      <c r="LMY1" s="6"/>
+      <c r="LNB1" s="6"/>
+      <c r="LNE1" s="6"/>
+      <c r="LNH1" s="6"/>
+      <c r="LNK1" s="6"/>
+      <c r="LNN1" s="6"/>
+      <c r="LNQ1" s="6"/>
+      <c r="LNT1" s="6"/>
+      <c r="LNW1" s="6"/>
+      <c r="LNZ1" s="6"/>
+      <c r="LOC1" s="6"/>
+      <c r="LOF1" s="6"/>
+      <c r="LOI1" s="6"/>
+      <c r="LOL1" s="6"/>
+      <c r="LOO1" s="6"/>
+      <c r="LOR1" s="6"/>
+      <c r="LOU1" s="6"/>
+      <c r="LOX1" s="6"/>
+      <c r="LPA1" s="6"/>
+      <c r="LPD1" s="6"/>
+      <c r="LPG1" s="6"/>
+      <c r="LPJ1" s="6"/>
+      <c r="LPM1" s="6"/>
+      <c r="LPP1" s="6"/>
+      <c r="LPS1" s="6"/>
+      <c r="LPV1" s="6"/>
+      <c r="LPY1" s="6"/>
+      <c r="LQB1" s="6"/>
+      <c r="LQE1" s="6"/>
+      <c r="LQH1" s="6"/>
+      <c r="LQK1" s="6"/>
+      <c r="LQN1" s="6"/>
+      <c r="LQQ1" s="6"/>
+      <c r="LQT1" s="6"/>
+      <c r="LQW1" s="6"/>
+      <c r="LQZ1" s="6"/>
+      <c r="LRC1" s="6"/>
+      <c r="LRF1" s="6"/>
+      <c r="LRI1" s="6"/>
+      <c r="LRL1" s="6"/>
+      <c r="LRO1" s="6"/>
+      <c r="LRR1" s="6"/>
+      <c r="LRU1" s="6"/>
+      <c r="LRX1" s="6"/>
+      <c r="LSA1" s="6"/>
+      <c r="LSD1" s="6"/>
+      <c r="LSG1" s="6"/>
+      <c r="LSJ1" s="6"/>
+      <c r="LSM1" s="6"/>
+      <c r="LSP1" s="6"/>
+      <c r="LSS1" s="6"/>
+      <c r="LSV1" s="6"/>
+      <c r="LSY1" s="6"/>
+      <c r="LTB1" s="6"/>
+      <c r="LTE1" s="6"/>
+      <c r="LTH1" s="6"/>
+      <c r="LTK1" s="6"/>
+      <c r="LTN1" s="6"/>
+      <c r="LTQ1" s="6"/>
+      <c r="LTT1" s="6"/>
+      <c r="LTW1" s="6"/>
+      <c r="LTZ1" s="6"/>
+      <c r="LUC1" s="6"/>
+      <c r="LUF1" s="6"/>
+      <c r="LUI1" s="6"/>
+      <c r="LUL1" s="6"/>
+      <c r="LUO1" s="6"/>
+      <c r="LUR1" s="6"/>
+      <c r="LUU1" s="6"/>
+      <c r="LUX1" s="6"/>
+      <c r="LVA1" s="6"/>
+      <c r="LVD1" s="6"/>
+      <c r="LVG1" s="6"/>
+      <c r="LVJ1" s="6"/>
+      <c r="LVM1" s="6"/>
+      <c r="LVP1" s="6"/>
+      <c r="LVS1" s="6"/>
+      <c r="LVV1" s="6"/>
+      <c r="LVY1" s="6"/>
+      <c r="LWB1" s="6"/>
+      <c r="LWE1" s="6"/>
+      <c r="LWH1" s="6"/>
+      <c r="LWK1" s="6"/>
+      <c r="LWN1" s="6"/>
+      <c r="LWQ1" s="6"/>
+      <c r="LWT1" s="6"/>
+      <c r="LWW1" s="6"/>
+      <c r="LWZ1" s="6"/>
+      <c r="LXC1" s="6"/>
+      <c r="LXF1" s="6"/>
+      <c r="LXI1" s="6"/>
+      <c r="LXL1" s="6"/>
+      <c r="LXO1" s="6"/>
+      <c r="LXR1" s="6"/>
+      <c r="LXU1" s="6"/>
+      <c r="LXX1" s="6"/>
+      <c r="LYA1" s="6"/>
+      <c r="LYD1" s="6"/>
+      <c r="LYG1" s="6"/>
+      <c r="LYJ1" s="6"/>
+      <c r="LYM1" s="6"/>
+      <c r="LYP1" s="6"/>
+      <c r="LYS1" s="6"/>
+      <c r="LYV1" s="6"/>
+      <c r="LYY1" s="6"/>
+      <c r="LZB1" s="6"/>
+      <c r="LZE1" s="6"/>
+      <c r="LZH1" s="6"/>
+      <c r="LZK1" s="6"/>
+      <c r="LZN1" s="6"/>
+      <c r="LZQ1" s="6"/>
+      <c r="LZT1" s="6"/>
+      <c r="LZW1" s="6"/>
+      <c r="LZZ1" s="6"/>
+      <c r="MAC1" s="6"/>
+      <c r="MAF1" s="6"/>
+      <c r="MAI1" s="6"/>
+      <c r="MAL1" s="6"/>
+      <c r="MAO1" s="6"/>
+      <c r="MAR1" s="6"/>
+      <c r="MAU1" s="6"/>
+      <c r="MAX1" s="6"/>
+      <c r="MBA1" s="6"/>
+      <c r="MBD1" s="6"/>
+      <c r="MBG1" s="6"/>
+      <c r="MBJ1" s="6"/>
+      <c r="MBM1" s="6"/>
+      <c r="MBP1" s="6"/>
+      <c r="MBS1" s="6"/>
+      <c r="MBV1" s="6"/>
+      <c r="MBY1" s="6"/>
+      <c r="MCB1" s="6"/>
+      <c r="MCE1" s="6"/>
+      <c r="MCH1" s="6"/>
+      <c r="MCK1" s="6"/>
+      <c r="MCN1" s="6"/>
+      <c r="MCQ1" s="6"/>
+      <c r="MCT1" s="6"/>
+      <c r="MCW1" s="6"/>
+      <c r="MCZ1" s="6"/>
+      <c r="MDC1" s="6"/>
+      <c r="MDF1" s="6"/>
+      <c r="MDI1" s="6"/>
+      <c r="MDL1" s="6"/>
+      <c r="MDO1" s="6"/>
+      <c r="MDR1" s="6"/>
+      <c r="MDU1" s="6"/>
+      <c r="MDX1" s="6"/>
+      <c r="MEA1" s="6"/>
+      <c r="MED1" s="6"/>
+      <c r="MEG1" s="6"/>
+      <c r="MEJ1" s="6"/>
+      <c r="MEM1" s="6"/>
+      <c r="MEP1" s="6"/>
+      <c r="MES1" s="6"/>
+      <c r="MEV1" s="6"/>
+      <c r="MEY1" s="6"/>
+      <c r="MFB1" s="6"/>
+      <c r="MFE1" s="6"/>
+      <c r="MFH1" s="6"/>
+      <c r="MFK1" s="6"/>
+      <c r="MFN1" s="6"/>
+      <c r="MFQ1" s="6"/>
+      <c r="MFT1" s="6"/>
+      <c r="MFW1" s="6"/>
+      <c r="MFZ1" s="6"/>
+      <c r="MGC1" s="6"/>
+      <c r="MGF1" s="6"/>
+      <c r="MGI1" s="6"/>
+      <c r="MGL1" s="6"/>
+      <c r="MGO1" s="6"/>
+      <c r="MGR1" s="6"/>
+      <c r="MGU1" s="6"/>
+      <c r="MGX1" s="6"/>
+      <c r="MHA1" s="6"/>
+      <c r="MHD1" s="6"/>
+      <c r="MHG1" s="6"/>
+      <c r="MHJ1" s="6"/>
+      <c r="MHM1" s="6"/>
+      <c r="MHP1" s="6"/>
+      <c r="MHS1" s="6"/>
+      <c r="MHV1" s="6"/>
+      <c r="MHY1" s="6"/>
+      <c r="MIB1" s="6"/>
+      <c r="MIE1" s="6"/>
+      <c r="MIH1" s="6"/>
+      <c r="MIK1" s="6"/>
+      <c r="MIN1" s="6"/>
+      <c r="MIQ1" s="6"/>
+      <c r="MIT1" s="6"/>
+      <c r="MIW1" s="6"/>
+      <c r="MIZ1" s="6"/>
+      <c r="MJC1" s="6"/>
+      <c r="MJF1" s="6"/>
+      <c r="MJI1" s="6"/>
+      <c r="MJL1" s="6"/>
+      <c r="MJO1" s="6"/>
+      <c r="MJR1" s="6"/>
+      <c r="MJU1" s="6"/>
+      <c r="MJX1" s="6"/>
+      <c r="MKA1" s="6"/>
+      <c r="MKD1" s="6"/>
+      <c r="MKG1" s="6"/>
+      <c r="MKJ1" s="6"/>
+      <c r="MKM1" s="6"/>
+      <c r="MKP1" s="6"/>
+      <c r="MKS1" s="6"/>
+      <c r="MKV1" s="6"/>
+      <c r="MKY1" s="6"/>
+      <c r="MLB1" s="6"/>
+      <c r="MLE1" s="6"/>
+      <c r="MLH1" s="6"/>
+      <c r="MLK1" s="6"/>
+      <c r="MLN1" s="6"/>
+      <c r="MLQ1" s="6"/>
+      <c r="MLT1" s="6"/>
+      <c r="MLW1" s="6"/>
+      <c r="MLZ1" s="6"/>
+      <c r="MMC1" s="6"/>
+      <c r="MMF1" s="6"/>
+      <c r="MMI1" s="6"/>
+      <c r="MML1" s="6"/>
+      <c r="MMO1" s="6"/>
+      <c r="MMR1" s="6"/>
+      <c r="MMU1" s="6"/>
+      <c r="MMX1" s="6"/>
+      <c r="MNA1" s="6"/>
+      <c r="MND1" s="6"/>
+      <c r="MNG1" s="6"/>
+      <c r="MNJ1" s="6"/>
+      <c r="MNM1" s="6"/>
+      <c r="MNP1" s="6"/>
+      <c r="MNS1" s="6"/>
+      <c r="MNV1" s="6"/>
+      <c r="MNY1" s="6"/>
+      <c r="MOB1" s="6"/>
+      <c r="MOE1" s="6"/>
+      <c r="MOH1" s="6"/>
+      <c r="MOK1" s="6"/>
+      <c r="MON1" s="6"/>
+      <c r="MOQ1" s="6"/>
+      <c r="MOT1" s="6"/>
+      <c r="MOW1" s="6"/>
+      <c r="MOZ1" s="6"/>
+      <c r="MPC1" s="6"/>
+      <c r="MPF1" s="6"/>
+      <c r="MPI1" s="6"/>
+      <c r="MPL1" s="6"/>
+      <c r="MPO1" s="6"/>
+      <c r="MPR1" s="6"/>
+      <c r="MPU1" s="6"/>
+      <c r="MPX1" s="6"/>
+      <c r="MQA1" s="6"/>
+      <c r="MQD1" s="6"/>
+      <c r="MQG1" s="6"/>
+      <c r="MQJ1" s="6"/>
+      <c r="MQM1" s="6"/>
+      <c r="MQP1" s="6"/>
+      <c r="MQS1" s="6"/>
+      <c r="MQV1" s="6"/>
+      <c r="MQY1" s="6"/>
+      <c r="MRB1" s="6"/>
+      <c r="MRE1" s="6"/>
+      <c r="MRH1" s="6"/>
+      <c r="MRK1" s="6"/>
+      <c r="MRN1" s="6"/>
+      <c r="MRQ1" s="6"/>
+      <c r="MRT1" s="6"/>
+      <c r="MRW1" s="6"/>
+      <c r="MRZ1" s="6"/>
+      <c r="MSC1" s="6"/>
+      <c r="MSF1" s="6"/>
+      <c r="MSI1" s="6"/>
+      <c r="MSL1" s="6"/>
+      <c r="MSO1" s="6"/>
+      <c r="MSR1" s="6"/>
+      <c r="MSU1" s="6"/>
+      <c r="MSX1" s="6"/>
+      <c r="MTA1" s="6"/>
+      <c r="MTD1" s="6"/>
+      <c r="MTG1" s="6"/>
+      <c r="MTJ1" s="6"/>
+      <c r="MTM1" s="6"/>
+      <c r="MTP1" s="6"/>
+      <c r="MTS1" s="6"/>
+      <c r="MTV1" s="6"/>
+      <c r="MTY1" s="6"/>
+      <c r="MUB1" s="6"/>
+      <c r="MUE1" s="6"/>
+      <c r="MUH1" s="6"/>
+      <c r="MUK1" s="6"/>
+      <c r="MUN1" s="6"/>
+      <c r="MUQ1" s="6"/>
+      <c r="MUT1" s="6"/>
+      <c r="MUW1" s="6"/>
+      <c r="MUZ1" s="6"/>
+      <c r="MVC1" s="6"/>
+      <c r="MVF1" s="6"/>
+      <c r="MVI1" s="6"/>
+      <c r="MVL1" s="6"/>
+      <c r="MVO1" s="6"/>
+      <c r="MVR1" s="6"/>
+      <c r="MVU1" s="6"/>
+      <c r="MVX1" s="6"/>
+      <c r="MWA1" s="6"/>
+      <c r="MWD1" s="6"/>
+      <c r="MWG1" s="6"/>
+      <c r="MWJ1" s="6"/>
+      <c r="MWM1" s="6"/>
+      <c r="MWP1" s="6"/>
+      <c r="MWS1" s="6"/>
+      <c r="MWV1" s="6"/>
+      <c r="MWY1" s="6"/>
+      <c r="MXB1" s="6"/>
+      <c r="MXE1" s="6"/>
+      <c r="MXH1" s="6"/>
+      <c r="MXK1" s="6"/>
+      <c r="MXN1" s="6"/>
+      <c r="MXQ1" s="6"/>
+      <c r="MXT1" s="6"/>
+      <c r="MXW1" s="6"/>
+      <c r="MXZ1" s="6"/>
+      <c r="MYC1" s="6"/>
+      <c r="MYF1" s="6"/>
+      <c r="MYI1" s="6"/>
+      <c r="MYL1" s="6"/>
+      <c r="MYO1" s="6"/>
+      <c r="MYR1" s="6"/>
+      <c r="MYU1" s="6"/>
+      <c r="MYX1" s="6"/>
+      <c r="MZA1" s="6"/>
+      <c r="MZD1" s="6"/>
+      <c r="MZG1" s="6"/>
+      <c r="MZJ1" s="6"/>
+      <c r="MZM1" s="6"/>
+      <c r="MZP1" s="6"/>
+      <c r="MZS1" s="6"/>
+      <c r="MZV1" s="6"/>
+      <c r="MZY1" s="6"/>
+      <c r="NAB1" s="6"/>
+      <c r="NAE1" s="6"/>
+      <c r="NAH1" s="6"/>
+      <c r="NAK1" s="6"/>
+      <c r="NAN1" s="6"/>
+      <c r="NAQ1" s="6"/>
+      <c r="NAT1" s="6"/>
+      <c r="NAW1" s="6"/>
+      <c r="NAZ1" s="6"/>
+      <c r="NBC1" s="6"/>
+      <c r="NBF1" s="6"/>
+      <c r="NBI1" s="6"/>
+      <c r="NBL1" s="6"/>
+      <c r="NBO1" s="6"/>
+      <c r="NBR1" s="6"/>
+      <c r="NBU1" s="6"/>
+      <c r="NBX1" s="6"/>
+      <c r="NCA1" s="6"/>
+      <c r="NCD1" s="6"/>
+      <c r="NCG1" s="6"/>
+      <c r="NCJ1" s="6"/>
+      <c r="NCM1" s="6"/>
+      <c r="NCP1" s="6"/>
+      <c r="NCS1" s="6"/>
+      <c r="NCV1" s="6"/>
+      <c r="NCY1" s="6"/>
+      <c r="NDB1" s="6"/>
+      <c r="NDE1" s="6"/>
+      <c r="NDH1" s="6"/>
+      <c r="NDK1" s="6"/>
+      <c r="NDN1" s="6"/>
+      <c r="NDQ1" s="6"/>
+      <c r="NDT1" s="6"/>
+      <c r="NDW1" s="6"/>
+      <c r="NDZ1" s="6"/>
+      <c r="NEC1" s="6"/>
+      <c r="NEF1" s="6"/>
+      <c r="NEI1" s="6"/>
+      <c r="NEL1" s="6"/>
+      <c r="NEO1" s="6"/>
+      <c r="NER1" s="6"/>
+      <c r="NEU1" s="6"/>
+      <c r="NEX1" s="6"/>
+      <c r="NFA1" s="6"/>
+      <c r="NFD1" s="6"/>
+      <c r="NFG1" s="6"/>
+      <c r="NFJ1" s="6"/>
+      <c r="NFM1" s="6"/>
+      <c r="NFP1" s="6"/>
+      <c r="NFS1" s="6"/>
+      <c r="NFV1" s="6"/>
+      <c r="NFY1" s="6"/>
+      <c r="NGB1" s="6"/>
+      <c r="NGE1" s="6"/>
+      <c r="NGH1" s="6"/>
+      <c r="NGK1" s="6"/>
+      <c r="NGN1" s="6"/>
+      <c r="NGQ1" s="6"/>
+      <c r="NGT1" s="6"/>
+      <c r="NGW1" s="6"/>
+      <c r="NGZ1" s="6"/>
+      <c r="NHC1" s="6"/>
+      <c r="NHF1" s="6"/>
+      <c r="NHI1" s="6"/>
+      <c r="NHL1" s="6"/>
+      <c r="NHO1" s="6"/>
+      <c r="NHR1" s="6"/>
+      <c r="NHU1" s="6"/>
+      <c r="NHX1" s="6"/>
+      <c r="NIA1" s="6"/>
+      <c r="NID1" s="6"/>
+      <c r="NIG1" s="6"/>
+      <c r="NIJ1" s="6"/>
+      <c r="NIM1" s="6"/>
+      <c r="NIP1" s="6"/>
+      <c r="NIS1" s="6"/>
+      <c r="NIV1" s="6"/>
+      <c r="NIY1" s="6"/>
+      <c r="NJB1" s="6"/>
+      <c r="NJE1" s="6"/>
+      <c r="NJH1" s="6"/>
+      <c r="NJK1" s="6"/>
+      <c r="NJN1" s="6"/>
+      <c r="NJQ1" s="6"/>
+      <c r="NJT1" s="6"/>
+      <c r="NJW1" s="6"/>
+      <c r="NJZ1" s="6"/>
+      <c r="NKC1" s="6"/>
+      <c r="NKF1" s="6"/>
+      <c r="NKI1" s="6"/>
+      <c r="NKL1" s="6"/>
+      <c r="NKO1" s="6"/>
+      <c r="NKR1" s="6"/>
+      <c r="NKU1" s="6"/>
+      <c r="NKX1" s="6"/>
+      <c r="NLA1" s="6"/>
+      <c r="NLD1" s="6"/>
+      <c r="NLG1" s="6"/>
+      <c r="NLJ1" s="6"/>
+      <c r="NLM1" s="6"/>
+      <c r="NLP1" s="6"/>
+      <c r="NLS1" s="6"/>
+      <c r="NLV1" s="6"/>
+      <c r="NLY1" s="6"/>
+      <c r="NMB1" s="6"/>
+      <c r="NME1" s="6"/>
+      <c r="NMH1" s="6"/>
+      <c r="NMK1" s="6"/>
+      <c r="NMN1" s="6"/>
+      <c r="NMQ1" s="6"/>
+      <c r="NMT1" s="6"/>
+      <c r="NMW1" s="6"/>
+      <c r="NMZ1" s="6"/>
+      <c r="NNC1" s="6"/>
+      <c r="NNF1" s="6"/>
+      <c r="NNI1" s="6"/>
+      <c r="NNL1" s="6"/>
+      <c r="NNO1" s="6"/>
+      <c r="NNR1" s="6"/>
+      <c r="NNU1" s="6"/>
+      <c r="NNX1" s="6"/>
+      <c r="NOA1" s="6"/>
+      <c r="NOD1" s="6"/>
+      <c r="NOG1" s="6"/>
+      <c r="NOJ1" s="6"/>
+      <c r="NOM1" s="6"/>
+      <c r="NOP1" s="6"/>
+      <c r="NOS1" s="6"/>
+      <c r="NOV1" s="6"/>
+      <c r="NOY1" s="6"/>
+      <c r="NPB1" s="6"/>
+      <c r="NPE1" s="6"/>
+      <c r="NPH1" s="6"/>
+      <c r="NPK1" s="6"/>
+      <c r="NPN1" s="6"/>
+      <c r="NPQ1" s="6"/>
+      <c r="NPT1" s="6"/>
+      <c r="NPW1" s="6"/>
+      <c r="NPZ1" s="6"/>
+      <c r="NQC1" s="6"/>
+      <c r="NQF1" s="6"/>
+      <c r="NQI1" s="6"/>
+      <c r="NQL1" s="6"/>
+      <c r="NQO1" s="6"/>
+      <c r="NQR1" s="6"/>
+      <c r="NQU1" s="6"/>
+      <c r="NQX1" s="6"/>
+      <c r="NRA1" s="6"/>
+      <c r="NRD1" s="6"/>
+      <c r="NRG1" s="6"/>
+      <c r="NRJ1" s="6"/>
+      <c r="NRM1" s="6"/>
+      <c r="NRP1" s="6"/>
+      <c r="NRS1" s="6"/>
+      <c r="NRV1" s="6"/>
+      <c r="NRY1" s="6"/>
+      <c r="NSB1" s="6"/>
+      <c r="NSE1" s="6"/>
+      <c r="NSH1" s="6"/>
+      <c r="NSK1" s="6"/>
+      <c r="NSN1" s="6"/>
+      <c r="NSQ1" s="6"/>
+      <c r="NST1" s="6"/>
+      <c r="NSW1" s="6"/>
+      <c r="NSZ1" s="6"/>
+      <c r="NTC1" s="6"/>
+      <c r="NTF1" s="6"/>
+      <c r="NTI1" s="6"/>
+      <c r="NTL1" s="6"/>
+      <c r="NTO1" s="6"/>
+      <c r="NTR1" s="6"/>
+      <c r="NTU1" s="6"/>
+      <c r="NTX1" s="6"/>
+      <c r="NUA1" s="6"/>
+      <c r="NUD1" s="6"/>
+      <c r="NUG1" s="6"/>
+      <c r="NUJ1" s="6"/>
+      <c r="NUM1" s="6"/>
+      <c r="NUP1" s="6"/>
+      <c r="NUS1" s="6"/>
+      <c r="NUV1" s="6"/>
+      <c r="NUY1" s="6"/>
+      <c r="NVB1" s="6"/>
+      <c r="NVE1" s="6"/>
+      <c r="NVH1" s="6"/>
+      <c r="NVK1" s="6"/>
+      <c r="NVN1" s="6"/>
+      <c r="NVQ1" s="6"/>
+      <c r="NVT1" s="6"/>
+      <c r="NVW1" s="6"/>
+      <c r="NVZ1" s="6"/>
+      <c r="NWC1" s="6"/>
+      <c r="NWF1" s="6"/>
+      <c r="NWI1" s="6"/>
+      <c r="NWL1" s="6"/>
+      <c r="NWO1" s="6"/>
+      <c r="NWR1" s="6"/>
+      <c r="NWU1" s="6"/>
+      <c r="NWX1" s="6"/>
+      <c r="NXA1" s="6"/>
+      <c r="NXD1" s="6"/>
+      <c r="NXG1" s="6"/>
+      <c r="NXJ1" s="6"/>
+      <c r="NXM1" s="6"/>
+      <c r="NXP1" s="6"/>
+      <c r="NXS1" s="6"/>
+      <c r="NXV1" s="6"/>
+      <c r="NXY1" s="6"/>
+      <c r="NYB1" s="6"/>
+      <c r="NYE1" s="6"/>
+      <c r="NYH1" s="6"/>
+      <c r="NYK1" s="6"/>
+      <c r="NYN1" s="6"/>
+      <c r="NYQ1" s="6"/>
+      <c r="NYT1" s="6"/>
+      <c r="NYW1" s="6"/>
+      <c r="NYZ1" s="6"/>
+      <c r="NZC1" s="6"/>
+      <c r="NZF1" s="6"/>
+      <c r="NZI1" s="6"/>
+      <c r="NZL1" s="6"/>
+      <c r="NZO1" s="6"/>
+      <c r="NZR1" s="6"/>
+      <c r="NZU1" s="6"/>
+      <c r="NZX1" s="6"/>
+      <c r="OAA1" s="6"/>
+      <c r="OAD1" s="6"/>
+      <c r="OAG1" s="6"/>
+      <c r="OAJ1" s="6"/>
+      <c r="OAM1" s="6"/>
+      <c r="OAP1" s="6"/>
+      <c r="OAS1" s="6"/>
+      <c r="OAV1" s="6"/>
+      <c r="OAY1" s="6"/>
+      <c r="OBB1" s="6"/>
+      <c r="OBE1" s="6"/>
+      <c r="OBH1" s="6"/>
+      <c r="OBK1" s="6"/>
+      <c r="OBN1" s="6"/>
+      <c r="OBQ1" s="6"/>
+      <c r="OBT1" s="6"/>
+      <c r="OBW1" s="6"/>
+      <c r="OBZ1" s="6"/>
+      <c r="OCC1" s="6"/>
+      <c r="OCF1" s="6"/>
+      <c r="OCI1" s="6"/>
+      <c r="OCL1" s="6"/>
+      <c r="OCO1" s="6"/>
+      <c r="OCR1" s="6"/>
+      <c r="OCU1" s="6"/>
+      <c r="OCX1" s="6"/>
+      <c r="ODA1" s="6"/>
+      <c r="ODD1" s="6"/>
+      <c r="ODG1" s="6"/>
+      <c r="ODJ1" s="6"/>
+      <c r="ODM1" s="6"/>
+      <c r="ODP1" s="6"/>
+      <c r="ODS1" s="6"/>
+      <c r="ODV1" s="6"/>
+      <c r="ODY1" s="6"/>
+      <c r="OEB1" s="6"/>
+      <c r="OEE1" s="6"/>
+      <c r="OEH1" s="6"/>
+      <c r="OEK1" s="6"/>
+      <c r="OEN1" s="6"/>
+      <c r="OEQ1" s="6"/>
+      <c r="OET1" s="6"/>
+      <c r="OEW1" s="6"/>
+      <c r="OEZ1" s="6"/>
+      <c r="OFC1" s="6"/>
+      <c r="OFF1" s="6"/>
+      <c r="OFI1" s="6"/>
+      <c r="OFL1" s="6"/>
+      <c r="OFO1" s="6"/>
+      <c r="OFR1" s="6"/>
+      <c r="OFU1" s="6"/>
+      <c r="OFX1" s="6"/>
+      <c r="OGA1" s="6"/>
+      <c r="OGD1" s="6"/>
+      <c r="OGG1" s="6"/>
+      <c r="OGJ1" s="6"/>
+      <c r="OGM1" s="6"/>
+      <c r="OGP1" s="6"/>
+      <c r="OGS1" s="6"/>
+      <c r="OGV1" s="6"/>
+      <c r="OGY1" s="6"/>
+      <c r="OHB1" s="6"/>
+      <c r="OHE1" s="6"/>
+      <c r="OHH1" s="6"/>
+      <c r="OHK1" s="6"/>
+      <c r="OHN1" s="6"/>
+      <c r="OHQ1" s="6"/>
+      <c r="OHT1" s="6"/>
+      <c r="OHW1" s="6"/>
+      <c r="OHZ1" s="6"/>
+      <c r="OIC1" s="6"/>
+      <c r="OIF1" s="6"/>
+      <c r="OII1" s="6"/>
+      <c r="OIL1" s="6"/>
+      <c r="OIO1" s="6"/>
+      <c r="OIR1" s="6"/>
+      <c r="OIU1" s="6"/>
+      <c r="OIX1" s="6"/>
+      <c r="OJA1" s="6"/>
+      <c r="OJD1" s="6"/>
+      <c r="OJG1" s="6"/>
+      <c r="OJJ1" s="6"/>
+      <c r="OJM1" s="6"/>
+      <c r="OJP1" s="6"/>
+      <c r="OJS1" s="6"/>
+      <c r="OJV1" s="6"/>
+      <c r="OJY1" s="6"/>
+      <c r="OKB1" s="6"/>
+      <c r="OKE1" s="6"/>
+      <c r="OKH1" s="6"/>
+      <c r="OKK1" s="6"/>
+      <c r="OKN1" s="6"/>
+      <c r="OKQ1" s="6"/>
+      <c r="OKT1" s="6"/>
+      <c r="OKW1" s="6"/>
+      <c r="OKZ1" s="6"/>
+      <c r="OLC1" s="6"/>
+      <c r="OLF1" s="6"/>
+      <c r="OLI1" s="6"/>
+      <c r="OLL1" s="6"/>
+      <c r="OLO1" s="6"/>
+      <c r="OLR1" s="6"/>
+      <c r="OLU1" s="6"/>
+      <c r="OLX1" s="6"/>
+      <c r="OMA1" s="6"/>
+      <c r="OMD1" s="6"/>
+      <c r="OMG1" s="6"/>
+      <c r="OMJ1" s="6"/>
+      <c r="OMM1" s="6"/>
+      <c r="OMP1" s="6"/>
+      <c r="OMS1" s="6"/>
+      <c r="OMV1" s="6"/>
+      <c r="OMY1" s="6"/>
+      <c r="ONB1" s="6"/>
+      <c r="ONE1" s="6"/>
+      <c r="ONH1" s="6"/>
+      <c r="ONK1" s="6"/>
+      <c r="ONN1" s="6"/>
+      <c r="ONQ1" s="6"/>
+      <c r="ONT1" s="6"/>
+      <c r="ONW1" s="6"/>
+      <c r="ONZ1" s="6"/>
+      <c r="OOC1" s="6"/>
+      <c r="OOF1" s="6"/>
+      <c r="OOI1" s="6"/>
+      <c r="OOL1" s="6"/>
+      <c r="OOO1" s="6"/>
+      <c r="OOR1" s="6"/>
+      <c r="OOU1" s="6"/>
+      <c r="OOX1" s="6"/>
+      <c r="OPA1" s="6"/>
+      <c r="OPD1" s="6"/>
+      <c r="OPG1" s="6"/>
+      <c r="OPJ1" s="6"/>
+      <c r="OPM1" s="6"/>
+      <c r="OPP1" s="6"/>
+      <c r="OPS1" s="6"/>
+      <c r="OPV1" s="6"/>
+      <c r="OPY1" s="6"/>
+      <c r="OQB1" s="6"/>
+      <c r="OQE1" s="6"/>
+      <c r="OQH1" s="6"/>
+      <c r="OQK1" s="6"/>
+      <c r="OQN1" s="6"/>
+      <c r="OQQ1" s="6"/>
+      <c r="OQT1" s="6"/>
+      <c r="OQW1" s="6"/>
+      <c r="OQZ1" s="6"/>
+      <c r="ORC1" s="6"/>
+      <c r="ORF1" s="6"/>
+      <c r="ORI1" s="6"/>
+      <c r="ORL1" s="6"/>
+      <c r="ORO1" s="6"/>
+      <c r="ORR1" s="6"/>
+      <c r="ORU1" s="6"/>
+      <c r="ORX1" s="6"/>
+      <c r="OSA1" s="6"/>
+      <c r="OSD1" s="6"/>
+      <c r="OSG1" s="6"/>
+      <c r="OSJ1" s="6"/>
+      <c r="OSM1" s="6"/>
+      <c r="OSP1" s="6"/>
+      <c r="OSS1" s="6"/>
+      <c r="OSV1" s="6"/>
+      <c r="OSY1" s="6"/>
+      <c r="OTB1" s="6"/>
+      <c r="OTE1" s="6"/>
+      <c r="OTH1" s="6"/>
+      <c r="OTK1" s="6"/>
+      <c r="OTN1" s="6"/>
+      <c r="OTQ1" s="6"/>
+      <c r="OTT1" s="6"/>
+      <c r="OTW1" s="6"/>
+      <c r="OTZ1" s="6"/>
+      <c r="OUC1" s="6"/>
+      <c r="OUF1" s="6"/>
+      <c r="OUI1" s="6"/>
+      <c r="OUL1" s="6"/>
+      <c r="OUO1" s="6"/>
+      <c r="OUR1" s="6"/>
+      <c r="OUU1" s="6"/>
+      <c r="OUX1" s="6"/>
+      <c r="OVA1" s="6"/>
+      <c r="OVD1" s="6"/>
+      <c r="OVG1" s="6"/>
+      <c r="OVJ1" s="6"/>
+      <c r="OVM1" s="6"/>
+      <c r="OVP1" s="6"/>
+      <c r="OVS1" s="6"/>
+      <c r="OVV1" s="6"/>
+      <c r="OVY1" s="6"/>
+      <c r="OWB1" s="6"/>
+      <c r="OWE1" s="6"/>
+      <c r="OWH1" s="6"/>
+      <c r="OWK1" s="6"/>
+      <c r="OWN1" s="6"/>
+      <c r="OWQ1" s="6"/>
+      <c r="OWT1" s="6"/>
+      <c r="OWW1" s="6"/>
+      <c r="OWZ1" s="6"/>
+      <c r="OXC1" s="6"/>
+      <c r="OXF1" s="6"/>
+      <c r="OXI1" s="6"/>
+      <c r="OXL1" s="6"/>
+      <c r="OXO1" s="6"/>
+      <c r="OXR1" s="6"/>
+      <c r="OXU1" s="6"/>
+      <c r="OXX1" s="6"/>
+      <c r="OYA1" s="6"/>
+      <c r="OYD1" s="6"/>
+      <c r="OYG1" s="6"/>
+      <c r="OYJ1" s="6"/>
+      <c r="OYM1" s="6"/>
+      <c r="OYP1" s="6"/>
+      <c r="OYS1" s="6"/>
+      <c r="OYV1" s="6"/>
+      <c r="OYY1" s="6"/>
+      <c r="OZB1" s="6"/>
+      <c r="OZE1" s="6"/>
+      <c r="OZH1" s="6"/>
+      <c r="OZK1" s="6"/>
+      <c r="OZN1" s="6"/>
+      <c r="OZQ1" s="6"/>
+      <c r="OZT1" s="6"/>
+      <c r="OZW1" s="6"/>
+      <c r="OZZ1" s="6"/>
+      <c r="PAC1" s="6"/>
+      <c r="PAF1" s="6"/>
+      <c r="PAI1" s="6"/>
+      <c r="PAL1" s="6"/>
+      <c r="PAO1" s="6"/>
+      <c r="PAR1" s="6"/>
+      <c r="PAU1" s="6"/>
+      <c r="PAX1" s="6"/>
+      <c r="PBA1" s="6"/>
+      <c r="PBD1" s="6"/>
+      <c r="PBG1" s="6"/>
+      <c r="PBJ1" s="6"/>
+      <c r="PBM1" s="6"/>
+      <c r="PBP1" s="6"/>
+      <c r="PBS1" s="6"/>
+      <c r="PBV1" s="6"/>
+      <c r="PBY1" s="6"/>
+      <c r="PCB1" s="6"/>
+      <c r="PCE1" s="6"/>
+      <c r="PCH1" s="6"/>
+      <c r="PCK1" s="6"/>
+      <c r="PCN1" s="6"/>
+      <c r="PCQ1" s="6"/>
+      <c r="PCT1" s="6"/>
+      <c r="PCW1" s="6"/>
+      <c r="PCZ1" s="6"/>
+      <c r="PDC1" s="6"/>
+      <c r="PDF1" s="6"/>
+      <c r="PDI1" s="6"/>
+      <c r="PDL1" s="6"/>
+      <c r="PDO1" s="6"/>
+      <c r="PDR1" s="6"/>
+      <c r="PDU1" s="6"/>
+      <c r="PDX1" s="6"/>
+      <c r="PEA1" s="6"/>
+      <c r="PED1" s="6"/>
+      <c r="PEG1" s="6"/>
+      <c r="PEJ1" s="6"/>
+      <c r="PEM1" s="6"/>
+      <c r="PEP1" s="6"/>
+      <c r="PES1" s="6"/>
+      <c r="PEV1" s="6"/>
+      <c r="PEY1" s="6"/>
+      <c r="PFB1" s="6"/>
+      <c r="PFE1" s="6"/>
+      <c r="PFH1" s="6"/>
+      <c r="PFK1" s="6"/>
+      <c r="PFN1" s="6"/>
+      <c r="PFQ1" s="6"/>
+      <c r="PFT1" s="6"/>
+      <c r="PFW1" s="6"/>
+      <c r="PFZ1" s="6"/>
+      <c r="PGC1" s="6"/>
+      <c r="PGF1" s="6"/>
+      <c r="PGI1" s="6"/>
+      <c r="PGL1" s="6"/>
+      <c r="PGO1" s="6"/>
+      <c r="PGR1" s="6"/>
+      <c r="PGU1" s="6"/>
+      <c r="PGX1" s="6"/>
+      <c r="PHA1" s="6"/>
+      <c r="PHD1" s="6"/>
+      <c r="PHG1" s="6"/>
+      <c r="PHJ1" s="6"/>
+      <c r="PHM1" s="6"/>
+      <c r="PHP1" s="6"/>
+      <c r="PHS1" s="6"/>
+      <c r="PHV1" s="6"/>
+      <c r="PHY1" s="6"/>
+      <c r="PIB1" s="6"/>
+      <c r="PIE1" s="6"/>
+      <c r="PIH1" s="6"/>
+      <c r="PIK1" s="6"/>
+      <c r="PIN1" s="6"/>
+      <c r="PIQ1" s="6"/>
+      <c r="PIT1" s="6"/>
+      <c r="PIW1" s="6"/>
+      <c r="PIZ1" s="6"/>
+      <c r="PJC1" s="6"/>
+      <c r="PJF1" s="6"/>
+      <c r="PJI1" s="6"/>
+      <c r="PJL1" s="6"/>
+      <c r="PJO1" s="6"/>
+      <c r="PJR1" s="6"/>
+      <c r="PJU1" s="6"/>
+      <c r="PJX1" s="6"/>
+      <c r="PKA1" s="6"/>
+      <c r="PKD1" s="6"/>
+      <c r="PKG1" s="6"/>
+      <c r="PKJ1" s="6"/>
+      <c r="PKM1" s="6"/>
+      <c r="PKP1" s="6"/>
+      <c r="PKS1" s="6"/>
+      <c r="PKV1" s="6"/>
+      <c r="PKY1" s="6"/>
+      <c r="PLB1" s="6"/>
+      <c r="PLE1" s="6"/>
+      <c r="PLH1" s="6"/>
+      <c r="PLK1" s="6"/>
+      <c r="PLN1" s="6"/>
+      <c r="PLQ1" s="6"/>
+      <c r="PLT1" s="6"/>
+      <c r="PLW1" s="6"/>
+      <c r="PLZ1" s="6"/>
+      <c r="PMC1" s="6"/>
+      <c r="PMF1" s="6"/>
+      <c r="PMI1" s="6"/>
+      <c r="PML1" s="6"/>
+      <c r="PMO1" s="6"/>
+      <c r="PMR1" s="6"/>
+      <c r="PMU1" s="6"/>
+      <c r="PMX1" s="6"/>
+      <c r="PNA1" s="6"/>
+      <c r="PND1" s="6"/>
+      <c r="PNG1" s="6"/>
+      <c r="PNJ1" s="6"/>
+      <c r="PNM1" s="6"/>
+      <c r="PNP1" s="6"/>
+      <c r="PNS1" s="6"/>
+      <c r="PNV1" s="6"/>
+      <c r="PNY1" s="6"/>
+      <c r="POB1" s="6"/>
+      <c r="POE1" s="6"/>
+      <c r="POH1" s="6"/>
+      <c r="POK1" s="6"/>
+      <c r="PON1" s="6"/>
+      <c r="POQ1" s="6"/>
+      <c r="POT1" s="6"/>
+      <c r="POW1" s="6"/>
+      <c r="POZ1" s="6"/>
+      <c r="PPC1" s="6"/>
+      <c r="PPF1" s="6"/>
+      <c r="PPI1" s="6"/>
+      <c r="PPL1" s="6"/>
+      <c r="PPO1" s="6"/>
+      <c r="PPR1" s="6"/>
+      <c r="PPU1" s="6"/>
+      <c r="PPX1" s="6"/>
+      <c r="PQA1" s="6"/>
+      <c r="PQD1" s="6"/>
+      <c r="PQG1" s="6"/>
+      <c r="PQJ1" s="6"/>
+      <c r="PQM1" s="6"/>
+      <c r="PQP1" s="6"/>
+      <c r="PQS1" s="6"/>
+      <c r="PQV1" s="6"/>
+      <c r="PQY1" s="6"/>
+      <c r="PRB1" s="6"/>
+      <c r="PRE1" s="6"/>
+      <c r="PRH1" s="6"/>
+      <c r="PRK1" s="6"/>
+      <c r="PRN1" s="6"/>
+      <c r="PRQ1" s="6"/>
+      <c r="PRT1" s="6"/>
+      <c r="PRW1" s="6"/>
+      <c r="PRZ1" s="6"/>
+      <c r="PSC1" s="6"/>
+      <c r="PSF1" s="6"/>
+      <c r="PSI1" s="6"/>
+      <c r="PSL1" s="6"/>
+      <c r="PSO1" s="6"/>
+      <c r="PSR1" s="6"/>
+      <c r="PSU1" s="6"/>
+      <c r="PSX1" s="6"/>
+      <c r="PTA1" s="6"/>
+      <c r="PTD1" s="6"/>
+      <c r="PTG1" s="6"/>
+      <c r="PTJ1" s="6"/>
+      <c r="PTM1" s="6"/>
+      <c r="PTP1" s="6"/>
+      <c r="PTS1" s="6"/>
+      <c r="PTV1" s="6"/>
+      <c r="PTY1" s="6"/>
+      <c r="PUB1" s="6"/>
+      <c r="PUE1" s="6"/>
+      <c r="PUH1" s="6"/>
+      <c r="PUK1" s="6"/>
+      <c r="PUN1" s="6"/>
+      <c r="PUQ1" s="6"/>
+      <c r="PUT1" s="6"/>
+      <c r="PUW1" s="6"/>
+      <c r="PUZ1" s="6"/>
+      <c r="PVC1" s="6"/>
+      <c r="PVF1" s="6"/>
+      <c r="PVI1" s="6"/>
+      <c r="PVL1" s="6"/>
+      <c r="PVO1" s="6"/>
+      <c r="PVR1" s="6"/>
+      <c r="PVU1" s="6"/>
+      <c r="PVX1" s="6"/>
+      <c r="PWA1" s="6"/>
+      <c r="PWD1" s="6"/>
+      <c r="PWG1" s="6"/>
+      <c r="PWJ1" s="6"/>
+      <c r="PWM1" s="6"/>
+      <c r="PWP1" s="6"/>
+      <c r="PWS1" s="6"/>
+      <c r="PWV1" s="6"/>
+      <c r="PWY1" s="6"/>
+      <c r="PXB1" s="6"/>
+      <c r="PXE1" s="6"/>
+      <c r="PXH1" s="6"/>
+      <c r="PXK1" s="6"/>
+      <c r="PXN1" s="6"/>
+      <c r="PXQ1" s="6"/>
+      <c r="PXT1" s="6"/>
+      <c r="PXW1" s="6"/>
+      <c r="PXZ1" s="6"/>
+      <c r="PYC1" s="6"/>
+      <c r="PYF1" s="6"/>
+      <c r="PYI1" s="6"/>
+      <c r="PYL1" s="6"/>
+      <c r="PYO1" s="6"/>
+      <c r="PYR1" s="6"/>
+      <c r="PYU1" s="6"/>
+      <c r="PYX1" s="6"/>
+      <c r="PZA1" s="6"/>
+      <c r="PZD1" s="6"/>
+      <c r="PZG1" s="6"/>
+      <c r="PZJ1" s="6"/>
+      <c r="PZM1" s="6"/>
+      <c r="PZP1" s="6"/>
+      <c r="PZS1" s="6"/>
+      <c r="PZV1" s="6"/>
+      <c r="PZY1" s="6"/>
+      <c r="QAB1" s="6"/>
+      <c r="QAE1" s="6"/>
+      <c r="QAH1" s="6"/>
+      <c r="QAK1" s="6"/>
+      <c r="QAN1" s="6"/>
+      <c r="QAQ1" s="6"/>
+      <c r="QAT1" s="6"/>
+      <c r="QAW1" s="6"/>
+      <c r="QAZ1" s="6"/>
+      <c r="QBC1" s="6"/>
+      <c r="QBF1" s="6"/>
+      <c r="QBI1" s="6"/>
+      <c r="QBL1" s="6"/>
+      <c r="QBO1" s="6"/>
+      <c r="QBR1" s="6"/>
+      <c r="QBU1" s="6"/>
+      <c r="QBX1" s="6"/>
+      <c r="QCA1" s="6"/>
+      <c r="QCD1" s="6"/>
+      <c r="QCG1" s="6"/>
+      <c r="QCJ1" s="6"/>
+      <c r="QCM1" s="6"/>
+      <c r="QCP1" s="6"/>
+      <c r="QCS1" s="6"/>
+      <c r="QCV1" s="6"/>
+      <c r="QCY1" s="6"/>
+      <c r="QDB1" s="6"/>
+      <c r="QDE1" s="6"/>
+      <c r="QDH1" s="6"/>
+      <c r="QDK1" s="6"/>
+      <c r="QDN1" s="6"/>
+      <c r="QDQ1" s="6"/>
+      <c r="QDT1" s="6"/>
+      <c r="QDW1" s="6"/>
+      <c r="QDZ1" s="6"/>
+      <c r="QEC1" s="6"/>
+      <c r="QEF1" s="6"/>
+      <c r="QEI1" s="6"/>
+      <c r="QEL1" s="6"/>
+      <c r="QEO1" s="6"/>
+      <c r="QER1" s="6"/>
+      <c r="QEU1" s="6"/>
+      <c r="QEX1" s="6"/>
+      <c r="QFA1" s="6"/>
+      <c r="QFD1" s="6"/>
+      <c r="QFG1" s="6"/>
+      <c r="QFJ1" s="6"/>
+      <c r="QFM1" s="6"/>
+      <c r="QFP1" s="6"/>
+      <c r="QFS1" s="6"/>
+      <c r="QFV1" s="6"/>
+      <c r="QFY1" s="6"/>
+      <c r="QGB1" s="6"/>
+      <c r="QGE1" s="6"/>
+      <c r="QGH1" s="6"/>
+      <c r="QGK1" s="6"/>
+      <c r="QGN1" s="6"/>
+      <c r="QGQ1" s="6"/>
+      <c r="QGT1" s="6"/>
+      <c r="QGW1" s="6"/>
+      <c r="QGZ1" s="6"/>
+      <c r="QHC1" s="6"/>
+      <c r="QHF1" s="6"/>
+      <c r="QHI1" s="6"/>
+      <c r="QHL1" s="6"/>
+      <c r="QHO1" s="6"/>
+      <c r="QHR1" s="6"/>
+      <c r="QHU1" s="6"/>
+      <c r="QHX1" s="6"/>
+      <c r="QIA1" s="6"/>
+      <c r="QID1" s="6"/>
+      <c r="QIG1" s="6"/>
+      <c r="QIJ1" s="6"/>
+      <c r="QIM1" s="6"/>
+      <c r="QIP1" s="6"/>
+      <c r="QIS1" s="6"/>
+      <c r="QIV1" s="6"/>
+      <c r="QIY1" s="6"/>
+      <c r="QJB1" s="6"/>
+      <c r="QJE1" s="6"/>
+      <c r="QJH1" s="6"/>
+      <c r="QJK1" s="6"/>
+      <c r="QJN1" s="6"/>
+      <c r="QJQ1" s="6"/>
+      <c r="QJT1" s="6"/>
+      <c r="QJW1" s="6"/>
+      <c r="QJZ1" s="6"/>
+      <c r="QKC1" s="6"/>
+      <c r="QKF1" s="6"/>
+      <c r="QKI1" s="6"/>
+      <c r="QKL1" s="6"/>
+      <c r="QKO1" s="6"/>
+      <c r="QKR1" s="6"/>
+      <c r="QKU1" s="6"/>
+      <c r="QKX1" s="6"/>
+      <c r="QLA1" s="6"/>
+      <c r="QLD1" s="6"/>
+      <c r="QLG1" s="6"/>
+      <c r="QLJ1" s="6"/>
+      <c r="QLM1" s="6"/>
+      <c r="QLP1" s="6"/>
+      <c r="QLS1" s="6"/>
+      <c r="QLV1" s="6"/>
+      <c r="QLY1" s="6"/>
+      <c r="QMB1" s="6"/>
+      <c r="QME1" s="6"/>
+      <c r="QMH1" s="6"/>
+      <c r="QMK1" s="6"/>
+      <c r="QMN1" s="6"/>
+      <c r="QMQ1" s="6"/>
+      <c r="QMT1" s="6"/>
+      <c r="QMW1" s="6"/>
+      <c r="QMZ1" s="6"/>
+      <c r="QNC1" s="6"/>
+      <c r="QNF1" s="6"/>
+      <c r="QNI1" s="6"/>
+      <c r="QNL1" s="6"/>
+      <c r="QNO1" s="6"/>
+      <c r="QNR1" s="6"/>
+      <c r="QNU1" s="6"/>
+      <c r="QNX1" s="6"/>
+      <c r="QOA1" s="6"/>
+      <c r="QOD1" s="6"/>
+      <c r="QOG1" s="6"/>
+      <c r="QOJ1" s="6"/>
+      <c r="QOM1" s="6"/>
+      <c r="QOP1" s="6"/>
+      <c r="QOS1" s="6"/>
+      <c r="QOV1" s="6"/>
+      <c r="QOY1" s="6"/>
+      <c r="QPB1" s="6"/>
+      <c r="QPE1" s="6"/>
+      <c r="QPH1" s="6"/>
+      <c r="QPK1" s="6"/>
+      <c r="QPN1" s="6"/>
+      <c r="QPQ1" s="6"/>
+      <c r="QPT1" s="6"/>
+      <c r="QPW1" s="6"/>
+      <c r="QPZ1" s="6"/>
+      <c r="QQC1" s="6"/>
+      <c r="QQF1" s="6"/>
+      <c r="QQI1" s="6"/>
+      <c r="QQL1" s="6"/>
+      <c r="QQO1" s="6"/>
+      <c r="QQR1" s="6"/>
+      <c r="QQU1" s="6"/>
+      <c r="QQX1" s="6"/>
+      <c r="QRA1" s="6"/>
+      <c r="QRD1" s="6"/>
+      <c r="QRG1" s="6"/>
+      <c r="QRJ1" s="6"/>
+      <c r="QRM1" s="6"/>
+      <c r="QRP1" s="6"/>
+      <c r="QRS1" s="6"/>
+      <c r="QRV1" s="6"/>
+      <c r="QRY1" s="6"/>
+      <c r="QSB1" s="6"/>
+      <c r="QSE1" s="6"/>
+      <c r="QSH1" s="6"/>
+      <c r="QSK1" s="6"/>
+      <c r="QSN1" s="6"/>
+      <c r="QSQ1" s="6"/>
+      <c r="QST1" s="6"/>
+      <c r="QSW1" s="6"/>
+      <c r="QSZ1" s="6"/>
+      <c r="QTC1" s="6"/>
+      <c r="QTF1" s="6"/>
+      <c r="QTI1" s="6"/>
+      <c r="QTL1" s="6"/>
+      <c r="QTO1" s="6"/>
+      <c r="QTR1" s="6"/>
+      <c r="QTU1" s="6"/>
+      <c r="QTX1" s="6"/>
+      <c r="QUA1" s="6"/>
+      <c r="QUD1" s="6"/>
+      <c r="QUG1" s="6"/>
+      <c r="QUJ1" s="6"/>
+      <c r="QUM1" s="6"/>
+      <c r="QUP1" s="6"/>
+      <c r="QUS1" s="6"/>
+      <c r="QUV1" s="6"/>
+      <c r="QUY1" s="6"/>
+      <c r="QVB1" s="6"/>
+      <c r="QVE1" s="6"/>
+      <c r="QVH1" s="6"/>
+      <c r="QVK1" s="6"/>
+      <c r="QVN1" s="6"/>
+      <c r="QVQ1" s="6"/>
+      <c r="QVT1" s="6"/>
+      <c r="QVW1" s="6"/>
+      <c r="QVZ1" s="6"/>
+      <c r="QWC1" s="6"/>
+      <c r="QWF1" s="6"/>
+      <c r="QWI1" s="6"/>
+      <c r="QWL1" s="6"/>
+      <c r="QWO1" s="6"/>
+      <c r="QWR1" s="6"/>
+      <c r="QWU1" s="6"/>
+      <c r="QWX1" s="6"/>
+      <c r="QXA1" s="6"/>
+      <c r="QXD1" s="6"/>
+      <c r="QXG1" s="6"/>
+      <c r="QXJ1" s="6"/>
+      <c r="QXM1" s="6"/>
+      <c r="QXP1" s="6"/>
+      <c r="QXS1" s="6"/>
+      <c r="QXV1" s="6"/>
+      <c r="QXY1" s="6"/>
+      <c r="QYB1" s="6"/>
+      <c r="QYE1" s="6"/>
+      <c r="QYH1" s="6"/>
+      <c r="QYK1" s="6"/>
+      <c r="QYN1" s="6"/>
+      <c r="QYQ1" s="6"/>
+      <c r="QYT1" s="6"/>
+      <c r="QYW1" s="6"/>
+      <c r="QYZ1" s="6"/>
+      <c r="QZC1" s="6"/>
+      <c r="QZF1" s="6"/>
+      <c r="QZI1" s="6"/>
+      <c r="QZL1" s="6"/>
+      <c r="QZO1" s="6"/>
+      <c r="QZR1" s="6"/>
+      <c r="QZU1" s="6"/>
+      <c r="QZX1" s="6"/>
+      <c r="RAA1" s="6"/>
+      <c r="RAD1" s="6"/>
+      <c r="RAG1" s="6"/>
+      <c r="RAJ1" s="6"/>
+      <c r="RAM1" s="6"/>
+      <c r="RAP1" s="6"/>
+      <c r="RAS1" s="6"/>
+      <c r="RAV1" s="6"/>
+      <c r="RAY1" s="6"/>
+      <c r="RBB1" s="6"/>
+      <c r="RBE1" s="6"/>
+      <c r="RBH1" s="6"/>
+      <c r="RBK1" s="6"/>
+      <c r="RBN1" s="6"/>
+      <c r="RBQ1" s="6"/>
+      <c r="RBT1" s="6"/>
+      <c r="RBW1" s="6"/>
+      <c r="RBZ1" s="6"/>
+      <c r="RCC1" s="6"/>
+      <c r="RCF1" s="6"/>
+      <c r="RCI1" s="6"/>
+      <c r="RCL1" s="6"/>
+      <c r="RCO1" s="6"/>
+      <c r="RCR1" s="6"/>
+      <c r="RCU1" s="6"/>
+      <c r="RCX1" s="6"/>
+      <c r="RDA1" s="6"/>
+      <c r="RDD1" s="6"/>
+      <c r="RDG1" s="6"/>
+      <c r="RDJ1" s="6"/>
+      <c r="RDM1" s="6"/>
+      <c r="RDP1" s="6"/>
+      <c r="RDS1" s="6"/>
+      <c r="RDV1" s="6"/>
+      <c r="RDY1" s="6"/>
+      <c r="REB1" s="6"/>
+      <c r="REE1" s="6"/>
+      <c r="REH1" s="6"/>
+      <c r="REK1" s="6"/>
+      <c r="REN1" s="6"/>
+      <c r="REQ1" s="6"/>
+      <c r="RET1" s="6"/>
+      <c r="REW1" s="6"/>
+      <c r="REZ1" s="6"/>
+      <c r="RFC1" s="6"/>
+      <c r="RFF1" s="6"/>
+      <c r="RFI1" s="6"/>
+      <c r="RFL1" s="6"/>
+      <c r="RFO1" s="6"/>
+      <c r="RFR1" s="6"/>
+      <c r="RFU1" s="6"/>
+      <c r="RFX1" s="6"/>
+      <c r="RGA1" s="6"/>
+      <c r="RGD1" s="6"/>
+      <c r="RGG1" s="6"/>
+      <c r="RGJ1" s="6"/>
+      <c r="RGM1" s="6"/>
+      <c r="RGP1" s="6"/>
+      <c r="RGS1" s="6"/>
+      <c r="RGV1" s="6"/>
+      <c r="RGY1" s="6"/>
+      <c r="RHB1" s="6"/>
+      <c r="RHE1" s="6"/>
+      <c r="RHH1" s="6"/>
+      <c r="RHK1" s="6"/>
+      <c r="RHN1" s="6"/>
+      <c r="RHQ1" s="6"/>
+      <c r="RHT1" s="6"/>
+      <c r="RHW1" s="6"/>
+      <c r="RHZ1" s="6"/>
+      <c r="RIC1" s="6"/>
+      <c r="RIF1" s="6"/>
+      <c r="RII1" s="6"/>
+      <c r="RIL1" s="6"/>
+      <c r="RIO1" s="6"/>
+      <c r="RIR1" s="6"/>
+      <c r="RIU1" s="6"/>
+      <c r="RIX1" s="6"/>
+      <c r="RJA1" s="6"/>
+      <c r="RJD1" s="6"/>
+      <c r="RJG1" s="6"/>
+      <c r="RJJ1" s="6"/>
+      <c r="RJM1" s="6"/>
+      <c r="RJP1" s="6"/>
+      <c r="RJS1" s="6"/>
+      <c r="RJV1" s="6"/>
+      <c r="RJY1" s="6"/>
+      <c r="RKB1" s="6"/>
+      <c r="RKE1" s="6"/>
+      <c r="RKH1" s="6"/>
+      <c r="RKK1" s="6"/>
+      <c r="RKN1" s="6"/>
+      <c r="RKQ1" s="6"/>
+      <c r="RKT1" s="6"/>
+      <c r="RKW1" s="6"/>
+      <c r="RKZ1" s="6"/>
+      <c r="RLC1" s="6"/>
+      <c r="RLF1" s="6"/>
+      <c r="RLI1" s="6"/>
+      <c r="RLL1" s="6"/>
+      <c r="RLO1" s="6"/>
+      <c r="RLR1" s="6"/>
+      <c r="RLU1" s="6"/>
+      <c r="RLX1" s="6"/>
+      <c r="RMA1" s="6"/>
+      <c r="RMD1" s="6"/>
+      <c r="RMG1" s="6"/>
+      <c r="RMJ1" s="6"/>
+      <c r="RMM1" s="6"/>
+      <c r="RMP1" s="6"/>
+      <c r="RMS1" s="6"/>
+      <c r="RMV1" s="6"/>
+      <c r="RMY1" s="6"/>
+      <c r="RNB1" s="6"/>
+      <c r="RNE1" s="6"/>
+      <c r="RNH1" s="6"/>
+      <c r="RNK1" s="6"/>
+      <c r="RNN1" s="6"/>
+      <c r="RNQ1" s="6"/>
+      <c r="RNT1" s="6"/>
+      <c r="RNW1" s="6"/>
+      <c r="RNZ1" s="6"/>
+      <c r="ROC1" s="6"/>
+      <c r="ROF1" s="6"/>
+      <c r="ROI1" s="6"/>
+      <c r="ROL1" s="6"/>
+      <c r="ROO1" s="6"/>
+      <c r="ROR1" s="6"/>
+      <c r="ROU1" s="6"/>
+      <c r="ROX1" s="6"/>
+      <c r="RPA1" s="6"/>
+      <c r="RPD1" s="6"/>
+      <c r="RPG1" s="6"/>
+      <c r="RPJ1" s="6"/>
+      <c r="RPM1" s="6"/>
+      <c r="RPP1" s="6"/>
+      <c r="RPS1" s="6"/>
+      <c r="RPV1" s="6"/>
+      <c r="RPY1" s="6"/>
+      <c r="RQB1" s="6"/>
+      <c r="RQE1" s="6"/>
+      <c r="RQH1" s="6"/>
+      <c r="RQK1" s="6"/>
+      <c r="RQN1" s="6"/>
+      <c r="RQQ1" s="6"/>
+      <c r="RQT1" s="6"/>
+      <c r="RQW1" s="6"/>
+      <c r="RQZ1" s="6"/>
+      <c r="RRC1" s="6"/>
+      <c r="RRF1" s="6"/>
+      <c r="RRI1" s="6"/>
+      <c r="RRL1" s="6"/>
+      <c r="RRO1" s="6"/>
+      <c r="RRR1" s="6"/>
+      <c r="RRU1" s="6"/>
+      <c r="RRX1" s="6"/>
+      <c r="RSA1" s="6"/>
+      <c r="RSD1" s="6"/>
+      <c r="RSG1" s="6"/>
+      <c r="RSJ1" s="6"/>
+      <c r="RSM1" s="6"/>
+      <c r="RSP1" s="6"/>
+      <c r="RSS1" s="6"/>
+      <c r="RSV1" s="6"/>
+      <c r="RSY1" s="6"/>
+      <c r="RTB1" s="6"/>
+      <c r="RTE1" s="6"/>
+      <c r="RTH1" s="6"/>
+      <c r="RTK1" s="6"/>
+      <c r="RTN1" s="6"/>
+      <c r="RTQ1" s="6"/>
+      <c r="RTT1" s="6"/>
+      <c r="RTW1" s="6"/>
+      <c r="RTZ1" s="6"/>
+      <c r="RUC1" s="6"/>
+      <c r="RUF1" s="6"/>
+      <c r="RUI1" s="6"/>
+      <c r="RUL1" s="6"/>
+      <c r="RUO1" s="6"/>
+      <c r="RUR1" s="6"/>
+      <c r="RUU1" s="6"/>
+      <c r="RUX1" s="6"/>
+      <c r="RVA1" s="6"/>
+      <c r="RVD1" s="6"/>
+      <c r="RVG1" s="6"/>
+      <c r="RVJ1" s="6"/>
+      <c r="RVM1" s="6"/>
+      <c r="RVP1" s="6"/>
+      <c r="RVS1" s="6"/>
+      <c r="RVV1" s="6"/>
+      <c r="RVY1" s="6"/>
+      <c r="RWB1" s="6"/>
+      <c r="RWE1" s="6"/>
+      <c r="RWH1" s="6"/>
+      <c r="RWK1" s="6"/>
+      <c r="RWN1" s="6"/>
+      <c r="RWQ1" s="6"/>
+      <c r="RWT1" s="6"/>
+      <c r="RWW1" s="6"/>
+      <c r="RWZ1" s="6"/>
+      <c r="RXC1" s="6"/>
+      <c r="RXF1" s="6"/>
+      <c r="RXI1" s="6"/>
+      <c r="RXL1" s="6"/>
+      <c r="RXO1" s="6"/>
+      <c r="RXR1" s="6"/>
+      <c r="RXU1" s="6"/>
+      <c r="RXX1" s="6"/>
+      <c r="RYA1" s="6"/>
+      <c r="RYD1" s="6"/>
+      <c r="RYG1" s="6"/>
+      <c r="RYJ1" s="6"/>
+      <c r="RYM1" s="6"/>
+      <c r="RYP1" s="6"/>
+      <c r="RYS1" s="6"/>
+      <c r="RYV1" s="6"/>
+      <c r="RYY1" s="6"/>
+      <c r="RZB1" s="6"/>
+      <c r="RZE1" s="6"/>
+      <c r="RZH1" s="6"/>
+      <c r="RZK1" s="6"/>
+      <c r="RZN1" s="6"/>
+      <c r="RZQ1" s="6"/>
+      <c r="RZT1" s="6"/>
+      <c r="RZW1" s="6"/>
+      <c r="RZZ1" s="6"/>
+      <c r="SAC1" s="6"/>
+      <c r="SAF1" s="6"/>
+      <c r="SAI1" s="6"/>
+      <c r="SAL1" s="6"/>
+      <c r="SAO1" s="6"/>
+      <c r="SAR1" s="6"/>
+      <c r="SAU1" s="6"/>
+      <c r="SAX1" s="6"/>
+      <c r="SBA1" s="6"/>
+      <c r="SBD1" s="6"/>
+      <c r="SBG1" s="6"/>
+      <c r="SBJ1" s="6"/>
+      <c r="SBM1" s="6"/>
+      <c r="SBP1" s="6"/>
+      <c r="SBS1" s="6"/>
+      <c r="SBV1" s="6"/>
+      <c r="SBY1" s="6"/>
+      <c r="SCB1" s="6"/>
+      <c r="SCE1" s="6"/>
+      <c r="SCH1" s="6"/>
+      <c r="SCK1" s="6"/>
+      <c r="SCN1" s="6"/>
+      <c r="SCQ1" s="6"/>
+      <c r="SCT1" s="6"/>
+      <c r="SCW1" s="6"/>
+      <c r="SCZ1" s="6"/>
+      <c r="SDC1" s="6"/>
+      <c r="SDF1" s="6"/>
+      <c r="SDI1" s="6"/>
+      <c r="SDL1" s="6"/>
+      <c r="SDO1" s="6"/>
+      <c r="SDR1" s="6"/>
+      <c r="SDU1" s="6"/>
+      <c r="SDX1" s="6"/>
+      <c r="SEA1" s="6"/>
+      <c r="SED1" s="6"/>
+      <c r="SEG1" s="6"/>
+      <c r="SEJ1" s="6"/>
+      <c r="SEM1" s="6"/>
+      <c r="SEP1" s="6"/>
+      <c r="SES1" s="6"/>
+      <c r="SEV1" s="6"/>
+      <c r="SEY1" s="6"/>
+      <c r="SFB1" s="6"/>
+      <c r="SFE1" s="6"/>
+      <c r="SFH1" s="6"/>
+      <c r="SFK1" s="6"/>
+      <c r="SFN1" s="6"/>
+      <c r="SFQ1" s="6"/>
+      <c r="SFT1" s="6"/>
+      <c r="SFW1" s="6"/>
+      <c r="SFZ1" s="6"/>
+      <c r="SGC1" s="6"/>
+      <c r="SGF1" s="6"/>
+      <c r="SGI1" s="6"/>
+      <c r="SGL1" s="6"/>
+      <c r="SGO1" s="6"/>
+      <c r="SGR1" s="6"/>
+      <c r="SGU1" s="6"/>
+      <c r="SGX1" s="6"/>
+      <c r="SHA1" s="6"/>
+      <c r="SHD1" s="6"/>
+      <c r="SHG1" s="6"/>
+      <c r="SHJ1" s="6"/>
+      <c r="SHM1" s="6"/>
+      <c r="SHP1" s="6"/>
+      <c r="SHS1" s="6"/>
+      <c r="SHV1" s="6"/>
+      <c r="SHY1" s="6"/>
+      <c r="SIB1" s="6"/>
+      <c r="SIE1" s="6"/>
+      <c r="SIH1" s="6"/>
+      <c r="SIK1" s="6"/>
+      <c r="SIN1" s="6"/>
+      <c r="SIQ1" s="6"/>
+      <c r="SIT1" s="6"/>
+      <c r="SIW1" s="6"/>
+      <c r="SIZ1" s="6"/>
+      <c r="SJC1" s="6"/>
+      <c r="SJF1" s="6"/>
+      <c r="SJI1" s="6"/>
+      <c r="SJL1" s="6"/>
+      <c r="SJO1" s="6"/>
+      <c r="SJR1" s="6"/>
+      <c r="SJU1" s="6"/>
+      <c r="SJX1" s="6"/>
+      <c r="SKA1" s="6"/>
+      <c r="SKD1" s="6"/>
+      <c r="SKG1" s="6"/>
+      <c r="SKJ1" s="6"/>
+      <c r="SKM1" s="6"/>
+      <c r="SKP1" s="6"/>
+      <c r="SKS1" s="6"/>
+      <c r="SKV1" s="6"/>
+      <c r="SKY1" s="6"/>
+      <c r="SLB1" s="6"/>
+      <c r="SLE1" s="6"/>
+      <c r="SLH1" s="6"/>
+      <c r="SLK1" s="6"/>
+      <c r="SLN1" s="6"/>
+      <c r="SLQ1" s="6"/>
+      <c r="SLT1" s="6"/>
+      <c r="SLW1" s="6"/>
+      <c r="SLZ1" s="6"/>
+      <c r="SMC1" s="6"/>
+      <c r="SMF1" s="6"/>
+      <c r="SMI1" s="6"/>
+      <c r="SML1" s="6"/>
+      <c r="SMO1" s="6"/>
+      <c r="SMR1" s="6"/>
+      <c r="SMU1" s="6"/>
+      <c r="SMX1" s="6"/>
+      <c r="SNA1" s="6"/>
+      <c r="SND1" s="6"/>
+      <c r="SNG1" s="6"/>
+      <c r="SNJ1" s="6"/>
+      <c r="SNM1" s="6"/>
+      <c r="SNP1" s="6"/>
+      <c r="SNS1" s="6"/>
+      <c r="SNV1" s="6"/>
+      <c r="SNY1" s="6"/>
+      <c r="SOB1" s="6"/>
+      <c r="SOE1" s="6"/>
+      <c r="SOH1" s="6"/>
+      <c r="SOK1" s="6"/>
+      <c r="SON1" s="6"/>
+      <c r="SOQ1" s="6"/>
+      <c r="SOT1" s="6"/>
+      <c r="SOW1" s="6"/>
+      <c r="SOZ1" s="6"/>
+      <c r="SPC1" s="6"/>
+      <c r="SPF1" s="6"/>
+      <c r="SPI1" s="6"/>
+      <c r="SPL1" s="6"/>
+      <c r="SPO1" s="6"/>
+      <c r="SPR1" s="6"/>
+      <c r="SPU1" s="6"/>
+      <c r="SPX1" s="6"/>
+      <c r="SQA1" s="6"/>
+      <c r="SQD1" s="6"/>
+      <c r="SQG1" s="6"/>
+      <c r="SQJ1" s="6"/>
+      <c r="SQM1" s="6"/>
+      <c r="SQP1" s="6"/>
+      <c r="SQS1" s="6"/>
+      <c r="SQV1" s="6"/>
+      <c r="SQY1" s="6"/>
+      <c r="SRB1" s="6"/>
+      <c r="SRE1" s="6"/>
+      <c r="SRH1" s="6"/>
+      <c r="SRK1" s="6"/>
+      <c r="SRN1" s="6"/>
+      <c r="SRQ1" s="6"/>
+      <c r="SRT1" s="6"/>
+      <c r="SRW1" s="6"/>
+      <c r="SRZ1" s="6"/>
+      <c r="SSC1" s="6"/>
+      <c r="SSF1" s="6"/>
+      <c r="SSI1" s="6"/>
+      <c r="SSL1" s="6"/>
+      <c r="SSO1" s="6"/>
+      <c r="SSR1" s="6"/>
+      <c r="SSU1" s="6"/>
+      <c r="SSX1" s="6"/>
+      <c r="STA1" s="6"/>
+      <c r="STD1" s="6"/>
+      <c r="STG1" s="6"/>
+      <c r="STJ1" s="6"/>
+      <c r="STM1" s="6"/>
+      <c r="STP1" s="6"/>
+      <c r="STS1" s="6"/>
+      <c r="STV1" s="6"/>
+      <c r="STY1" s="6"/>
+      <c r="SUB1" s="6"/>
+      <c r="SUE1" s="6"/>
+      <c r="SUH1" s="6"/>
+      <c r="SUK1" s="6"/>
+      <c r="SUN1" s="6"/>
+      <c r="SUQ1" s="6"/>
+      <c r="SUT1" s="6"/>
+      <c r="SUW1" s="6"/>
+      <c r="SUZ1" s="6"/>
+      <c r="SVC1" s="6"/>
+      <c r="SVF1" s="6"/>
+      <c r="SVI1" s="6"/>
+      <c r="SVL1" s="6"/>
+      <c r="SVO1" s="6"/>
+      <c r="SVR1" s="6"/>
+      <c r="SVU1" s="6"/>
+      <c r="SVX1" s="6"/>
+      <c r="SWA1" s="6"/>
+      <c r="SWD1" s="6"/>
+      <c r="SWG1" s="6"/>
+      <c r="SWJ1" s="6"/>
+      <c r="SWM1" s="6"/>
+      <c r="SWP1" s="6"/>
+      <c r="SWS1" s="6"/>
+      <c r="SWV1" s="6"/>
+      <c r="SWY1" s="6"/>
+      <c r="SXB1" s="6"/>
+      <c r="SXE1" s="6"/>
+      <c r="SXH1" s="6"/>
+      <c r="SXK1" s="6"/>
+      <c r="SXN1" s="6"/>
+      <c r="SXQ1" s="6"/>
+      <c r="SXT1" s="6"/>
+      <c r="SXW1" s="6"/>
+      <c r="SXZ1" s="6"/>
+      <c r="SYC1" s="6"/>
+      <c r="SYF1" s="6"/>
+      <c r="SYI1" s="6"/>
+      <c r="SYL1" s="6"/>
+      <c r="SYO1" s="6"/>
+      <c r="SYR1" s="6"/>
+      <c r="SYU1" s="6"/>
+      <c r="SYX1" s="6"/>
+      <c r="SZA1" s="6"/>
+      <c r="SZD1" s="6"/>
+      <c r="SZG1" s="6"/>
+      <c r="SZJ1" s="6"/>
+      <c r="SZM1" s="6"/>
+      <c r="SZP1" s="6"/>
+      <c r="SZS1" s="6"/>
+      <c r="SZV1" s="6"/>
+      <c r="SZY1" s="6"/>
+      <c r="TAB1" s="6"/>
+      <c r="TAE1" s="6"/>
+      <c r="TAH1" s="6"/>
+      <c r="TAK1" s="6"/>
+      <c r="TAN1" s="6"/>
+      <c r="TAQ1" s="6"/>
+      <c r="TAT1" s="6"/>
+      <c r="TAW1" s="6"/>
+      <c r="TAZ1" s="6"/>
+      <c r="TBC1" s="6"/>
+      <c r="TBF1" s="6"/>
+      <c r="TBI1" s="6"/>
+      <c r="TBL1" s="6"/>
+      <c r="TBO1" s="6"/>
+      <c r="TBR1" s="6"/>
+      <c r="TBU1" s="6"/>
+      <c r="TBX1" s="6"/>
+      <c r="TCA1" s="6"/>
+      <c r="TCD1" s="6"/>
+      <c r="TCG1" s="6"/>
+      <c r="TCJ1" s="6"/>
+      <c r="TCM1" s="6"/>
+      <c r="TCP1" s="6"/>
+      <c r="TCS1" s="6"/>
+      <c r="TCV1" s="6"/>
+      <c r="TCY1" s="6"/>
+      <c r="TDB1" s="6"/>
+      <c r="TDE1" s="6"/>
+      <c r="TDH1" s="6"/>
+      <c r="TDK1" s="6"/>
+      <c r="TDN1" s="6"/>
+      <c r="TDQ1" s="6"/>
+      <c r="TDT1" s="6"/>
+      <c r="TDW1" s="6"/>
+      <c r="TDZ1" s="6"/>
+      <c r="TEC1" s="6"/>
+      <c r="TEF1" s="6"/>
+      <c r="TEI1" s="6"/>
+      <c r="TEL1" s="6"/>
+      <c r="TEO1" s="6"/>
+      <c r="TER1" s="6"/>
+      <c r="TEU1" s="6"/>
+      <c r="TEX1" s="6"/>
+      <c r="TFA1" s="6"/>
+      <c r="TFD1" s="6"/>
+      <c r="TFG1" s="6"/>
+      <c r="TFJ1" s="6"/>
+      <c r="TFM1" s="6"/>
+      <c r="TFP1" s="6"/>
+      <c r="TFS1" s="6"/>
+      <c r="TFV1" s="6"/>
+      <c r="TFY1" s="6"/>
+      <c r="TGB1" s="6"/>
+      <c r="TGE1" s="6"/>
+      <c r="TGH1" s="6"/>
+      <c r="TGK1" s="6"/>
+      <c r="TGN1" s="6"/>
+      <c r="TGQ1" s="6"/>
+      <c r="TGT1" s="6"/>
+      <c r="TGW1" s="6"/>
+      <c r="TGZ1" s="6"/>
+      <c r="THC1" s="6"/>
+      <c r="THF1" s="6"/>
+      <c r="THI1" s="6"/>
+      <c r="THL1" s="6"/>
+      <c r="THO1" s="6"/>
+      <c r="THR1" s="6"/>
+      <c r="THU1" s="6"/>
+      <c r="THX1" s="6"/>
+      <c r="TIA1" s="6"/>
+      <c r="TID1" s="6"/>
+      <c r="TIG1" s="6"/>
+      <c r="TIJ1" s="6"/>
+      <c r="TIM1" s="6"/>
+      <c r="TIP1" s="6"/>
+      <c r="TIS1" s="6"/>
+      <c r="TIV1" s="6"/>
+      <c r="TIY1" s="6"/>
+      <c r="TJB1" s="6"/>
+      <c r="TJE1" s="6"/>
+      <c r="TJH1" s="6"/>
+      <c r="TJK1" s="6"/>
+      <c r="TJN1" s="6"/>
+      <c r="TJQ1" s="6"/>
+      <c r="TJT1" s="6"/>
+      <c r="TJW1" s="6"/>
+      <c r="TJZ1" s="6"/>
+      <c r="TKC1" s="6"/>
+      <c r="TKF1" s="6"/>
+      <c r="TKI1" s="6"/>
+      <c r="TKL1" s="6"/>
+      <c r="TKO1" s="6"/>
+      <c r="TKR1" s="6"/>
+      <c r="TKU1" s="6"/>
+      <c r="TKX1" s="6"/>
+      <c r="TLA1" s="6"/>
+      <c r="TLD1" s="6"/>
+      <c r="TLG1" s="6"/>
+      <c r="TLJ1" s="6"/>
+      <c r="TLM1" s="6"/>
+      <c r="TLP1" s="6"/>
+      <c r="TLS1" s="6"/>
+      <c r="TLV1" s="6"/>
+      <c r="TLY1" s="6"/>
+      <c r="TMB1" s="6"/>
+      <c r="TME1" s="6"/>
+      <c r="TMH1" s="6"/>
+      <c r="TMK1" s="6"/>
+      <c r="TMN1" s="6"/>
+      <c r="TMQ1" s="6"/>
+      <c r="TMT1" s="6"/>
+      <c r="TMW1" s="6"/>
+      <c r="TMZ1" s="6"/>
+      <c r="TNC1" s="6"/>
+      <c r="TNF1" s="6"/>
+      <c r="TNI1" s="6"/>
+      <c r="TNL1" s="6"/>
+      <c r="TNO1" s="6"/>
+      <c r="TNR1" s="6"/>
+      <c r="TNU1" s="6"/>
+      <c r="TNX1" s="6"/>
+      <c r="TOA1" s="6"/>
+      <c r="TOD1" s="6"/>
+      <c r="TOG1" s="6"/>
+      <c r="TOJ1" s="6"/>
+      <c r="TOM1" s="6"/>
+      <c r="TOP1" s="6"/>
+      <c r="TOS1" s="6"/>
+      <c r="TOV1" s="6"/>
+      <c r="TOY1" s="6"/>
+      <c r="TPB1" s="6"/>
+      <c r="TPE1" s="6"/>
+      <c r="TPH1" s="6"/>
+      <c r="TPK1" s="6"/>
+      <c r="TPN1" s="6"/>
+      <c r="TPQ1" s="6"/>
+      <c r="TPT1" s="6"/>
+      <c r="TPW1" s="6"/>
+      <c r="TPZ1" s="6"/>
+      <c r="TQC1" s="6"/>
+      <c r="TQF1" s="6"/>
+      <c r="TQI1" s="6"/>
+      <c r="TQL1" s="6"/>
+      <c r="TQO1" s="6"/>
+      <c r="TQR1" s="6"/>
+      <c r="TQU1" s="6"/>
+      <c r="TQX1" s="6"/>
+      <c r="TRA1" s="6"/>
+      <c r="TRD1" s="6"/>
+      <c r="TRG1" s="6"/>
+      <c r="TRJ1" s="6"/>
+      <c r="TRM1" s="6"/>
+      <c r="TRP1" s="6"/>
+      <c r="TRS1" s="6"/>
+      <c r="TRV1" s="6"/>
+      <c r="TRY1" s="6"/>
+      <c r="TSB1" s="6"/>
+      <c r="TSE1" s="6"/>
+      <c r="TSH1" s="6"/>
+      <c r="TSK1" s="6"/>
+      <c r="TSN1" s="6"/>
+      <c r="TSQ1" s="6"/>
+      <c r="TST1" s="6"/>
+      <c r="TSW1" s="6"/>
+      <c r="TSZ1" s="6"/>
+      <c r="TTC1" s="6"/>
+      <c r="TTF1" s="6"/>
+      <c r="TTI1" s="6"/>
+      <c r="TTL1" s="6"/>
+      <c r="TTO1" s="6"/>
+      <c r="TTR1" s="6"/>
+      <c r="TTU1" s="6"/>
+      <c r="TTX1" s="6"/>
+      <c r="TUA1" s="6"/>
+      <c r="TUD1" s="6"/>
+      <c r="TUG1" s="6"/>
+      <c r="TUJ1" s="6"/>
+      <c r="TUM1" s="6"/>
+      <c r="TUP1" s="6"/>
+      <c r="TUS1" s="6"/>
+      <c r="TUV1" s="6"/>
+      <c r="TUY1" s="6"/>
+      <c r="TVB1" s="6"/>
+      <c r="TVE1" s="6"/>
+      <c r="TVH1" s="6"/>
+      <c r="TVK1" s="6"/>
+      <c r="TVN1" s="6"/>
+      <c r="TVQ1" s="6"/>
+      <c r="TVT1" s="6"/>
+      <c r="TVW1" s="6"/>
+      <c r="TVZ1" s="6"/>
+      <c r="TWC1" s="6"/>
+      <c r="TWF1" s="6"/>
+      <c r="TWI1" s="6"/>
+      <c r="TWL1" s="6"/>
+      <c r="TWO1" s="6"/>
+      <c r="TWR1" s="6"/>
+      <c r="TWU1" s="6"/>
+      <c r="TWX1" s="6"/>
+      <c r="TXA1" s="6"/>
+      <c r="TXD1" s="6"/>
+      <c r="TXG1" s="6"/>
+      <c r="TXJ1" s="6"/>
+      <c r="TXM1" s="6"/>
+      <c r="TXP1" s="6"/>
+      <c r="TXS1" s="6"/>
+      <c r="TXV1" s="6"/>
+      <c r="TXY1" s="6"/>
+      <c r="TYB1" s="6"/>
+      <c r="TYE1" s="6"/>
+      <c r="TYH1" s="6"/>
+      <c r="TYK1" s="6"/>
+      <c r="TYN1" s="6"/>
+      <c r="TYQ1" s="6"/>
+      <c r="TYT1" s="6"/>
+      <c r="TYW1" s="6"/>
+      <c r="TYZ1" s="6"/>
+      <c r="TZC1" s="6"/>
+      <c r="TZF1" s="6"/>
+      <c r="TZI1" s="6"/>
+      <c r="TZL1" s="6"/>
+      <c r="TZO1" s="6"/>
+      <c r="TZR1" s="6"/>
+      <c r="TZU1" s="6"/>
+      <c r="TZX1" s="6"/>
+      <c r="UAA1" s="6"/>
+      <c r="UAD1" s="6"/>
+      <c r="UAG1" s="6"/>
+      <c r="UAJ1" s="6"/>
+      <c r="UAM1" s="6"/>
+      <c r="UAP1" s="6"/>
+      <c r="UAS1" s="6"/>
+      <c r="UAV1" s="6"/>
+      <c r="UAY1" s="6"/>
+      <c r="UBB1" s="6"/>
+      <c r="UBE1" s="6"/>
+      <c r="UBH1" s="6"/>
+      <c r="UBK1" s="6"/>
+      <c r="UBN1" s="6"/>
+      <c r="UBQ1" s="6"/>
+      <c r="UBT1" s="6"/>
+      <c r="UBW1" s="6"/>
+      <c r="UBZ1" s="6"/>
+      <c r="UCC1" s="6"/>
+      <c r="UCF1" s="6"/>
+      <c r="UCI1" s="6"/>
+      <c r="UCL1" s="6"/>
+      <c r="UCO1" s="6"/>
+      <c r="UCR1" s="6"/>
+      <c r="UCU1" s="6"/>
+      <c r="UCX1" s="6"/>
+      <c r="UDA1" s="6"/>
+      <c r="UDD1" s="6"/>
+      <c r="UDG1" s="6"/>
+      <c r="UDJ1" s="6"/>
+      <c r="UDM1" s="6"/>
+      <c r="UDP1" s="6"/>
+      <c r="UDS1" s="6"/>
+      <c r="UDV1" s="6"/>
+      <c r="UDY1" s="6"/>
+      <c r="UEB1" s="6"/>
+      <c r="UEE1" s="6"/>
+      <c r="UEH1" s="6"/>
+      <c r="UEK1" s="6"/>
+      <c r="UEN1" s="6"/>
+      <c r="UEQ1" s="6"/>
+      <c r="UET1" s="6"/>
+      <c r="UEW1" s="6"/>
+      <c r="UEZ1" s="6"/>
+      <c r="UFC1" s="6"/>
+      <c r="UFF1" s="6"/>
+      <c r="UFI1" s="6"/>
+      <c r="UFL1" s="6"/>
+      <c r="UFO1" s="6"/>
+      <c r="UFR1" s="6"/>
+      <c r="UFU1" s="6"/>
+      <c r="UFX1" s="6"/>
+      <c r="UGA1" s="6"/>
+      <c r="UGD1" s="6"/>
+      <c r="UGG1" s="6"/>
+      <c r="UGJ1" s="6"/>
+      <c r="UGM1" s="6"/>
+      <c r="UGP1" s="6"/>
+      <c r="UGS1" s="6"/>
+      <c r="UGV1" s="6"/>
+      <c r="UGY1" s="6"/>
+      <c r="UHB1" s="6"/>
+      <c r="UHE1" s="6"/>
+      <c r="UHH1" s="6"/>
+      <c r="UHK1" s="6"/>
+      <c r="UHN1" s="6"/>
+      <c r="UHQ1" s="6"/>
+      <c r="UHT1" s="6"/>
+      <c r="UHW1" s="6"/>
+      <c r="UHZ1" s="6"/>
+      <c r="UIC1" s="6"/>
+      <c r="UIF1" s="6"/>
+      <c r="UII1" s="6"/>
+      <c r="UIL1" s="6"/>
+      <c r="UIO1" s="6"/>
+      <c r="UIR1" s="6"/>
+      <c r="UIU1" s="6"/>
+      <c r="UIX1" s="6"/>
+      <c r="UJA1" s="6"/>
+      <c r="UJD1" s="6"/>
+      <c r="UJG1" s="6"/>
+      <c r="UJJ1" s="6"/>
+      <c r="UJM1" s="6"/>
+      <c r="UJP1" s="6"/>
+      <c r="UJS1" s="6"/>
+      <c r="UJV1" s="6"/>
+      <c r="UJY1" s="6"/>
+      <c r="UKB1" s="6"/>
+      <c r="UKE1" s="6"/>
+      <c r="UKH1" s="6"/>
+      <c r="UKK1" s="6"/>
+      <c r="UKN1" s="6"/>
+      <c r="UKQ1" s="6"/>
+      <c r="UKT1" s="6"/>
+      <c r="UKW1" s="6"/>
+      <c r="UKZ1" s="6"/>
+      <c r="ULC1" s="6"/>
+      <c r="ULF1" s="6"/>
+      <c r="ULI1" s="6"/>
+      <c r="ULL1" s="6"/>
+      <c r="ULO1" s="6"/>
+      <c r="ULR1" s="6"/>
+      <c r="ULU1" s="6"/>
+      <c r="ULX1" s="6"/>
+      <c r="UMA1" s="6"/>
+      <c r="UMD1" s="6"/>
+      <c r="UMG1" s="6"/>
+      <c r="UMJ1" s="6"/>
+      <c r="UMM1" s="6"/>
+      <c r="UMP1" s="6"/>
+      <c r="UMS1" s="6"/>
+      <c r="UMV1" s="6"/>
+      <c r="UMY1" s="6"/>
+      <c r="UNB1" s="6"/>
+      <c r="UNE1" s="6"/>
+      <c r="UNH1" s="6"/>
+      <c r="UNK1" s="6"/>
+      <c r="UNN1" s="6"/>
+      <c r="UNQ1" s="6"/>
+      <c r="UNT1" s="6"/>
+      <c r="UNW1" s="6"/>
+      <c r="UNZ1" s="6"/>
+      <c r="UOC1" s="6"/>
+      <c r="UOF1" s="6"/>
+      <c r="UOI1" s="6"/>
+      <c r="UOL1" s="6"/>
+      <c r="UOO1" s="6"/>
+      <c r="UOR1" s="6"/>
+      <c r="UOU1" s="6"/>
+      <c r="UOX1" s="6"/>
+      <c r="UPA1" s="6"/>
+      <c r="UPD1" s="6"/>
+      <c r="UPG1" s="6"/>
+      <c r="UPJ1" s="6"/>
+      <c r="UPM1" s="6"/>
+      <c r="UPP1" s="6"/>
+      <c r="UPS1" s="6"/>
+      <c r="UPV1" s="6"/>
+      <c r="UPY1" s="6"/>
+      <c r="UQB1" s="6"/>
+      <c r="UQE1" s="6"/>
+      <c r="UQH1" s="6"/>
+      <c r="UQK1" s="6"/>
+      <c r="UQN1" s="6"/>
+      <c r="UQQ1" s="6"/>
+      <c r="UQT1" s="6"/>
+      <c r="UQW1" s="6"/>
+      <c r="UQZ1" s="6"/>
+      <c r="URC1" s="6"/>
+      <c r="URF1" s="6"/>
+      <c r="URI1" s="6"/>
+      <c r="URL1" s="6"/>
+      <c r="URO1" s="6"/>
+      <c r="URR1" s="6"/>
+      <c r="URU1" s="6"/>
+      <c r="URX1" s="6"/>
+      <c r="USA1" s="6"/>
+      <c r="USD1" s="6"/>
+      <c r="USG1" s="6"/>
+      <c r="USJ1" s="6"/>
+      <c r="USM1" s="6"/>
+      <c r="USP1" s="6"/>
+      <c r="USS1" s="6"/>
+      <c r="USV1" s="6"/>
+      <c r="USY1" s="6"/>
+      <c r="UTB1" s="6"/>
+      <c r="UTE1" s="6"/>
+      <c r="UTH1" s="6"/>
+      <c r="UTK1" s="6"/>
+      <c r="UTN1" s="6"/>
+      <c r="UTQ1" s="6"/>
+      <c r="UTT1" s="6"/>
+      <c r="UTW1" s="6"/>
+      <c r="UTZ1" s="6"/>
+      <c r="UUC1" s="6"/>
+      <c r="UUF1" s="6"/>
+      <c r="UUI1" s="6"/>
+      <c r="UUL1" s="6"/>
+      <c r="UUO1" s="6"/>
+      <c r="UUR1" s="6"/>
+      <c r="UUU1" s="6"/>
+      <c r="UUX1" s="6"/>
+      <c r="UVA1" s="6"/>
+      <c r="UVD1" s="6"/>
+      <c r="UVG1" s="6"/>
+      <c r="UVJ1" s="6"/>
+      <c r="UVM1" s="6"/>
+      <c r="UVP1" s="6"/>
+      <c r="UVS1" s="6"/>
+      <c r="UVV1" s="6"/>
+      <c r="UVY1" s="6"/>
+      <c r="UWB1" s="6"/>
+      <c r="UWE1" s="6"/>
+      <c r="UWH1" s="6"/>
+      <c r="UWK1" s="6"/>
+      <c r="UWN1" s="6"/>
+      <c r="UWQ1" s="6"/>
+      <c r="UWT1" s="6"/>
+      <c r="UWW1" s="6"/>
+      <c r="UWZ1" s="6"/>
+      <c r="UXC1" s="6"/>
+      <c r="UXF1" s="6"/>
+      <c r="UXI1" s="6"/>
+      <c r="UXL1" s="6"/>
+      <c r="UXO1" s="6"/>
+      <c r="UXR1" s="6"/>
+      <c r="UXU1" s="6"/>
+      <c r="UXX1" s="6"/>
+      <c r="UYA1" s="6"/>
+      <c r="UYD1" s="6"/>
+      <c r="UYG1" s="6"/>
+      <c r="UYJ1" s="6"/>
+      <c r="UYM1" s="6"/>
+      <c r="UYP1" s="6"/>
+      <c r="UYS1" s="6"/>
+      <c r="UYV1" s="6"/>
+      <c r="UYY1" s="6"/>
+      <c r="UZB1" s="6"/>
+      <c r="UZE1" s="6"/>
+      <c r="UZH1" s="6"/>
+      <c r="UZK1" s="6"/>
+      <c r="UZN1" s="6"/>
+      <c r="UZQ1" s="6"/>
+      <c r="UZT1" s="6"/>
+      <c r="UZW1" s="6"/>
+      <c r="UZZ1" s="6"/>
+      <c r="VAC1" s="6"/>
+      <c r="VAF1" s="6"/>
+      <c r="VAI1" s="6"/>
+      <c r="VAL1" s="6"/>
+      <c r="VAO1" s="6"/>
+      <c r="VAR1" s="6"/>
+      <c r="VAU1" s="6"/>
+      <c r="VAX1" s="6"/>
+      <c r="VBA1" s="6"/>
+      <c r="VBD1" s="6"/>
+      <c r="VBG1" s="6"/>
+      <c r="VBJ1" s="6"/>
+      <c r="VBM1" s="6"/>
+      <c r="VBP1" s="6"/>
+      <c r="VBS1" s="6"/>
+      <c r="VBV1" s="6"/>
+      <c r="VBY1" s="6"/>
+      <c r="VCB1" s="6"/>
+      <c r="VCE1" s="6"/>
+      <c r="VCH1" s="6"/>
+      <c r="VCK1" s="6"/>
+      <c r="VCN1" s="6"/>
+      <c r="VCQ1" s="6"/>
+      <c r="VCT1" s="6"/>
+      <c r="VCW1" s="6"/>
+      <c r="VCZ1" s="6"/>
+      <c r="VDC1" s="6"/>
+      <c r="VDF1" s="6"/>
+      <c r="VDI1" s="6"/>
+      <c r="VDL1" s="6"/>
+      <c r="VDO1" s="6"/>
+      <c r="VDR1" s="6"/>
+      <c r="VDU1" s="6"/>
+      <c r="VDX1" s="6"/>
+      <c r="VEA1" s="6"/>
+      <c r="VED1" s="6"/>
+      <c r="VEG1" s="6"/>
+      <c r="VEJ1" s="6"/>
+      <c r="VEM1" s="6"/>
+      <c r="VEP1" s="6"/>
+      <c r="VES1" s="6"/>
+      <c r="VEV1" s="6"/>
+      <c r="VEY1" s="6"/>
+      <c r="VFB1" s="6"/>
+      <c r="VFE1" s="6"/>
+      <c r="VFH1" s="6"/>
+      <c r="VFK1" s="6"/>
+      <c r="VFN1" s="6"/>
+      <c r="VFQ1" s="6"/>
+      <c r="VFT1" s="6"/>
+      <c r="VFW1" s="6"/>
+      <c r="VFZ1" s="6"/>
+      <c r="VGC1" s="6"/>
+      <c r="VGF1" s="6"/>
+      <c r="VGI1" s="6"/>
+      <c r="VGL1" s="6"/>
+      <c r="VGO1" s="6"/>
+      <c r="VGR1" s="6"/>
+      <c r="VGU1" s="6"/>
+      <c r="VGX1" s="6"/>
+      <c r="VHA1" s="6"/>
+      <c r="VHD1" s="6"/>
+      <c r="VHG1" s="6"/>
+      <c r="VHJ1" s="6"/>
+      <c r="VHM1" s="6"/>
+      <c r="VHP1" s="6"/>
+      <c r="VHS1" s="6"/>
+      <c r="VHV1" s="6"/>
+      <c r="VHY1" s="6"/>
+      <c r="VIB1" s="6"/>
+      <c r="VIE1" s="6"/>
+      <c r="VIH1" s="6"/>
+      <c r="VIK1" s="6"/>
+      <c r="VIN1" s="6"/>
+      <c r="VIQ1" s="6"/>
+      <c r="VIT1" s="6"/>
+      <c r="VIW1" s="6"/>
+      <c r="VIZ1" s="6"/>
+      <c r="VJC1" s="6"/>
+      <c r="VJF1" s="6"/>
+      <c r="VJI1" s="6"/>
+      <c r="VJL1" s="6"/>
+      <c r="VJO1" s="6"/>
+      <c r="VJR1" s="6"/>
+      <c r="VJU1" s="6"/>
+      <c r="VJX1" s="6"/>
+      <c r="VKA1" s="6"/>
+      <c r="VKD1" s="6"/>
+      <c r="VKG1" s="6"/>
+      <c r="VKJ1" s="6"/>
+      <c r="VKM1" s="6"/>
+      <c r="VKP1" s="6"/>
+      <c r="VKS1" s="6"/>
+      <c r="VKV1" s="6"/>
+      <c r="VKY1" s="6"/>
+      <c r="VLB1" s="6"/>
+      <c r="VLE1" s="6"/>
+      <c r="VLH1" s="6"/>
+      <c r="VLK1" s="6"/>
+      <c r="VLN1" s="6"/>
+      <c r="VLQ1" s="6"/>
+      <c r="VLT1" s="6"/>
+      <c r="VLW1" s="6"/>
+      <c r="VLZ1" s="6"/>
+      <c r="VMC1" s="6"/>
+      <c r="VMF1" s="6"/>
+      <c r="VMI1" s="6"/>
+      <c r="VML1" s="6"/>
+      <c r="VMO1" s="6"/>
+      <c r="VMR1" s="6"/>
+      <c r="VMU1" s="6"/>
+      <c r="VMX1" s="6"/>
+      <c r="VNA1" s="6"/>
+      <c r="VND1" s="6"/>
+      <c r="VNG1" s="6"/>
+      <c r="VNJ1" s="6"/>
+      <c r="VNM1" s="6"/>
+      <c r="VNP1" s="6"/>
+      <c r="VNS1" s="6"/>
+      <c r="VNV1" s="6"/>
+      <c r="VNY1" s="6"/>
+      <c r="VOB1" s="6"/>
+      <c r="VOE1" s="6"/>
+      <c r="VOH1" s="6"/>
+      <c r="VOK1" s="6"/>
+      <c r="VON1" s="6"/>
+      <c r="VOQ1" s="6"/>
+      <c r="VOT1" s="6"/>
+      <c r="VOW1" s="6"/>
+      <c r="VOZ1" s="6"/>
+      <c r="VPC1" s="6"/>
+      <c r="VPF1" s="6"/>
+      <c r="VPI1" s="6"/>
+      <c r="VPL1" s="6"/>
+      <c r="VPO1" s="6"/>
+      <c r="VPR1" s="6"/>
+      <c r="VPU1" s="6"/>
+      <c r="VPX1" s="6"/>
+      <c r="VQA1" s="6"/>
+      <c r="VQD1" s="6"/>
+      <c r="VQG1" s="6"/>
+      <c r="VQJ1" s="6"/>
+      <c r="VQM1" s="6"/>
+      <c r="VQP1" s="6"/>
+      <c r="VQS1" s="6"/>
+      <c r="VQV1" s="6"/>
+      <c r="VQY1" s="6"/>
+      <c r="VRB1" s="6"/>
+      <c r="VRE1" s="6"/>
+      <c r="VRH1" s="6"/>
+      <c r="VRK1" s="6"/>
+      <c r="VRN1" s="6"/>
+      <c r="VRQ1" s="6"/>
+      <c r="VRT1" s="6"/>
+      <c r="VRW1" s="6"/>
+      <c r="VRZ1" s="6"/>
+      <c r="VSC1" s="6"/>
+      <c r="VSF1" s="6"/>
+      <c r="VSI1" s="6"/>
+      <c r="VSL1" s="6"/>
+      <c r="VSO1" s="6"/>
+      <c r="VSR1" s="6"/>
+      <c r="VSU1" s="6"/>
+      <c r="VSX1" s="6"/>
+      <c r="VTA1" s="6"/>
+      <c r="VTD1" s="6"/>
+      <c r="VTG1" s="6"/>
+      <c r="VTJ1" s="6"/>
+      <c r="VTM1" s="6"/>
+      <c r="VTP1" s="6"/>
+      <c r="VTS1" s="6"/>
+      <c r="VTV1" s="6"/>
+      <c r="VTY1" s="6"/>
+      <c r="VUB1" s="6"/>
+      <c r="VUE1" s="6"/>
+      <c r="VUH1" s="6"/>
+      <c r="VUK1" s="6"/>
+      <c r="VUN1" s="6"/>
+      <c r="VUQ1" s="6"/>
+      <c r="VUT1" s="6"/>
+      <c r="VUW1" s="6"/>
+      <c r="VUZ1" s="6"/>
+      <c r="VVC1" s="6"/>
+      <c r="VVF1" s="6"/>
+      <c r="VVI1" s="6"/>
+      <c r="VVL1" s="6"/>
+      <c r="VVO1" s="6"/>
+      <c r="VVR1" s="6"/>
+      <c r="VVU1" s="6"/>
+      <c r="VVX1" s="6"/>
+      <c r="VWA1" s="6"/>
+      <c r="VWD1" s="6"/>
+      <c r="VWG1" s="6"/>
+      <c r="VWJ1" s="6"/>
+      <c r="VWM1" s="6"/>
+      <c r="VWP1" s="6"/>
+      <c r="VWS1" s="6"/>
+      <c r="VWV1" s="6"/>
+      <c r="VWY1" s="6"/>
+      <c r="VXB1" s="6"/>
+      <c r="VXE1" s="6"/>
+      <c r="VXH1" s="6"/>
+      <c r="VXK1" s="6"/>
+      <c r="VXN1" s="6"/>
+      <c r="VXQ1" s="6"/>
+      <c r="VXT1" s="6"/>
+      <c r="VXW1" s="6"/>
+      <c r="VXZ1" s="6"/>
+      <c r="VYC1" s="6"/>
+      <c r="VYF1" s="6"/>
+      <c r="VYI1" s="6"/>
+      <c r="VYL1" s="6"/>
+      <c r="VYO1" s="6"/>
+      <c r="VYR1" s="6"/>
+      <c r="VYU1" s="6"/>
+      <c r="VYX1" s="6"/>
+      <c r="VZA1" s="6"/>
+      <c r="VZD1" s="6"/>
+      <c r="VZG1" s="6"/>
+      <c r="VZJ1" s="6"/>
+      <c r="VZM1" s="6"/>
+      <c r="VZP1" s="6"/>
+      <c r="VZS1" s="6"/>
+      <c r="VZV1" s="6"/>
+      <c r="VZY1" s="6"/>
+      <c r="WAB1" s="6"/>
+      <c r="WAE1" s="6"/>
+      <c r="WAH1" s="6"/>
+      <c r="WAK1" s="6"/>
+      <c r="WAN1" s="6"/>
+      <c r="WAQ1" s="6"/>
+      <c r="WAT1" s="6"/>
+      <c r="WAW1" s="6"/>
+      <c r="WAZ1" s="6"/>
+      <c r="WBC1" s="6"/>
+      <c r="WBF1" s="6"/>
+      <c r="WBI1" s="6"/>
+      <c r="WBL1" s="6"/>
+      <c r="WBO1" s="6"/>
+      <c r="WBR1" s="6"/>
+      <c r="WBU1" s="6"/>
+      <c r="WBX1" s="6"/>
+      <c r="WCA1" s="6"/>
+      <c r="WCD1" s="6"/>
+      <c r="WCG1" s="6"/>
+      <c r="WCJ1" s="6"/>
+      <c r="WCM1" s="6"/>
+      <c r="WCP1" s="6"/>
+      <c r="WCS1" s="6"/>
+      <c r="WCV1" s="6"/>
+      <c r="WCY1" s="6"/>
+      <c r="WDB1" s="6"/>
+      <c r="WDE1" s="6"/>
+      <c r="WDH1" s="6"/>
+      <c r="WDK1" s="6"/>
+      <c r="WDN1" s="6"/>
+      <c r="WDQ1" s="6"/>
+      <c r="WDT1" s="6"/>
+      <c r="WDW1" s="6"/>
+      <c r="WDZ1" s="6"/>
+      <c r="WEC1" s="6"/>
+      <c r="WEF1" s="6"/>
+      <c r="WEI1" s="6"/>
+      <c r="WEL1" s="6"/>
+      <c r="WEO1" s="6"/>
+      <c r="WER1" s="6"/>
+      <c r="WEU1" s="6"/>
+      <c r="WEX1" s="6"/>
+      <c r="WFA1" s="6"/>
+      <c r="WFD1" s="6"/>
+      <c r="WFG1" s="6"/>
+      <c r="WFJ1" s="6"/>
+      <c r="WFM1" s="6"/>
+      <c r="WFP1" s="6"/>
+      <c r="WFS1" s="6"/>
+      <c r="WFV1" s="6"/>
+      <c r="WFY1" s="6"/>
+      <c r="WGB1" s="6"/>
+      <c r="WGE1" s="6"/>
+      <c r="WGH1" s="6"/>
+      <c r="WGK1" s="6"/>
+      <c r="WGN1" s="6"/>
+      <c r="WGQ1" s="6"/>
+      <c r="WGT1" s="6"/>
+      <c r="WGW1" s="6"/>
+      <c r="WGZ1" s="6"/>
+      <c r="WHC1" s="6"/>
+      <c r="WHF1" s="6"/>
+      <c r="WHI1" s="6"/>
+      <c r="WHL1" s="6"/>
+      <c r="WHO1" s="6"/>
+      <c r="WHR1" s="6"/>
+      <c r="WHU1" s="6"/>
+      <c r="WHX1" s="6"/>
+      <c r="WIA1" s="6"/>
+      <c r="WID1" s="6"/>
+      <c r="WIG1" s="6"/>
+      <c r="WIJ1" s="6"/>
+      <c r="WIM1" s="6"/>
+      <c r="WIP1" s="6"/>
+      <c r="WIS1" s="6"/>
+      <c r="WIV1" s="6"/>
+      <c r="WIY1" s="6"/>
+      <c r="WJB1" s="6"/>
+      <c r="WJE1" s="6"/>
+      <c r="WJH1" s="6"/>
+      <c r="WJK1" s="6"/>
+      <c r="WJN1" s="6"/>
+      <c r="WJQ1" s="6"/>
+      <c r="WJT1" s="6"/>
+      <c r="WJW1" s="6"/>
+      <c r="WJZ1" s="6"/>
+      <c r="WKC1" s="6"/>
+      <c r="WKF1" s="6"/>
+      <c r="WKI1" s="6"/>
+      <c r="WKL1" s="6"/>
+      <c r="WKO1" s="6"/>
+      <c r="WKR1" s="6"/>
+      <c r="WKU1" s="6"/>
+      <c r="WKX1" s="6"/>
+      <c r="WLA1" s="6"/>
+      <c r="WLD1" s="6"/>
+      <c r="WLG1" s="6"/>
+      <c r="WLJ1" s="6"/>
+      <c r="WLM1" s="6"/>
+      <c r="WLP1" s="6"/>
+      <c r="WLS1" s="6"/>
+      <c r="WLV1" s="6"/>
+      <c r="WLY1" s="6"/>
+      <c r="WMB1" s="6"/>
+      <c r="WME1" s="6"/>
+      <c r="WMH1" s="6"/>
+      <c r="WMK1" s="6"/>
+      <c r="WMN1" s="6"/>
+      <c r="WMQ1" s="6"/>
+      <c r="WMT1" s="6"/>
+      <c r="WMW1" s="6"/>
+      <c r="WMZ1" s="6"/>
+      <c r="WNC1" s="6"/>
+      <c r="WNF1" s="6"/>
+      <c r="WNI1" s="6"/>
+      <c r="WNL1" s="6"/>
+      <c r="WNO1" s="6"/>
+      <c r="WNR1" s="6"/>
+      <c r="WNU1" s="6"/>
+      <c r="WNX1" s="6"/>
+      <c r="WOA1" s="6"/>
+      <c r="WOD1" s="6"/>
+      <c r="WOG1" s="6"/>
+      <c r="WOJ1" s="6"/>
+      <c r="WOM1" s="6"/>
+      <c r="WOP1" s="6"/>
+      <c r="WOS1" s="6"/>
+      <c r="WOV1" s="6"/>
+      <c r="WOY1" s="6"/>
+      <c r="WPB1" s="6"/>
+      <c r="WPE1" s="6"/>
+      <c r="WPH1" s="6"/>
+      <c r="WPK1" s="6"/>
+      <c r="WPN1" s="6"/>
+      <c r="WPQ1" s="6"/>
+      <c r="WPT1" s="6"/>
+      <c r="WPW1" s="6"/>
+      <c r="WPZ1" s="6"/>
+      <c r="WQC1" s="6"/>
+      <c r="WQF1" s="6"/>
+      <c r="WQI1" s="6"/>
+      <c r="WQL1" s="6"/>
+      <c r="WQO1" s="6"/>
+      <c r="WQR1" s="6"/>
+      <c r="WQU1" s="6"/>
+      <c r="WQX1" s="6"/>
+      <c r="WRA1" s="6"/>
+      <c r="WRD1" s="6"/>
+      <c r="WRG1" s="6"/>
+      <c r="WRJ1" s="6"/>
+      <c r="WRM1" s="6"/>
+      <c r="WRP1" s="6"/>
+      <c r="WRS1" s="6"/>
+      <c r="WRV1" s="6"/>
+      <c r="WRY1" s="6"/>
+      <c r="WSB1" s="6"/>
+      <c r="WSE1" s="6"/>
+      <c r="WSH1" s="6"/>
+      <c r="WSK1" s="6"/>
+      <c r="WSN1" s="6"/>
+      <c r="WSQ1" s="6"/>
+      <c r="WST1" s="6"/>
+      <c r="WSW1" s="6"/>
+      <c r="WSZ1" s="6"/>
+      <c r="WTC1" s="6"/>
+      <c r="WTF1" s="6"/>
+      <c r="WTI1" s="6"/>
+      <c r="WTL1" s="6"/>
+      <c r="WTO1" s="6"/>
+      <c r="WTR1" s="6"/>
+      <c r="WTU1" s="6"/>
+      <c r="WTX1" s="6"/>
+      <c r="WUA1" s="6"/>
+      <c r="WUD1" s="6"/>
+      <c r="WUG1" s="6"/>
+      <c r="WUJ1" s="6"/>
+      <c r="WUM1" s="6"/>
+      <c r="WUP1" s="6"/>
+      <c r="WUS1" s="6"/>
+      <c r="WUV1" s="6"/>
+      <c r="WUY1" s="6"/>
+      <c r="WVB1" s="6"/>
+      <c r="WVE1" s="6"/>
+      <c r="WVH1" s="6"/>
+      <c r="WVK1" s="6"/>
+      <c r="WVN1" s="6"/>
+      <c r="WVQ1" s="6"/>
+      <c r="WVT1" s="6"/>
+      <c r="WVW1" s="6"/>
+      <c r="WVZ1" s="6"/>
+      <c r="WWC1" s="6"/>
+      <c r="WWF1" s="6"/>
+      <c r="WWI1" s="6"/>
+      <c r="WWL1" s="6"/>
+      <c r="WWO1" s="6"/>
+      <c r="WWR1" s="6"/>
+      <c r="WWU1" s="6"/>
+      <c r="WWX1" s="6"/>
+      <c r="WXA1" s="6"/>
+      <c r="WXD1" s="6"/>
+      <c r="WXG1" s="6"/>
+      <c r="WXJ1" s="6"/>
+      <c r="WXM1" s="6"/>
+      <c r="WXP1" s="6"/>
+      <c r="WXS1" s="6"/>
+      <c r="WXV1" s="6"/>
+      <c r="WXY1" s="6"/>
+      <c r="WYB1" s="6"/>
+      <c r="WYE1" s="6"/>
+      <c r="WYH1" s="6"/>
+      <c r="WYK1" s="6"/>
+      <c r="WYN1" s="6"/>
+      <c r="WYQ1" s="6"/>
+      <c r="WYT1" s="6"/>
+      <c r="WYW1" s="6"/>
+      <c r="WYZ1" s="6"/>
+      <c r="WZC1" s="6"/>
+      <c r="WZF1" s="6"/>
+      <c r="WZI1" s="6"/>
+      <c r="WZL1" s="6"/>
+      <c r="WZO1" s="6"/>
+      <c r="WZR1" s="6"/>
+      <c r="WZU1" s="6"/>
+      <c r="WZX1" s="6"/>
+      <c r="XAA1" s="6"/>
+      <c r="XAD1" s="6"/>
+      <c r="XAG1" s="6"/>
+      <c r="XAJ1" s="6"/>
+      <c r="XAM1" s="6"/>
+      <c r="XAP1" s="6"/>
+      <c r="XAS1" s="6"/>
+      <c r="XAV1" s="6"/>
+      <c r="XAY1" s="6"/>
+      <c r="XBB1" s="6"/>
+      <c r="XBE1" s="6"/>
+      <c r="XBH1" s="6"/>
+      <c r="XBK1" s="6"/>
+      <c r="XBN1" s="6"/>
+      <c r="XBQ1" s="6"/>
+      <c r="XBT1" s="6"/>
+      <c r="XBW1" s="6"/>
+      <c r="XBZ1" s="6"/>
+      <c r="XCC1" s="6"/>
+      <c r="XCF1" s="6"/>
+      <c r="XCI1" s="6"/>
+      <c r="XCL1" s="6"/>
+      <c r="XCO1" s="6"/>
+      <c r="XCR1" s="6"/>
+      <c r="XCU1" s="6"/>
+      <c r="XCX1" s="6"/>
+      <c r="XDA1" s="6"/>
+      <c r="XDD1" s="6"/>
+      <c r="XDG1" s="6"/>
+      <c r="XDJ1" s="6"/>
+      <c r="XDM1" s="6"/>
+      <c r="XDP1" s="6"/>
+      <c r="XDS1" s="6"/>
+      <c r="XDV1" s="6"/>
+      <c r="XDY1" s="6"/>
+      <c r="XEB1" s="6"/>
+      <c r="XEE1" s="6"/>
+      <c r="XEH1" s="6"/>
+      <c r="XEK1" s="6"/>
+      <c r="XEN1" s="6"/>
+      <c r="XEQ1" s="6"/>
+      <c r="XET1" s="6"/>
+      <c r="XEW1" s="6"/>
+      <c r="XEZ1" s="6"/>
+      <c r="XFC1" s="6"/>
+    </row>
+    <row r="2" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="6"/>
+    </row>
+    <row r="3" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="10">
+        <v>0</v>
+      </c>
+      <c r="D6" s="8"/>
+    </row>
+    <row r="7" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="10">
+        <v>365</v>
+      </c>
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="9"/>
+    </row>
+    <row r="10" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" s="9"/>
+    </row>
+    <row r="11" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9"/>
+    </row>
+    <row r="12" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="9"/>
+    </row>
+    <row r="13" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="9"/>
+    </row>
+    <row r="14" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="9"/>
+    </row>
+    <row r="15" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+      <c r="C15" s="11"/>
+      <c r="D15" s="9"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C5" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{DF88B38D-103F-4C4B-B791-6EEFDCF362A1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31A8171-F5E4-4C99-A795-CE56041B2248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5A6051-8296-450D-97E6-F3F57BC3DADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6533,7 +6533,7 @@
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="7"/>
@@ -6652,7 +6652,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{DF88B38D-103F-4C4B-B791-6EEFDCF362A1}"/>
+    <hyperlink ref="C5" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{BA19A19E-28C3-4176-A764-AFC1DFD8FA01}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E5A6051-8296-450D-97E6-F3F57BC3DADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5BF87E-6060-48D9-ABA0-A3B85493D2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="28">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t xml:space="preserve">Automation Internal Program for Announcement </t>
+  </si>
+  <si>
+    <t>cke_1_contents</t>
   </si>
 </sst>
 </file>
@@ -474,14 +477,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,7 +495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -503,7 +506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -514,7 +517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -525,7 +528,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -536,7 +539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -547,7 +550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -558,7 +561,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -569,18 +572,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -591,7 +594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -602,7 +605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -613,7 +616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -624,7 +627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -635,7 +638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -658,13 +661,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A1553C-F7A5-4DD1-9371-6162AF52CB21}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="40.5703125" customWidth="1"/>
-    <col min="3" max="3" width="64.28515625" customWidth="1"/>
+    <col min="2" max="2" width="40.54296875" customWidth="1"/>
+    <col min="3" max="3" width="64.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -686,7 +689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -697,7 +700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -708,7 +711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -719,7 +722,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -730,7 +733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -741,7 +744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -752,7 +755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -763,7 +766,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -774,7 +777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -785,7 +788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -796,7 +799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -807,7 +810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -818,7 +821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -840,14 +843,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50E0F2B-3F25-474D-88CC-BA332CE28F6A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="44.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="30.81640625" customWidth="1"/>
+    <col min="3" max="3" width="44.81640625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -858,7 +861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -869,7 +872,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -880,7 +883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -891,7 +894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -902,7 +905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -913,7 +916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -924,7 +927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -935,7 +938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -946,7 +949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -957,7 +960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -968,7 +971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -979,7 +982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -990,7 +993,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1012,14 +1015,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0851E1-AAF8-44F9-AFC4-73C66EBF0B6F}">
   <dimension ref="A1:XFC15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="53.140625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="53.1796875" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6490,7 +6493,7 @@
       <c r="XEZ1" s="6"/>
       <c r="XFC1" s="6"/>
     </row>
-    <row r="2" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -6502,7 +6505,7 @@
       </c>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -6514,7 +6517,7 @@
       </c>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6526,7 +6529,7 @@
       </c>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6538,7 +6541,7 @@
       </c>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -6550,7 +6553,7 @@
       </c>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -6562,7 +6565,7 @@
       </c>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -6574,7 +6577,7 @@
       </c>
       <c r="D8" s="9"/>
     </row>
-    <row r="9" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -6586,7 +6589,7 @@
       </c>
       <c r="D9" s="9"/>
     </row>
-    <row r="10" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -6598,7 +6601,7 @@
       </c>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -6610,7 +6613,7 @@
       </c>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -6622,7 +6625,7 @@
       </c>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6634,7 +6637,7 @@
       </c>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -6646,7 +6649,7 @@
       </c>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
       <c r="C15" s="11"/>
       <c r="D15" s="9"/>
     </row>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5BF87E-6060-48D9-ABA0-A3B85493D2A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C2D777-E65F-4829-8D0D-35716EACC84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -477,14 +477,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,7 +495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -506,7 +506,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -517,7 +517,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -528,7 +528,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -539,7 +539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -550,7 +550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -561,7 +561,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -572,7 +572,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -583,7 +583,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -594,7 +594,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -605,7 +605,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -616,7 +616,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -627,7 +627,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -638,7 +638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -661,13 +661,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A1553C-F7A5-4DD1-9371-6162AF52CB21}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="40.54296875" customWidth="1"/>
-    <col min="3" max="3" width="64.26953125" customWidth="1"/>
+    <col min="2" max="2" width="40.5703125" customWidth="1"/>
+    <col min="3" max="3" width="64.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -678,7 +678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -689,7 +689,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -700,7 +700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -711,7 +711,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -722,7 +722,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -733,7 +733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -744,7 +744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -755,7 +755,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -766,7 +766,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -777,7 +777,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -788,7 +788,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -799,7 +799,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -810,7 +810,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -821,7 +821,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -843,14 +843,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50E0F2B-3F25-474D-88CC-BA332CE28F6A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.81640625" customWidth="1"/>
-    <col min="3" max="3" width="44.81640625" style="7" customWidth="1"/>
-    <col min="4" max="4" width="20.26953125" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" customWidth="1"/>
+    <col min="3" max="3" width="44.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -861,7 +861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -872,7 +872,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -883,7 +883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -894,7 +894,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -905,7 +905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -916,7 +916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -927,7 +927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -938,7 +938,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -949,7 +949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -960,7 +960,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -971,7 +971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -982,7 +982,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -993,7 +993,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1015,14 +1015,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0851E1-AAF8-44F9-AFC4-73C66EBF0B6F}">
   <dimension ref="A1:XFC15"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="53.1796875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6493,7 +6493,7 @@
       <c r="XEZ1" s="6"/>
       <c r="XFC1" s="6"/>
     </row>
-    <row r="2" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -6505,7 +6505,7 @@
       </c>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6541,7 +6541,7 @@
       </c>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -6565,7 +6565,7 @@
       </c>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="D8" s="9"/>
     </row>
-    <row r="9" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -6589,7 +6589,7 @@
       </c>
       <c r="D9" s="9"/>
     </row>
-    <row r="10" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -6613,7 +6613,7 @@
       </c>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6637,7 +6637,7 @@
       </c>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
       <c r="C15" s="11"/>
       <c r="D15" s="9"/>
     </row>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78C2D777-E65F-4829-8D0D-35716EACC84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3C964-56A0-4DF7-B08F-C675F7915CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="29">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -108,12 +108,15 @@
   <si>
     <t>cke_1_contents</t>
   </si>
+  <si>
+    <t>Objectives__c</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +151,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -170,7 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -195,6 +204,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -476,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
@@ -577,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -648,6 +658,12 @@
       <c r="C15" s="3" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="12"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1019,7 +1035,7 @@
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="53.140625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="60.7109375" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -6650,7 +6666,15 @@
       <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
-      <c r="C15" s="11"/>
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
       <c r="D15" s="9"/>
     </row>
   </sheetData>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3C964-56A0-4DF7-B08F-C675F7915CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1022C3-9A9C-457D-8A9C-00907410FF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="29">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -106,10 +106,10 @@
     <t xml:space="preserve">Automation Internal Program for Announcement </t>
   </si>
   <si>
-    <t>cke_1_contents</t>
+    <t>Objectives__c</t>
   </si>
   <si>
-    <t>Objectives__c</t>
+    <t>fieldAccount__c</t>
   </si>
 </sst>
 </file>
@@ -587,7 +587,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -6550,7 +6550,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>13</v>
@@ -6682,5 +6682,6 @@
     <hyperlink ref="C5" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{BA19A19E-28C3-4176-A764-AFC1DFD8FA01}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,17 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F1022C3-9A9C-457D-8A9C-00907410FF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30546FB0-A7E3-4EB5-99E7-8D184D9B803A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
-    <sheet name="Creation1" sheetId="4" r:id="rId2"/>
-    <sheet name="CreationWithoutDescription" sheetId="5" r:id="rId3"/>
-    <sheet name="CreationForAnnouncement" sheetId="6" r:id="rId4"/>
+    <sheet name="Creation_v" sheetId="7" r:id="rId2"/>
+    <sheet name="AnnouncementCreation_v" sheetId="8" r:id="rId3"/>
+    <sheet name="Creation1" sheetId="4" r:id="rId4"/>
+    <sheet name="CreationWithoutDescription" sheetId="5" r:id="rId5"/>
+    <sheet name="CreationForAnnouncement" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -23,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="54">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -111,12 +113,87 @@
   <si>
     <t>fieldAccount__c</t>
   </si>
+  <si>
+    <t>fieldProgramName__c</t>
+  </si>
+  <si>
+    <t>Internal Program Flow</t>
+  </si>
+  <si>
+    <t>fieldProgramType__c</t>
+  </si>
+  <si>
+    <t>fieldFunderType__c</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>fieldCFDA_Data__c</t>
+  </si>
+  <si>
+    <t>checked</t>
+  </si>
+  <si>
+    <t>fieldAnnouncementName__c</t>
+  </si>
+  <si>
+    <t>fieldAnnouncementDescription__c</t>
+  </si>
+  <si>
+    <t>Announcement test</t>
+  </si>
+  <si>
+    <t>fieldFOAPublicationDate__c</t>
+  </si>
+  <si>
+    <t>fieldApplicationDeadlineWithDateTime__c</t>
+  </si>
+  <si>
+    <t>fieldProjectedAwardDateTime__c</t>
+  </si>
+  <si>
+    <t>fieldEligibleApplicantTypes__c</t>
+  </si>
+  <si>
+    <t>State government</t>
+  </si>
+  <si>
+    <t>Financials</t>
+  </si>
+  <si>
+    <t>fieldAwardCeiling__c</t>
+  </si>
+  <si>
+    <t>fieldAwardFloor__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedAverageSizeOfAward__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedNumberOfAwards__c</t>
+  </si>
+  <si>
+    <t>fieldObligatedAmount__c</t>
+  </si>
+  <si>
+    <t>Overview</t>
+  </si>
+  <si>
+    <t>fieldEstimatedProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldEstimatedProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>Announcement created for calendar test</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -157,6 +234,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -179,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -205,6 +288,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -487,14 +571,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,7 +589,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -516,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -527,7 +611,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -538,7 +622,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -549,7 +633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -560,7 +644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -571,7 +655,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -582,7 +666,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -593,7 +677,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -604,7 +688,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -615,7 +699,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -626,7 +710,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -637,7 +721,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -648,7 +732,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -659,10 +743,10 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B16" s="12"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
     </row>
   </sheetData>
@@ -675,15 +759,377 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8294947D-3D8A-4BC8-9038-91856880D2A5}">
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{4D10864A-444C-46A3-A0C2-EF386BE911DD}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A7CB43F-0F6B-40EE-96F8-8B1B43B17A1C}">
+  <dimension ref="A1:C16"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="11">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C15" s="11"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="C16" s="11"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C7" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{3A21C0D4-D75B-4B84-9BF0-DE94ED6E842F}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A1553C-F7A5-4DD1-9371-6162AF52CB21}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="40.5703125" customWidth="1"/>
-    <col min="3" max="3" width="64.28515625" customWidth="1"/>
+    <col min="2" max="2" width="40.5546875" customWidth="1"/>
+    <col min="3" max="3" width="64.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -694,7 +1140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -705,7 +1151,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -716,7 +1162,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -727,7 +1173,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -738,7 +1184,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -749,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -760,7 +1206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -771,7 +1217,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -782,7 +1228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -793,7 +1239,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -804,7 +1250,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -815,7 +1261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -826,7 +1272,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -837,7 +1283,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -856,17 +1302,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50E0F2B-3F25-474D-88CC-BA332CE28F6A}">
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.85546875" customWidth="1"/>
-    <col min="3" max="3" width="44.85546875" style="7" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
+    <col min="3" max="3" width="44.88671875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -877,7 +1323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -888,7 +1334,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -899,7 +1345,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -910,7 +1356,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -921,7 +1367,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -932,7 +1378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -943,7 +1389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -954,7 +1400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -965,7 +1411,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -976,7 +1422,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -987,7 +1433,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -998,7 +1444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -1009,7 +1455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -1028,17 +1474,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0851E1-AAF8-44F9-AFC4-73C66EBF0B6F}">
   <dimension ref="A1:XFC15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="1" max="1" width="23.109375" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="60.7109375" style="10" customWidth="1"/>
+    <col min="3" max="3" width="60.6640625" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6509,7 +6955,7 @@
       <c r="XEZ1" s="6"/>
       <c r="XFC1" s="6"/>
     </row>
-    <row r="2" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -6521,7 +6967,7 @@
       </c>
       <c r="D2" s="6"/>
     </row>
-    <row r="3" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -6533,7 +6979,7 @@
       </c>
       <c r="D3" s="7"/>
     </row>
-    <row r="4" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -6545,7 +6991,7 @@
       </c>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -6557,7 +7003,7 @@
       </c>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -6569,7 +7015,7 @@
       </c>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -6581,7 +7027,7 @@
       </c>
       <c r="D7" s="9"/>
     </row>
-    <row r="8" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -6593,7 +7039,7 @@
       </c>
       <c r="D8" s="9"/>
     </row>
-    <row r="9" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -6605,7 +7051,7 @@
       </c>
       <c r="D9" s="9"/>
     </row>
-    <row r="10" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -6617,7 +7063,7 @@
       </c>
       <c r="D10" s="9"/>
     </row>
-    <row r="11" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -6629,7 +7075,7 @@
       </c>
       <c r="D11" s="9"/>
     </row>
-    <row r="12" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -6641,7 +7087,7 @@
       </c>
       <c r="D12" s="9"/>
     </row>
-    <row r="13" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -6653,7 +7099,7 @@
       </c>
       <c r="D13" s="9"/>
     </row>
-    <row r="14" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -6665,7 +7111,7 @@
       </c>
       <c r="D14" s="9"/>
     </row>
-    <row r="15" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>3</v>
       </c>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30546FB0-A7E3-4EB5-99E7-8D184D9B803A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5284B5BB-16D9-4603-8806-FB224E9E3A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -604,11 +604,11 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="B3" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5284B5BB-16D9-4603-8806-FB224E9E3A6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798419C6-67D0-40EA-99DB-446C44FBB53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -978,10 +978,10 @@
         <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
+      </c>
+      <c r="C3">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -989,10 +989,10 @@
         <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1000,10 +1000,10 @@
         <v>50</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C5">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -1011,10 +1011,10 @@
         <v>50</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
-        <v>365</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -1022,10 +1022,10 @@
         <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -1033,10 +1033,10 @@
         <v>50</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
+        <v>42</v>
+      </c>
+      <c r="C8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1044,10 +1044,10 @@
         <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
+        <v>52</v>
+      </c>
+      <c r="C9">
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -1113,7 +1113,7 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{3A21C0D4-D75B-4B84-9BF0-DE94ED6E842F}"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{3A21C0D4-D75B-4B84-9BF0-DE94ED6E842F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{798419C6-67D0-40EA-99DB-446C44FBB53B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB15489-1E26-4B25-8F25-CA7DA7A46F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -285,8 +285,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -604,7 +602,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C3" t="s">
@@ -744,7 +742,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="12"/>
+      <c r="B16" s="10"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="5"/>
@@ -782,7 +780,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="11" t="s">
         <v>29</v>
       </c>
       <c r="C2" t="s">
@@ -793,7 +791,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="11" t="s">
         <v>31</v>
       </c>
       <c r="C3" t="s">
@@ -804,7 +802,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="11" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -837,7 +835,7 @@
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -848,7 +846,7 @@
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="11" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -859,7 +857,7 @@
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="11" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="3" t="s">
@@ -1101,15 +1099,15 @@
       <c r="B14" t="s">
         <v>49</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="5">
         <v>15000</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C15" s="11"/>
+      <c r="C15" s="5"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="C16" s="11"/>
+      <c r="C16" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1481,7 +1479,7 @@
   <cols>
     <col min="1" max="1" width="23.109375" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="3" width="60.6640625" style="10" customWidth="1"/>
+    <col min="3" max="3" width="60.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1023 1026:2046 2049:3072 3075:4095 4098:5118 5121:6144 6147:7167 7170:8190 8193:9216 9219:10239 10242:11262 11265:12288 12291:13311 13314:14334 14337:15360 15363:16383" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6986,7 +6984,7 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="7"/>
@@ -7010,7 +7008,7 @@
       <c r="B6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="10">
+      <c r="C6">
         <v>0</v>
       </c>
       <c r="D6" s="8"/>
@@ -7022,7 +7020,7 @@
       <c r="B7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7">
         <v>365</v>
       </c>
       <c r="D7" s="9"/>
@@ -7034,7 +7032,7 @@
       <c r="B8" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="9"/>
@@ -7046,7 +7044,7 @@
       <c r="B9" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="9"/>
@@ -7058,7 +7056,7 @@
       <c r="B10" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="9"/>
@@ -7070,7 +7068,7 @@
       <c r="B11" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="9"/>
@@ -7082,7 +7080,7 @@
       <c r="B12" t="s">
         <v>22</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="D12" s="9"/>
@@ -7094,7 +7092,7 @@
       <c r="B13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D13" s="9"/>
@@ -7106,7 +7104,7 @@
       <c r="B14" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="5" t="s">
         <v>6</v>
       </c>
       <c r="D14" s="9"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25330"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB15489-1E26-4B25-8F25-CA7DA7A46F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C2F22D-A80F-4A4A-BED7-D7934971F184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -828,7 +828,7 @@
         <v>15</v>
       </c>
       <c r="C6" s="3">
-        <v>365</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25427"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C2F22D-A80F-4A4A-BED7-D7934971F184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3232C1BC-B0C0-4C5A-A076-7ED811AB15E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
@@ -193,7 +193,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -229,12 +229,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF202124"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <sz val="7"/>
       <color rgb="FF202124"/>
       <name val="Consolas"/>
@@ -262,7 +256,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -286,7 +280,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -568,12 +561,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D795F61-CC1F-4314-B1D8-0852B981BA18}">
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -591,8 +584,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>5</v>
+      <c r="B2" s="10" t="s">
+        <v>29</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -602,22 +595,22 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>34</v>
+      <c r="B3" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
+      <c r="B4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -625,10 +618,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="C5" s="3">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -636,43 +629,43 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3">
-        <v>0</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3">
-        <v>365</v>
+      <c r="B7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" t="s">
-        <v>16</v>
+      <c r="B8" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" t="s">
-        <v>8</v>
+      <c r="B9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -742,14 +735,11 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B16" s="10"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B18" s="5"/>
+      <c r="B16" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C5" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{7EE9E90B-967F-44F2-8381-163CD7361D89}"/>
+    <hyperlink ref="C4" r:id="rId1" display="https://test7-internal.my.salesforce.com/00E0b000001Fm3Y" xr:uid="{E1F97CBA-2299-4C5C-9A3F-BE0AC4C69AE9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -780,7 +770,7 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>29</v>
       </c>
       <c r="C2" t="s">
@@ -791,7 +781,7 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>31</v>
       </c>
       <c r="C3" t="s">
@@ -802,7 +792,7 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -835,7 +825,7 @@
       <c r="A7" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -846,7 +836,7 @@
       <c r="A8" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -857,7 +847,7 @@
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="3" t="s">

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25831"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26026"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3232C1BC-B0C0-4C5A-A076-7ED811AB15E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3229B9D4-1230-4DCB-8AEC-916D61FB28D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="3" r:id="rId1"/>
     <sheet name="Creation_v" sheetId="7" r:id="rId2"/>
     <sheet name="AnnouncementCreation_v" sheetId="8" r:id="rId3"/>
-    <sheet name="Creation1" sheetId="4" r:id="rId4"/>
-    <sheet name="CreationWithoutDescription" sheetId="5" r:id="rId5"/>
-    <sheet name="CreationForAnnouncement" sheetId="6" r:id="rId6"/>
+    <sheet name="AnnouncementCreationCalendar_v" sheetId="9" r:id="rId4"/>
+    <sheet name="Creation1" sheetId="4" r:id="rId5"/>
+    <sheet name="CreationWithoutDescription" sheetId="5" r:id="rId6"/>
+    <sheet name="CreationForAnnouncement" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="54">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1109,6 +1110,163 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E032D7E5-9EEB-448F-87FD-9AA9E6F783C2}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="36.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="5">
+        <v>15000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A1553C-F7A5-4DD1-9371-6162AF52CB21}">
   <dimension ref="A1:C15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1290,7 +1448,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50E0F2B-3F25-474D-88CC-BA332CE28F6A}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1462,7 +1620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D0851E1-AAF8-44F9-AFC4-73C66EBF0B6F}">
   <dimension ref="A1:XFC15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/Program_Field_Values.xlsx
+++ b/src/main/resources/Program_Field_Values.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69AC121B-031D-455D-8FCE-629B53FF6DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD10F27-EC68-4ED0-B54C-4EFBE52702AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation_Bulk_Record" sheetId="11" r:id="rId1"/>
@@ -621,7 +621,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -632,7 +632,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -643,7 +643,7 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
